--- a/Results/Phase 2/Hydrogen/hydrogen photochemical ozone formation results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen photochemical ozone formation results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01562336541537822</v>
+        <v>0.01562336541537824</v>
       </c>
       <c r="C2" t="n">
         <v>0.01527337266097949</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0154971685753846</v>
+        <v>0.01549716857538461</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01209661509329324</v>
+        <v>0.01209661509329323</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01542554683442085</v>
+        <v>0.01542554683442086</v>
       </c>
       <c r="G2" t="n">
         <v>0.01582769837690653</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01562336541537822</v>
+        <v>0.01562336541537824</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01562336541537822</v>
+        <v>0.01562336541537824</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01560877972852148</v>
+        <v>0.01560877972852149</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01562336541537822</v>
+        <v>0.01562336541537824</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01562336541537822</v>
+        <v>0.01562336541537824</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01589032535921681</v>
+        <v>0.01589032535921682</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0155909596968663</v>
+        <v>0.01559095969686631</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01562336541537822</v>
+        <v>0.01562336541537824</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01562336541537822</v>
+        <v>0.01562336541537824</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01562336541537822</v>
+        <v>0.01562336541537824</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01562336541537822</v>
+        <v>0.01562336541537824</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01562336541537822</v>
+        <v>0.01562336541537824</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01562336541537822</v>
+        <v>0.01562336541537824</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01562336541537822</v>
+        <v>0.01562336541537824</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01544968574299074</v>
+        <v>0.01544968574299075</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01562336541537822</v>
+        <v>0.01562336541537824</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01562336541537822</v>
+        <v>0.01562336541537824</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01562336541537822</v>
+        <v>0.01562336541537824</v>
       </c>
       <c r="Z2" t="n">
         <v>0.01545535760384437</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01562336541537822</v>
+        <v>0.01562336541537824</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01562336541537822</v>
+        <v>0.01562336541537824</v>
       </c>
     </row>
     <row r="3">
@@ -683,7 +683,7 @@
         <v>0.01546261818597194</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0121602199770556</v>
+        <v>0.01216021997705559</v>
       </c>
       <c r="F3" t="n">
         <v>0.01546261818597194</v>
@@ -698,7 +698,7 @@
         <v>0.01546261818597194</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01544803082890928</v>
+        <v>0.01544803082890929</v>
       </c>
       <c r="K3" t="n">
         <v>0.01546261818597194</v>
@@ -762,28 +762,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1084915218218617</v>
+        <v>0.1084915218218618</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02784938031805054</v>
+        <v>0.02784938031805057</v>
       </c>
       <c r="D4" t="n">
-        <v>0.09620854064767348</v>
+        <v>0.09620854064767337</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04837247964370531</v>
+        <v>0.04837247964370513</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0759376746098845</v>
+        <v>0.07593767460988424</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1796581718581602</v>
+        <v>0.1796581718581599</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1520843876619193</v>
+        <v>0.1520843876619195</v>
       </c>
       <c r="I4" t="n">
-        <v>0.106275449453778</v>
+        <v>0.1062754494537777</v>
       </c>
       <c r="J4" t="n">
         <v>0.1260905497944527</v>
@@ -792,55 +792,55 @@
         <v>0.1652712397235451</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1586475290329506</v>
+        <v>0.1586475290329508</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2178970117813389</v>
+        <v>0.2178970117813386</v>
       </c>
       <c r="N4" t="n">
-        <v>0.149613702743138</v>
+        <v>0.1496137027431378</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1014334055221889</v>
+        <v>0.1014334055221886</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1158295171583194</v>
+        <v>0.1158295171583192</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.07157899349043162</v>
+        <v>0.07157899349043136</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1007238642139695</v>
+        <v>0.1007238642139696</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1049646799137332</v>
+        <v>0.104964679913733</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1350074325833035</v>
+        <v>0.1350074325833034</v>
       </c>
       <c r="U4" t="n">
-        <v>0.149613702743138</v>
+        <v>0.1496137027431376</v>
       </c>
       <c r="V4" t="n">
-        <v>0.05757123438087468</v>
+        <v>0.05757123438087447</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1227682379882083</v>
+        <v>0.1227682379882084</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1039684845351473</v>
+        <v>0.1039684845351472</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1199474602933814</v>
+        <v>0.119947460293381</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.07640539800107474</v>
+        <v>0.07640539800107458</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1245501404299834</v>
+        <v>0.1245501404299833</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.230148729572896</v>
+        <v>0.2301487295728958</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003767919653303837</v>
+        <v>0.003767919653303843</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003767919653303835</v>
+        <v>0.003767919653303842</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003767919653303835</v>
+        <v>0.003767919653303842</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003767919653303835</v>
+        <v>0.003767919653303842</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003767919653303837</v>
+        <v>0.003767919653303843</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003767919653303835</v>
+        <v>0.003767919653303842</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003767919653303835</v>
+        <v>0.003767919653303842</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003767919653303835</v>
+        <v>0.003767919653303842</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00376416479720509</v>
+        <v>0.003764164797205095</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003767919653303835</v>
+        <v>0.003767919653303842</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003767919653303835</v>
+        <v>0.003767919653303842</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003767919653303835</v>
+        <v>0.003767919653303842</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003767919653303837</v>
+        <v>0.003767919653303843</v>
       </c>
       <c r="O5" t="n">
-        <v>0.003767919653303837</v>
+        <v>0.003767919653303843</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003767919653303837</v>
+        <v>0.003767919653303843</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.003767919653303837</v>
+        <v>0.003767919653303843</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003767919653303835</v>
+        <v>0.003767919653303842</v>
       </c>
       <c r="S5" t="n">
-        <v>0.003767919653303835</v>
+        <v>0.003767919653303842</v>
       </c>
       <c r="T5" t="n">
-        <v>0.003767919653303835</v>
+        <v>0.003767919653303842</v>
       </c>
       <c r="U5" t="n">
-        <v>0.00366763855774016</v>
+        <v>0.003667638557740169</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003744429959673013</v>
+        <v>0.003744429959673011</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003767919653303837</v>
+        <v>0.003767919653303843</v>
       </c>
       <c r="X5" t="n">
-        <v>0.003767919653303837</v>
+        <v>0.003767919653303843</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.00366763855774016</v>
+        <v>0.003667638557740169</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.003767919653303835</v>
+        <v>0.003767919653303842</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.003767919653303835</v>
+        <v>0.003767919653303842</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003767919653303837</v>
+        <v>0.003767919653303843</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005019032488064115</v>
+        <v>0.007725002602876899</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007725002602876892</v>
+        <v>0.007725002602876899</v>
       </c>
       <c r="D6" t="n">
-        <v>0.005019032488064115</v>
+        <v>0.005019032488064114</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007725002602876892</v>
+        <v>0.005019032488064114</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005019032488064115</v>
+        <v>0.007725002602876899</v>
       </c>
       <c r="G6" t="n">
-        <v>0.005019032488064115</v>
+        <v>0.007725002602876899</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007725002602876892</v>
+        <v>0.007725002602876899</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007725002602876892</v>
+        <v>0.005019032488064114</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00501527763196533</v>
+        <v>0.007721247746778143</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005019032488064115</v>
+        <v>0.005019032488064114</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007725002602876892</v>
+        <v>0.005019032488064114</v>
       </c>
       <c r="M6" t="n">
-        <v>0.005019032488064115</v>
+        <v>0.005019032488064114</v>
       </c>
       <c r="N6" t="n">
-        <v>0.005036400456118796</v>
+        <v>0.005036400456118787</v>
       </c>
       <c r="O6" t="n">
-        <v>0.007749690608037253</v>
+        <v>0.007749690608037268</v>
       </c>
       <c r="P6" t="n">
-        <v>0.007749697525878001</v>
+        <v>0.007749697525878016</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.005019032488064115</v>
+        <v>0.005019032488064114</v>
       </c>
       <c r="R6" t="n">
-        <v>0.007725002602876892</v>
+        <v>0.005019032488064114</v>
       </c>
       <c r="S6" t="n">
-        <v>0.007725002602876892</v>
+        <v>0.007725002602876899</v>
       </c>
       <c r="T6" t="n">
-        <v>0.005019032488064115</v>
+        <v>0.005019032488064114</v>
       </c>
       <c r="U6" t="n">
-        <v>0.005019032488064115</v>
+        <v>0.005019032488064114</v>
       </c>
       <c r="V6" t="n">
-        <v>0.00770151290924606</v>
+        <v>0.007701512909246061</v>
       </c>
       <c r="W6" t="n">
-        <v>0.005166269274631321</v>
+        <v>0.007749694880289323</v>
       </c>
       <c r="X6" t="n">
-        <v>0.007725002602876892</v>
+        <v>0.007725002602876899</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.005129250489781153</v>
+        <v>0.005129250489781252</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.005019032488064115</v>
+        <v>0.005019032488064114</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.007725002602876892</v>
+        <v>0.005019032488064114</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.005071861955896354</v>
+        <v>0.005071861955896355</v>
       </c>
     </row>
     <row r="7">
@@ -1026,43 +1026,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.006198616089646636</v>
+        <v>0.006198616089646639</v>
       </c>
       <c r="C7" t="n">
-        <v>0.006198616089646636</v>
+        <v>0.006198616089646639</v>
       </c>
       <c r="D7" t="n">
-        <v>0.006198616089646636</v>
+        <v>0.006198616089646639</v>
       </c>
       <c r="E7" t="n">
-        <v>0.006198616089646636</v>
+        <v>0.006198616089646639</v>
       </c>
       <c r="F7" t="n">
-        <v>0.006198616089646636</v>
+        <v>0.006198616089646639</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006198616089646636</v>
+        <v>0.006198616089646639</v>
       </c>
       <c r="H7" t="n">
-        <v>0.006198616089646636</v>
+        <v>0.006198616089646639</v>
       </c>
       <c r="I7" t="n">
-        <v>0.006198616089646636</v>
+        <v>0.006198616089646639</v>
       </c>
       <c r="J7" t="n">
         <v>0.006194861233547884</v>
       </c>
       <c r="K7" t="n">
-        <v>0.006198616089646636</v>
+        <v>0.006198616089646639</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006198616089646636</v>
+        <v>0.006198616089646639</v>
       </c>
       <c r="M7" t="n">
-        <v>0.006198616089646636</v>
+        <v>0.006198616089646639</v>
       </c>
       <c r="N7" t="n">
-        <v>0.006198616089646637</v>
+        <v>0.006198616089646639</v>
       </c>
       <c r="O7" t="n">
         <v>0.006198454029571213</v>
@@ -1071,40 +1071,40 @@
         <v>0.006198454029571213</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.006198616089646636</v>
+        <v>0.006198616089646639</v>
       </c>
       <c r="R7" t="n">
-        <v>0.006198616089646636</v>
+        <v>0.006198616089646639</v>
       </c>
       <c r="S7" t="n">
-        <v>0.006198616089646636</v>
+        <v>0.006198616089646639</v>
       </c>
       <c r="T7" t="n">
-        <v>0.006198616089646636</v>
+        <v>0.006198616089646639</v>
       </c>
       <c r="U7" t="n">
-        <v>0.006196136469040591</v>
+        <v>0.006196136469040596</v>
       </c>
       <c r="V7" t="n">
-        <v>0.006175126396015804</v>
+        <v>0.0061751263960158</v>
       </c>
       <c r="W7" t="n">
-        <v>0.006198616089646636</v>
+        <v>0.006198616089646639</v>
       </c>
       <c r="X7" t="n">
-        <v>0.006198616089646636</v>
+        <v>0.006198616089646639</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.006198616089646636</v>
+        <v>0.006198616089646639</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.006198616089646636</v>
+        <v>0.006198616089646639</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.006198616089646636</v>
+        <v>0.006198616089646639</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.006198616089646636</v>
+        <v>0.006198616089646639</v>
       </c>
     </row>
     <row r="8">
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008804133182261873</v>
+        <v>0.008804133182261887</v>
       </c>
       <c r="C8" t="n">
         <v>0.01276814188475516</v>
@@ -1123,13 +1123,13 @@
         <v>0.01276814188475516</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01276814188475516</v>
+        <v>0.01065742418278395</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009421679409170066</v>
+        <v>0.009421679409170072</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01276814188475516</v>
+        <v>0.01359010491191604</v>
       </c>
       <c r="H8" t="n">
         <v>0.01276814188475516</v>
@@ -1138,7 +1138,7 @@
         <v>0.01276814188475516</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01276438702865638</v>
+        <v>0.0127643870286564</v>
       </c>
       <c r="K8" t="n">
         <v>0.01276814188475516</v>
@@ -1147,19 +1147,19 @@
         <v>0.01276814188475516</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01276814188475516</v>
+        <v>0.01276814188475512</v>
       </c>
       <c r="N8" t="n">
-        <v>0.009695371974744004</v>
+        <v>0.009695371974744011</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01053979582354748</v>
+        <v>0.0105397958235475</v>
       </c>
       <c r="P8" t="n">
-        <v>0.010332807134372</v>
+        <v>0.01033280713437201</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.008025114999717841</v>
+        <v>0.008025114999717847</v>
       </c>
       <c r="R8" t="n">
         <v>0.01276814188475516</v>
@@ -1171,28 +1171,28 @@
         <v>0.01276814188475516</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01032721085858135</v>
+        <v>0.01083156608829595</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01274465219112432</v>
+        <v>0.01165924784609868</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01276892092052834</v>
+        <v>0.01276892092052835</v>
       </c>
       <c r="X8" t="n">
-        <v>0.008388424270485587</v>
+        <v>0.008388424270485594</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01670639298604951</v>
+        <v>0.01670639298604953</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01276814188475516</v>
+        <v>0.008730499686035138</v>
       </c>
       <c r="AA8" t="n">
         <v>0.01276814188475516</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0169088804342542</v>
+        <v>0.01690888043425422</v>
       </c>
     </row>
     <row r="9">
@@ -1211,13 +1211,13 @@
         <v>0.01731196954847123</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01731196954847123</v>
+        <v>0.01657464227404891</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01731196954847123</v>
+        <v>0.009947271682601915</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01731196954847123</v>
+        <v>0.0173119703313857</v>
       </c>
       <c r="H9" t="n">
         <v>0.01731196954847123</v>
@@ -1247,7 +1247,7 @@
         <v>0.01860095059914529</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01731197033138571</v>
+        <v>0.0173119703313857</v>
       </c>
       <c r="R9" t="n">
         <v>0.01731196954847123</v>
@@ -1262,7 +1262,7 @@
         <v>0.01731196954847123</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01728847985484041</v>
+        <v>0.02097511377542059</v>
       </c>
       <c r="W9" t="n">
         <v>0.01731196954847123</v>
@@ -1274,7 +1274,7 @@
         <v>0.01731196954847123</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01731196954847123</v>
+        <v>0.01538583900837169</v>
       </c>
       <c r="AA9" t="n">
         <v>0.01731196954847123</v>
@@ -1290,16 +1290,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01315639583636698</v>
+        <v>0.01315639583636697</v>
       </c>
       <c r="C10" t="n">
         <v>0.01499889287904482</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01368854095856797</v>
+        <v>0.01368854095856798</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01125101120908555</v>
+        <v>0.01125101120908553</v>
       </c>
       <c r="F10" t="n">
         <v>0.01411468919464335</v>
@@ -1311,7 +1311,7 @@
         <v>0.01273936970464588</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01351968784906489</v>
+        <v>0.0135196878490649</v>
       </c>
       <c r="J10" t="n">
         <v>0.01290856593853793</v>
@@ -1323,7 +1323,7 @@
         <v>0.01229653902079863</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01140109361340129</v>
+        <v>0.0114010936134013</v>
       </c>
       <c r="N10" t="n">
         <v>0.01312931679940364</v>
@@ -1332,10 +1332,10 @@
         <v>0.01325961133131966</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01303515548486109</v>
+        <v>0.01303515548486107</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01413221798752872</v>
+        <v>0.01413221798752873</v>
       </c>
       <c r="R10" t="n">
         <v>0.01365139586336617</v>
@@ -1344,22 +1344,22 @@
         <v>0.01330714576122505</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01295255249821778</v>
+        <v>0.01295255249821779</v>
       </c>
       <c r="U10" t="n">
         <v>0.01241965408605107</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01435693465297364</v>
+        <v>0.01435693465297365</v>
       </c>
       <c r="W10" t="n">
         <v>0.01305332690118343</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01351139263633737</v>
+        <v>0.01351139263633738</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.01311328144929933</v>
+        <v>0.01311328144929934</v>
       </c>
       <c r="Z10" t="n">
         <v>0.01391121233176689</v>
@@ -1378,79 +1378,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01457402689681341</v>
+        <v>0.01457402689681342</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01506237616852276</v>
+        <v>0.01506237616852277</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01468995778326713</v>
+        <v>0.01468995778326714</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01168292220639044</v>
+        <v>0.01168292220639042</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01481223484777152</v>
+        <v>0.01481223484777153</v>
       </c>
       <c r="G11" t="n">
         <v>0.01411408693844765</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01438427867789688</v>
+        <v>0.01438427867789689</v>
       </c>
       <c r="I11" t="n">
         <v>0.01473932592033391</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01445331511060809</v>
+        <v>0.0144533151106081</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01419847678424978</v>
+        <v>0.0141984767842498</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01418278930552873</v>
+        <v>0.01418278930552874</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01404231873538633</v>
+        <v>0.01404231873538636</v>
       </c>
       <c r="N11" t="n">
         <v>0.01452930013018741</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01462099027594516</v>
+        <v>0.01462099027594517</v>
       </c>
       <c r="P11" t="n">
         <v>0.01451886215050816</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01501802908535269</v>
+        <v>0.01501802908535271</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01479925348656953</v>
+        <v>0.01479925348656955</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01464261859303534</v>
+        <v>0.01464261859303535</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01448127752834536</v>
+        <v>0.01448127752834537</v>
       </c>
       <c r="U11" t="n">
         <v>0.01423880705256304</v>
       </c>
       <c r="V11" t="n">
-        <v>0.01491897884900129</v>
+        <v>0.0149189788490013</v>
       </c>
       <c r="W11" t="n">
-        <v>0.01452713020284369</v>
+        <v>0.0145271302028437</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01473555157210761</v>
+        <v>0.01473555157210762</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01455440971330024</v>
+        <v>0.01455440971330025</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.01474946299614397</v>
+        <v>0.01474946299614398</v>
       </c>
       <c r="AA11" t="n">
         <v>0.01451891812327081</v>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01447773757473199</v>
+        <v>0.01447773757473198</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01451452118616317</v>
+        <v>0.01451452118616318</v>
       </c>
       <c r="D2" t="n">
         <v>0.01450397141252809</v>
@@ -1634,7 +1634,7 @@
         <v>0.01162762677391938</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01451841910728115</v>
+        <v>0.01451841910728114</v>
       </c>
       <c r="G2" t="n">
         <v>0.01436593907361446</v>
@@ -1643,19 +1643,19 @@
         <v>0.01455691449093804</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01450486990848027</v>
+        <v>0.01450486990848026</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01453239719858126</v>
+        <v>0.01453239719858125</v>
       </c>
       <c r="K2" t="n">
         <v>0.01453679310881773</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01453662259165497</v>
+        <v>0.01453662259165496</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01450160522356412</v>
+        <v>0.01450160522356411</v>
       </c>
       <c r="N2" t="n">
         <v>0.01452615750541624</v>
@@ -1664,7 +1664,7 @@
         <v>0.0145419932966868</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01452725704077616</v>
+        <v>0.01452725704077615</v>
       </c>
       <c r="Q2" t="n">
         <v>0.01449820915691442</v>
@@ -1673,25 +1673,25 @@
         <v>0.0145012848955379</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01453378615018862</v>
+        <v>0.01453378615018863</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01450928915999158</v>
+        <v>0.01450928915999157</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01453723932158088</v>
+        <v>0.0145372393215809</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01441605969279782</v>
+        <v>0.01441605969279781</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01470590771466462</v>
+        <v>0.01470590771466461</v>
       </c>
       <c r="X2" t="n">
         <v>0.01474846288372657</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01466422912445867</v>
+        <v>0.01466422912445866</v>
       </c>
       <c r="Z2" t="n">
         <v>0.01453790458275351</v>
@@ -1700,7 +1700,7 @@
         <v>0.01467160194630903</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01433654502044625</v>
+        <v>0.01433654502044624</v>
       </c>
     </row>
     <row r="3">
@@ -1719,13 +1719,13 @@
         <v>0.01471950595982508</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01181619068208555</v>
+        <v>0.01181619068208554</v>
       </c>
       <c r="F3" t="n">
         <v>0.01473393785043017</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01455075488185505</v>
+        <v>0.01455075488185506</v>
       </c>
       <c r="H3" t="n">
         <v>0.01471950595982508</v>
@@ -1770,7 +1770,7 @@
         <v>0.01471936740624618</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01459198142359801</v>
+        <v>0.01459198142359802</v>
       </c>
       <c r="W3" t="n">
         <v>0.01471950595982508</v>
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007218135813833048</v>
+        <v>0.007218135813833059</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01171665298418707</v>
+        <v>0.01171665298418709</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01425483853330919</v>
+        <v>0.01425483853330922</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009355558543102825</v>
+        <v>0.009355558543102859</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01476629484308917</v>
+        <v>0.01476629484308916</v>
       </c>
       <c r="G4" t="n">
-        <v>0.016732513742069</v>
+        <v>0.01673251374206889</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02926094213953244</v>
+        <v>0.02926094213953243</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01481920632289907</v>
+        <v>0.01481920632289906</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02072193748589353</v>
+        <v>0.02072193748589354</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01960440407822131</v>
+        <v>0.01960440407822132</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02085915024926109</v>
+        <v>0.02085915024926107</v>
       </c>
       <c r="M4" t="n">
         <v>0.01392831963674939</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02011726147141741</v>
+        <v>0.02011726147141742</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02154943680590863</v>
+        <v>0.02154943680590862</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01846419361345289</v>
+        <v>0.01846419361345288</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01241758352683755</v>
+        <v>0.01241758352683756</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02463228635659779</v>
+        <v>0.02463228635659778</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01986993881835606</v>
+        <v>0.01986993881835605</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01605367893336849</v>
+        <v>0.01605367893336852</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02072175350929729</v>
+        <v>0.02072175350929726</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02171403788173755</v>
+        <v>0.02171403788173758</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06487815662679654</v>
+        <v>0.06487815662679647</v>
       </c>
       <c r="X4" t="n">
-        <v>0.08732843124711777</v>
+        <v>0.08732843124711759</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.05544142114484612</v>
+        <v>0.05544142114484613</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01978216693009642</v>
+        <v>0.01978216693009644</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.05699395159881795</v>
+        <v>0.05699395159881804</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.01024264580203734</v>
+        <v>0.01024264580203738</v>
       </c>
     </row>
     <row r="5">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002345786567352135</v>
+        <v>0.002345786567352139</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002345786567352136</v>
+        <v>0.002345786567352148</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002345786567352136</v>
+        <v>0.002345786567352148</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002345786567352136</v>
+        <v>0.002345786567352148</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002345786567352135</v>
+        <v>0.002345786567352139</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002345786567352136</v>
+        <v>0.002345786567352148</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002345786567352136</v>
+        <v>0.002345786567352148</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002345786567352136</v>
+        <v>0.002345786567352148</v>
       </c>
       <c r="J5" t="n">
         <v>0.002344155628217559</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002345786567352136</v>
+        <v>0.002345786567352148</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002345786567352136</v>
+        <v>0.002345786567352148</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002345786567352136</v>
+        <v>0.002345786567352148</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02011726147141741</v>
+        <v>0.02011726147141742</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002345786567352135</v>
+        <v>0.002345786567352139</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002345786567352135</v>
+        <v>0.002345786567352139</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002345786567352135</v>
+        <v>0.002345786567352139</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002345786567352136</v>
+        <v>0.002345786567352148</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002345786567352136</v>
+        <v>0.002345786567352148</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002345786567352136</v>
+        <v>0.002345786567352148</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002290610401039206</v>
+        <v>0.002290610401039198</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002335548151811191</v>
+        <v>0.002335548151811192</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002345786567352138</v>
+        <v>0.002345786567352149</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002345786567352135</v>
+        <v>0.002345786567352139</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.002290610401039206</v>
+        <v>0.002290610401039199</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002345786567352136</v>
+        <v>0.002345786567352148</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002345786567352136</v>
+        <v>0.002345786567352148</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.002345786567352135</v>
+        <v>0.002345786567352139</v>
       </c>
     </row>
     <row r="6">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005007345840524392</v>
+        <v>0.003364618065839401</v>
       </c>
       <c r="C6" t="n">
-        <v>0.005007345840524392</v>
+        <v>0.003364618065839401</v>
       </c>
       <c r="D6" t="n">
-        <v>0.005007345840524392</v>
+        <v>0.005007345840524424</v>
       </c>
       <c r="E6" t="n">
-        <v>0.005007345840524392</v>
+        <v>0.003364618065839401</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005007345840524392</v>
+        <v>0.003364618065839401</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003364618065839381</v>
+        <v>0.005007345840524424</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003364618065839381</v>
+        <v>0.005007345840524424</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003364618065839381</v>
+        <v>0.005007345840524424</v>
       </c>
       <c r="J6" t="n">
-        <v>0.003362987126704796</v>
+        <v>0.005005714901389818</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005007345840524392</v>
+        <v>0.003364618065839401</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003364618065839381</v>
+        <v>0.005007345840524424</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003364618065839381</v>
+        <v>0.005007345840524424</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02011726147141741</v>
+        <v>0.02011726147141742</v>
       </c>
       <c r="O6" t="n">
-        <v>0.005101316436641715</v>
+        <v>0.005101316436641731</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003302413533652302</v>
+        <v>0.005053504890492641</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.005007345840524392</v>
+        <v>0.005007345840524424</v>
       </c>
       <c r="R6" t="n">
-        <v>0.003364618065839381</v>
+        <v>0.005007345840524424</v>
       </c>
       <c r="S6" t="n">
-        <v>0.003364618065839381</v>
+        <v>0.005007345840524424</v>
       </c>
       <c r="T6" t="n">
-        <v>0.005007345840524392</v>
+        <v>0.003364618065839401</v>
       </c>
       <c r="U6" t="n">
-        <v>0.003364618065839381</v>
+        <v>0.005007345840524424</v>
       </c>
       <c r="V6" t="n">
-        <v>0.003354379650298442</v>
+        <v>0.004997107424983454</v>
       </c>
       <c r="W6" t="n">
-        <v>0.003487092568551804</v>
+        <v>0.003487092568551812</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003364618065839381</v>
+        <v>0.003364618065839401</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.003488431505572739</v>
+        <v>0.003488431505572757</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.005007345840524392</v>
+        <v>0.003364618065839401</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003364618065839381</v>
+        <v>0.003364618065839401</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003364661779463122</v>
+        <v>0.003364661779463148</v>
       </c>
     </row>
     <row r="7">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.003865500464490127</v>
+        <v>0.003865500464490134</v>
       </c>
       <c r="C7" t="n">
-        <v>0.003865500464490127</v>
+        <v>0.003865500464490134</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003865500464490127</v>
+        <v>0.003865500464490134</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003865500464490127</v>
+        <v>0.003865500464490134</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003865500464490127</v>
+        <v>0.003865500464490134</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003865500464490127</v>
+        <v>0.003865500464490134</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003865500464490127</v>
+        <v>0.003865500464490134</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003865500464490127</v>
+        <v>0.003865500464490134</v>
       </c>
       <c r="J7" t="n">
         <v>0.003863869525355548</v>
       </c>
       <c r="K7" t="n">
-        <v>0.003865500464490127</v>
+        <v>0.003865500464490134</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003865500464490127</v>
+        <v>0.003865500464490134</v>
       </c>
       <c r="M7" t="n">
-        <v>0.003865500464490127</v>
+        <v>0.003865500464490134</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02011726147141741</v>
+        <v>0.02011726147141742</v>
       </c>
       <c r="O7" t="n">
-        <v>0.003865367017001001</v>
+        <v>0.003865367017001007</v>
       </c>
       <c r="P7" t="n">
-        <v>0.003865367017001001</v>
+        <v>0.003865367017001007</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.003865500464490127</v>
+        <v>0.003865500464490134</v>
       </c>
       <c r="R7" t="n">
-        <v>0.003865500464490127</v>
+        <v>0.003865500464490134</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003865500464490127</v>
+        <v>0.003865500464490134</v>
       </c>
       <c r="T7" t="n">
-        <v>0.003865500464490127</v>
+        <v>0.003865500464490134</v>
       </c>
       <c r="U7" t="n">
-        <v>0.003862937095435137</v>
+        <v>0.003862937095435146</v>
       </c>
       <c r="V7" t="n">
-        <v>0.00385526204894918</v>
+        <v>0.003855262048949181</v>
       </c>
       <c r="W7" t="n">
-        <v>0.003865500464490127</v>
+        <v>0.003865500464490134</v>
       </c>
       <c r="X7" t="n">
-        <v>0.003865500464490127</v>
+        <v>0.003865500464490134</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.003865500464490127</v>
+        <v>0.003865500464490134</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.003865500464490127</v>
+        <v>0.003865500464490134</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.003865500464490127</v>
+        <v>0.003865500464490134</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.003865500464490127</v>
+        <v>0.003865500464490134</v>
       </c>
     </row>
     <row r="8">
@@ -2150,85 +2150,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.005647329110624867</v>
+        <v>0.005647329110624882</v>
       </c>
       <c r="C8" t="n">
-        <v>0.008260978984831415</v>
+        <v>0.008260978984831462</v>
       </c>
       <c r="D8" t="n">
-        <v>0.008260978984831415</v>
+        <v>0.008260978984831462</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008260978984831415</v>
+        <v>0.006869287525654968</v>
       </c>
       <c r="F8" t="n">
-        <v>0.006054505214154914</v>
+        <v>0.006054505214154933</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008260978984831415</v>
+        <v>0.008802936312238064</v>
       </c>
       <c r="H8" t="n">
-        <v>0.008260978984831415</v>
+        <v>0.008260978984831462</v>
       </c>
       <c r="I8" t="n">
-        <v>0.008260978984831415</v>
+        <v>0.008260978984831462</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008259348045696852</v>
+        <v>0.00825934804569689</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008260978984831415</v>
+        <v>0.008260978984831462</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008260978984831415</v>
+        <v>0.008260978984831462</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008260978984831415</v>
+        <v>0.008260978984831165</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02011726147141741</v>
+        <v>0.02011726147141742</v>
       </c>
       <c r="O8" t="n">
-        <v>0.006791729837670417</v>
+        <v>0.006791729837670432</v>
       </c>
       <c r="P8" t="n">
-        <v>0.006655252851534694</v>
+        <v>0.006655252851534704</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.005133687258040395</v>
+        <v>0.005133687258040416</v>
       </c>
       <c r="R8" t="n">
-        <v>0.008260978984831415</v>
+        <v>0.008260978984831462</v>
       </c>
       <c r="S8" t="n">
-        <v>0.008260978984831415</v>
+        <v>0.008260978984831462</v>
       </c>
       <c r="T8" t="n">
-        <v>0.008260978984831415</v>
+        <v>0.008260978984831462</v>
       </c>
       <c r="U8" t="n">
-        <v>0.006650906707242382</v>
+        <v>0.006983408232874412</v>
       </c>
       <c r="V8" t="n">
-        <v>0.008250740569290486</v>
+        <v>0.007534313610041587</v>
       </c>
       <c r="W8" t="n">
-        <v>0.008261492637236491</v>
+        <v>0.008261492637236502</v>
       </c>
       <c r="X8" t="n">
-        <v>0.005373233459507998</v>
+        <v>0.005373233459508019</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01085645007606803</v>
+        <v>0.01085645007606806</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.008260978984831415</v>
+        <v>0.005598779222829359</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.008260978984831415</v>
+        <v>0.008260978984831462</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0109911548238071</v>
+        <v>0.01099115482380712</v>
       </c>
     </row>
     <row r="9">
@@ -2238,85 +2238,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.006559274112582039</v>
+        <v>0.006559274112582037</v>
       </c>
       <c r="C9" t="n">
-        <v>0.007949076580408309</v>
+        <v>0.007949076580408316</v>
       </c>
       <c r="D9" t="n">
-        <v>0.007949076580408309</v>
+        <v>0.007949076580408316</v>
       </c>
       <c r="E9" t="n">
-        <v>0.007949076580408309</v>
+        <v>0.007628316575767558</v>
       </c>
       <c r="F9" t="n">
-        <v>0.007949076580408309</v>
+        <v>0.004745201330004026</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007949076580408309</v>
+        <v>0.007949077537283808</v>
       </c>
       <c r="H9" t="n">
-        <v>0.007949076580408309</v>
+        <v>0.007949076580408316</v>
       </c>
       <c r="I9" t="n">
-        <v>0.007949076580408309</v>
+        <v>0.007949076580408316</v>
       </c>
       <c r="J9" t="n">
-        <v>0.007947445641273735</v>
+        <v>0.007947445641273719</v>
       </c>
       <c r="K9" t="n">
-        <v>0.007949076580408309</v>
+        <v>0.007949076580408316</v>
       </c>
       <c r="L9" t="n">
-        <v>0.007949076580408309</v>
+        <v>0.007949076580408316</v>
       </c>
       <c r="M9" t="n">
-        <v>0.007949076580408309</v>
+        <v>0.007949076580408316</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02011726147141741</v>
+        <v>0.02011726147141742</v>
       </c>
       <c r="O9" t="n">
-        <v>0.008409656572437703</v>
+        <v>0.008409656572437724</v>
       </c>
       <c r="P9" t="n">
-        <v>0.008509824610378205</v>
+        <v>0.008509824610378231</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.007949077537283798</v>
+        <v>0.007949077537283808</v>
       </c>
       <c r="R9" t="n">
-        <v>0.007949076580408309</v>
+        <v>0.007949076580408316</v>
       </c>
       <c r="S9" t="n">
-        <v>0.007949076580408309</v>
+        <v>0.007949076580408316</v>
       </c>
       <c r="T9" t="n">
-        <v>0.007949076580408309</v>
+        <v>0.007949076580408316</v>
       </c>
       <c r="U9" t="n">
-        <v>0.007949076580408309</v>
+        <v>0.007949076580408316</v>
       </c>
       <c r="V9" t="n">
-        <v>0.00793883816486737</v>
+        <v>0.009542641298571929</v>
       </c>
       <c r="W9" t="n">
-        <v>0.007949076580408309</v>
+        <v>0.007949076580408316</v>
       </c>
       <c r="X9" t="n">
-        <v>0.007949076580408309</v>
+        <v>0.007949076580408316</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.007949076580408309</v>
+        <v>0.007949076580408316</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.007949076580408309</v>
+        <v>0.007111149658331154</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.007949076580408309</v>
+        <v>0.007949076580408316</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.007949076580408309</v>
+        <v>0.007949076580408316</v>
       </c>
     </row>
     <row r="10">
@@ -2326,55 +2326,55 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01460601636100911</v>
+        <v>0.01460601636100912</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01453387456803568</v>
+        <v>0.01453387456803567</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01445413009121175</v>
+        <v>0.01445413009121176</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0116536087676088</v>
+        <v>0.01165360876760879</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01446252577129354</v>
+        <v>0.01446252577129355</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01418516251883343</v>
+        <v>0.01418516251883345</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01414790953523573</v>
+        <v>0.01414790953523574</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01444937750663698</v>
+        <v>0.01444937750663699</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01427546605363097</v>
+        <v>0.01427546605363096</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01430909543705548</v>
+        <v>0.0143090954370555</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01425862244596123</v>
+        <v>0.01425862244596124</v>
       </c>
       <c r="M10" t="n">
         <v>0.01446761776577984</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01432249340670973</v>
+        <v>0.01432249340670974</v>
       </c>
       <c r="O10" t="n">
         <v>0.0142225161374957</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01430684093387206</v>
+        <v>0.01430684093387207</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01448727760691773</v>
+        <v>0.01448727760691775</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0141987270836239</v>
+        <v>0.01419872708362391</v>
       </c>
       <c r="S10" t="n">
         <v>0.01427395976817931</v>
@@ -2383,25 +2383,25 @@
         <v>0.0144221920009415</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01425362289590767</v>
+        <v>0.01425362289590766</v>
       </c>
       <c r="V10" t="n">
         <v>0.01409780300470161</v>
       </c>
       <c r="W10" t="n">
-        <v>0.01326027810386648</v>
+        <v>0.01326027810386649</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01262889323379488</v>
+        <v>0.01262889323379487</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.01350563592771837</v>
+        <v>0.01350563592771838</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01425871302402034</v>
+        <v>0.01425871302402036</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.01346377320294515</v>
+        <v>0.01346377320294516</v>
       </c>
       <c r="AB10" t="n">
         <v>0.01439620958228374</v>
@@ -2426,31 +2426,31 @@
         <v>0.01155365148471463</v>
       </c>
       <c r="F11" t="n">
-        <v>0.014394925746335</v>
+        <v>0.01439492574633499</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01419959338336589</v>
+        <v>0.01419959338336588</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01429683629618016</v>
+        <v>0.01429683629618015</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01438196060143136</v>
+        <v>0.01438196060143135</v>
       </c>
       <c r="J11" t="n">
         <v>0.01433091419249279</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01434663045415513</v>
+        <v>0.01434663045415512</v>
       </c>
       <c r="L11" t="n">
         <v>0.0143269191240983</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01438709117761782</v>
+        <v>0.01438709117761781</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01434551552854481</v>
+        <v>0.01434551552854482</v>
       </c>
       <c r="O11" t="n">
         <v>0.014315910051709</v>
@@ -2459,7 +2459,7 @@
         <v>0.01433975879523714</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01439254505731615</v>
+        <v>0.01439254505731616</v>
       </c>
       <c r="R11" t="n">
         <v>0.01428388459422299</v>
@@ -2474,19 +2474,19 @@
         <v>0.01432532408513717</v>
       </c>
       <c r="V11" t="n">
-        <v>0.01419120693734679</v>
+        <v>0.01419120693734678</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0140419543899202</v>
+        <v>0.01404195438992019</v>
       </c>
       <c r="X11" t="n">
         <v>0.01382524402455527</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01411209901196855</v>
+        <v>0.01411209901196857</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.0143275265419195</v>
+        <v>0.01432752654191951</v>
       </c>
       <c r="AA11" t="n">
         <v>0.0141002395401458</v>
@@ -2661,16 +2661,16 @@
         <v>0.01537540416687931</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01511339687549585</v>
+        <v>0.01511339687549584</v>
       </c>
       <c r="D2" t="n">
         <v>0.01530280409209221</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01198817382509695</v>
+        <v>0.01198817382509698</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01519007058727384</v>
+        <v>0.01519007058727383</v>
       </c>
       <c r="G2" t="n">
         <v>0.01543167699063563</v>
@@ -2682,7 +2682,7 @@
         <v>0.01537540416687931</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01536260371496529</v>
+        <v>0.01536260371496528</v>
       </c>
       <c r="K2" t="n">
         <v>0.01537918662762964</v>
@@ -2691,16 +2691,16 @@
         <v>0.01537540416687931</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01547235217189752</v>
+        <v>0.01547235217189753</v>
       </c>
       <c r="N2" t="n">
         <v>0.01530333167219614</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01537532759067712</v>
+        <v>0.01537532759067711</v>
       </c>
       <c r="P2" t="n">
-        <v>0.015375382593168</v>
+        <v>0.01537538259316799</v>
       </c>
       <c r="Q2" t="n">
         <v>0.01537540308026128</v>
@@ -2718,13 +2718,13 @@
         <v>0.01537552502541433</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01513312602948559</v>
+        <v>0.0151331260294856</v>
       </c>
       <c r="W2" t="n">
         <v>0.01537540416687931</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01536512162122662</v>
+        <v>0.01536512162122661</v>
       </c>
       <c r="Y2" t="n">
         <v>0.01537522834096425</v>
@@ -2746,82 +2746,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01528501413478297</v>
+        <v>0.01528501413478296</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01530634890972558</v>
+        <v>0.01530634890972557</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01528501413478297</v>
+        <v>0.01528501413478296</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0120851035488038</v>
+        <v>0.01208510354880382</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01529271898140564</v>
+        <v>0.01529271898140563</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0152021803905381</v>
+        <v>0.01520218039053809</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01528501413478297</v>
+        <v>0.01528501413478296</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01528501413478297</v>
+        <v>0.01528501413478296</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01527221221840934</v>
+        <v>0.01527221221840933</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01528915324563048</v>
+        <v>0.01528915324563047</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01528501413478297</v>
+        <v>0.01528501413478296</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01528498407625273</v>
+        <v>0.01528498407625272</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01528501413478297</v>
+        <v>0.01528501413478296</v>
       </c>
       <c r="O3" t="n">
         <v>0.01528493033732736</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01528499052676945</v>
+        <v>0.01528499052676944</v>
       </c>
       <c r="Q3" t="n">
         <v>0.01528501294568708</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01528578992155798</v>
+        <v>0.01528578992155797</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01528501413478297</v>
+        <v>0.01528501413478296</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01528497768455923</v>
+        <v>0.01528497768455922</v>
       </c>
       <c r="U3" t="n">
         <v>0.0152851463904946</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01527265483242196</v>
+        <v>0.01527265483242197</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01528501413478297</v>
+        <v>0.01528501413478296</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01527376191961181</v>
+        <v>0.0152737619196118</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01528482172828865</v>
+        <v>0.01528482172828864</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01528596498318645</v>
+        <v>0.01528596498318644</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01528501413478297</v>
+        <v>0.01528501413478296</v>
       </c>
       <c r="AB3" t="n">
         <v>0.01512151641621286</v>
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08247307981781139</v>
+        <v>0.082473079817811</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02453517352248198</v>
+        <v>0.02453517352248196</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08456677883198666</v>
+        <v>0.0845667788319865</v>
       </c>
       <c r="E4" t="n">
         <v>0.03595852920955495</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0505090687693623</v>
+        <v>0.05050906876936237</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1292210064010111</v>
+        <v>0.129221006401011</v>
       </c>
       <c r="H4" t="n">
-        <v>0.10523611474773</v>
+        <v>0.1052361147477302</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06134214491812057</v>
+        <v>0.06134214491812061</v>
       </c>
       <c r="J4" t="n">
-        <v>0.09803954007181671</v>
+        <v>0.09803954007181669</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1198217487533734</v>
+        <v>0.1198217487533735</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1338066623030356</v>
+        <v>0.1338066623030358</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1334512335342503</v>
+        <v>0.1334512335342505</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1241661458600952</v>
+        <v>0.124166145860095</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07745117246908834</v>
+        <v>0.07745117246908835</v>
       </c>
       <c r="P4" t="n">
         <v>0.1276745270153682</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.05358118659066973</v>
+        <v>0.05358118659066977</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05310765332454907</v>
+        <v>0.05310765332454911</v>
       </c>
       <c r="S4" t="n">
-        <v>0.09385129619918646</v>
+        <v>0.09385129619918678</v>
       </c>
       <c r="T4" t="n">
-        <v>0.08999755047029807</v>
+        <v>0.08999755047029792</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1241661458600952</v>
+        <v>0.124166145860095</v>
       </c>
       <c r="V4" t="n">
-        <v>0.03528431035240084</v>
+        <v>0.03528431035240082</v>
       </c>
       <c r="W4" t="n">
         <v>0.1302356437712186</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1051326502976201</v>
+        <v>0.1051326502976202</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.09962858288815048</v>
+        <v>0.09962858288815052</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.05644978540382884</v>
+        <v>0.05644978540382876</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.09582947744878888</v>
+        <v>0.09582947744878904</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1872989008500971</v>
+        <v>0.1872989008500968</v>
       </c>
     </row>
     <row r="5">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003378213979691723</v>
+        <v>0.003378213979691714</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003378213979691721</v>
+        <v>0.003378213979691716</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003378213979691721</v>
+        <v>0.003378213979691716</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003378213979691721</v>
+        <v>0.003378213979691716</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003378213979691723</v>
+        <v>0.003378213979691714</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003378213979691721</v>
+        <v>0.003378213979691716</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003378213979691721</v>
+        <v>0.003378213979691716</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003378213979691721</v>
+        <v>0.003378213979691716</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003373997771197242</v>
+        <v>0.003373997771197236</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003378213979691721</v>
+        <v>0.003378213979691716</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003378213979691721</v>
+        <v>0.003378213979691716</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003378213979691721</v>
+        <v>0.003378213979691716</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003378213979691723</v>
+        <v>0.003378213979691714</v>
       </c>
       <c r="O5" t="n">
-        <v>0.003378213979691723</v>
+        <v>0.003378213979691714</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003378213979691723</v>
+        <v>0.003378213979691714</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.003378213979691723</v>
+        <v>0.003378213979691714</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003378213979691721</v>
+        <v>0.003378213979691716</v>
       </c>
       <c r="S5" t="n">
-        <v>0.003378213979691721</v>
+        <v>0.003378213979691716</v>
       </c>
       <c r="T5" t="n">
-        <v>0.003378213979691721</v>
+        <v>0.003378213979691716</v>
       </c>
       <c r="U5" t="n">
-        <v>0.003303793259755992</v>
+        <v>0.003303793259755981</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003351474795154334</v>
+        <v>0.003351474795154318</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003378213979691723</v>
+        <v>0.003378213979691714</v>
       </c>
       <c r="X5" t="n">
-        <v>0.003378213979691723</v>
+        <v>0.003378213979691714</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003303793259755992</v>
+        <v>0.003303793259755981</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.003378213979691721</v>
+        <v>0.003378213979691716</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.003378213979691721</v>
+        <v>0.003378213979691716</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003378213979691723</v>
+        <v>0.003378213979691714</v>
       </c>
     </row>
     <row r="6">
@@ -3010,85 +3010,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.006917317765424842</v>
+        <v>0.004590152143026106</v>
       </c>
       <c r="C6" t="n">
-        <v>0.006917317765424842</v>
+        <v>0.006917317765424843</v>
       </c>
       <c r="D6" t="n">
-        <v>0.004590152143026113</v>
+        <v>0.006917317765424843</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004590152143026113</v>
+        <v>0.004590152143026106</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006917317765424842</v>
+        <v>0.004590152143026106</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006917317765424842</v>
+        <v>0.004590152143026106</v>
       </c>
       <c r="H6" t="n">
-        <v>0.004590152143026113</v>
+        <v>0.006917317765424843</v>
       </c>
       <c r="I6" t="n">
-        <v>0.004590152143026113</v>
+        <v>0.004590152143026106</v>
       </c>
       <c r="J6" t="n">
-        <v>0.006913101556930363</v>
+        <v>0.006913101556930352</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004590152143026113</v>
+        <v>0.006917317765424843</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004590152143026113</v>
+        <v>0.004590152143026106</v>
       </c>
       <c r="M6" t="n">
-        <v>0.004590152143026113</v>
+        <v>0.004590152143026106</v>
       </c>
       <c r="N6" t="n">
-        <v>0.004602807894647315</v>
+        <v>0.004602807894647347</v>
       </c>
       <c r="O6" t="n">
-        <v>0.006932826209672061</v>
+        <v>0.006932826209672076</v>
       </c>
       <c r="P6" t="n">
-        <v>0.006932828635616497</v>
+        <v>0.006932828635616517</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.004590152143026113</v>
+        <v>0.006917317765424843</v>
       </c>
       <c r="R6" t="n">
-        <v>0.004590152143026113</v>
+        <v>0.006917317765424843</v>
       </c>
       <c r="S6" t="n">
-        <v>0.004590152143026113</v>
+        <v>0.006917317765424843</v>
       </c>
       <c r="T6" t="n">
-        <v>0.006917317765424842</v>
+        <v>0.004590152143026106</v>
       </c>
       <c r="U6" t="n">
-        <v>0.006917317765424842</v>
+        <v>0.004590152143026106</v>
       </c>
       <c r="V6" t="n">
-        <v>0.006890578580887459</v>
+        <v>0.006890578580887443</v>
       </c>
       <c r="W6" t="n">
-        <v>0.006932805653735111</v>
+        <v>0.006932805653735122</v>
       </c>
       <c r="X6" t="n">
-        <v>0.004590152143026113</v>
+        <v>0.006917317765424843</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.004690552267850019</v>
+        <v>0.004690552267850025</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.004590152143026113</v>
+        <v>0.006917317765424843</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.006917317765424842</v>
+        <v>0.004590152143026106</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.004634224165155912</v>
+        <v>0.004634224165155918</v>
       </c>
     </row>
     <row r="7">
@@ -3098,85 +3098,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.005455121004612189</v>
+        <v>0.005455121004612183</v>
       </c>
       <c r="C7" t="n">
-        <v>0.005455121004612189</v>
+        <v>0.005455121004612183</v>
       </c>
       <c r="D7" t="n">
-        <v>0.005455121004612189</v>
+        <v>0.005455121004612183</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005455121004612189</v>
+        <v>0.005455121004612183</v>
       </c>
       <c r="F7" t="n">
-        <v>0.005455121004612189</v>
+        <v>0.005455121004612183</v>
       </c>
       <c r="G7" t="n">
-        <v>0.005455121004612189</v>
+        <v>0.005455121004612183</v>
       </c>
       <c r="H7" t="n">
-        <v>0.005455121004612189</v>
+        <v>0.005455121004612183</v>
       </c>
       <c r="I7" t="n">
-        <v>0.005455121004612189</v>
+        <v>0.005455121004612183</v>
       </c>
       <c r="J7" t="n">
-        <v>0.005450904796117707</v>
+        <v>0.005450904796117709</v>
       </c>
       <c r="K7" t="n">
-        <v>0.005455121004612189</v>
+        <v>0.005455121004612183</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005455121004612189</v>
+        <v>0.005455121004612183</v>
       </c>
       <c r="M7" t="n">
-        <v>0.005455121004612189</v>
+        <v>0.005455121004612183</v>
       </c>
       <c r="N7" t="n">
-        <v>0.005455121004612189</v>
+        <v>0.005455121004612184</v>
       </c>
       <c r="O7" t="n">
-        <v>0.005454971345352702</v>
+        <v>0.005454971345352694</v>
       </c>
       <c r="P7" t="n">
-        <v>0.005454971345352702</v>
+        <v>0.005454971345352694</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.005455121004612189</v>
+        <v>0.005455121004612183</v>
       </c>
       <c r="R7" t="n">
-        <v>0.005455121004612189</v>
+        <v>0.005455121004612183</v>
       </c>
       <c r="S7" t="n">
-        <v>0.005455121004612189</v>
+        <v>0.005455121004612183</v>
       </c>
       <c r="T7" t="n">
-        <v>0.005455121004612189</v>
+        <v>0.005455121004612183</v>
       </c>
       <c r="U7" t="n">
-        <v>0.005452522481600927</v>
+        <v>0.005452522481600931</v>
       </c>
       <c r="V7" t="n">
-        <v>0.005428381820074794</v>
+        <v>0.005428381820074784</v>
       </c>
       <c r="W7" t="n">
-        <v>0.005455121004612189</v>
+        <v>0.005455121004612183</v>
       </c>
       <c r="X7" t="n">
-        <v>0.005455121004612189</v>
+        <v>0.005455121004612183</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.005455121004612189</v>
+        <v>0.005455121004612183</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.005455121004612189</v>
+        <v>0.005455121004612183</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.005455121004612189</v>
+        <v>0.005455121004612183</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.005455121004612189</v>
+        <v>0.005455121004612183</v>
       </c>
     </row>
     <row r="8">
@@ -3189,82 +3189,82 @@
         <v>0.007748596671606883</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01120020601474691</v>
+        <v>0.01120020601474692</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01120020601474691</v>
+        <v>0.01120020601474692</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01120020601474691</v>
+        <v>0.009362325856713601</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008286317066907082</v>
+        <v>0.008286317066907073</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01120020601474691</v>
+        <v>0.01191591969680278</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01120020601474691</v>
+        <v>0.01120020601474692</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01120020601474691</v>
+        <v>0.01120020601474692</v>
       </c>
       <c r="J8" t="n">
         <v>0.01119598980625243</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01120020601474691</v>
+        <v>0.01120020601474692</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01120020601474691</v>
+        <v>0.01120020601474692</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01120020601474691</v>
+        <v>0.01120020601474669</v>
       </c>
       <c r="N8" t="n">
-        <v>0.008524631330875453</v>
+        <v>0.008524631330875441</v>
       </c>
       <c r="O8" t="n">
-        <v>0.009259902482949885</v>
+        <v>0.009259902482949871</v>
       </c>
       <c r="P8" t="n">
-        <v>0.009079669757220259</v>
+        <v>0.009079669757220254</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.00707027665800943</v>
+        <v>0.007070276658009426</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01120020601474691</v>
+        <v>0.01120020601474692</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01120020601474691</v>
+        <v>0.01120020601474692</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01120020601474691</v>
+        <v>0.01120020601474692</v>
       </c>
       <c r="U8" t="n">
-        <v>0.009074483326675879</v>
+        <v>0.009513623750128061</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01117346683020952</v>
+        <v>0.01022799672162798</v>
       </c>
       <c r="W8" t="n">
         <v>0.01120088434975117</v>
       </c>
       <c r="X8" t="n">
-        <v>0.007386623509579663</v>
+        <v>0.007386623509579665</v>
       </c>
       <c r="Y8" t="n">
         <v>0.01462881601988031</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01120020601474691</v>
+        <v>0.007684481256507844</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01120020601474691</v>
+        <v>0.01120020601474692</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01480570058763403</v>
+        <v>0.01480570058763401</v>
       </c>
     </row>
     <row r="9">
@@ -3277,82 +3277,82 @@
         <v>0.01127584221592071</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0137536440384122</v>
+        <v>0.01375364403841221</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0137536440384122</v>
+        <v>0.01375364403841221</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0137536440384122</v>
+        <v>0.01318177831837653</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0137536440384122</v>
+        <v>0.008041633166361346</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0137536440384122</v>
+        <v>0.01375364512242332</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0137536440384122</v>
+        <v>0.01375364403841221</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0137536440384122</v>
+        <v>0.01375364403841221</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01374942782991774</v>
+        <v>0.01374942782991773</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0137536440384122</v>
+        <v>0.01375364403841221</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0137536440384122</v>
+        <v>0.01375364403841221</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0137536440384122</v>
+        <v>0.01375364403841221</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0137536440384122</v>
+        <v>0.01375364403841221</v>
       </c>
       <c r="O9" t="n">
         <v>0.01457478576123226</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01475336976177248</v>
+        <v>0.01475336976177249</v>
       </c>
       <c r="Q9" t="n">
         <v>0.01375364512242332</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0137536440384122</v>
+        <v>0.01375364403841221</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0137536440384122</v>
+        <v>0.01375364403841221</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0137536440384122</v>
+        <v>0.01375364403841221</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0137536440384122</v>
+        <v>0.01375364403841221</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01372690485387483</v>
+        <v>0.01658623423477865</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0137536440384122</v>
+        <v>0.01375364403841221</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0137536440384122</v>
+        <v>0.01375364403841221</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0137536440384122</v>
+        <v>0.01375364403841221</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0137536440384122</v>
+        <v>0.01225975030463356</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0137536440384122</v>
+        <v>0.01375364403841221</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0137536440384122</v>
+        <v>0.01375364403841221</v>
       </c>
     </row>
     <row r="10">
@@ -3368,79 +3368,79 @@
         <v>0.01486496760720181</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01362048761661909</v>
+        <v>0.01362048761661908</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01137503874330566</v>
+        <v>0.01137503874330567</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01433448505389496</v>
+        <v>0.01433448505389495</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01229618109017896</v>
+        <v>0.01229618109017895</v>
       </c>
       <c r="H10" t="n">
-        <v>0.013279953642799</v>
+        <v>0.01327995364279898</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01411341450064997</v>
+        <v>0.01411341450064996</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01316107840247597</v>
+        <v>0.01316107840247596</v>
       </c>
       <c r="K10" t="n">
         <v>0.01270344200933321</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01243646884530454</v>
+        <v>0.01243646884530453</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01263725834002918</v>
+        <v>0.01263725834002916</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01361033258856778</v>
+        <v>0.01361033258856777</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01348536818453658</v>
+        <v>0.01348536818453657</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01239888558444714</v>
+        <v>0.01239888558444713</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01422836148052772</v>
+        <v>0.01422836148052771</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01429587880850441</v>
+        <v>0.0142958788085044</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01320553942804176</v>
+        <v>0.01320553942804174</v>
       </c>
       <c r="T10" t="n">
         <v>0.01350678673491585</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0125865559261555</v>
+        <v>0.01258655592615548</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01451599576248731</v>
+        <v>0.01451599576248733</v>
       </c>
       <c r="W10" t="n">
         <v>0.01253994350974138</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01314495377825075</v>
+        <v>0.01314495377825073</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.01318303164419922</v>
+        <v>0.01318303164419921</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01406734625938294</v>
+        <v>0.01406734625938295</v>
       </c>
       <c r="AA10" t="n">
         <v>0.01328401326047031</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.01152000666761082</v>
+        <v>0.01152000666761081</v>
       </c>
     </row>
     <row r="11">
@@ -3450,61 +3450,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0145237966681225</v>
+        <v>0.01452379666812249</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01491256697624879</v>
+        <v>0.01491256697624878</v>
       </c>
       <c r="D11" t="n">
         <v>0.01454543922179639</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01166509207575304</v>
+        <v>0.01166509207575305</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01475407109654614</v>
+        <v>0.01475407109654613</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01410943804810197</v>
+        <v>0.01410943804810195</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01446309525327794</v>
+        <v>0.01446309525327793</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01484232259968229</v>
+        <v>0.01484232259968228</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01440203110093132</v>
+        <v>0.01440203110093131</v>
       </c>
       <c r="K11" t="n">
         <v>0.0142026797749416</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01407930698239141</v>
+        <v>0.0140793069823914</v>
       </c>
       <c r="M11" t="n">
         <v>0.01426762852411453</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01454134623177482</v>
+        <v>0.0145413462317748</v>
       </c>
       <c r="O11" t="n">
         <v>0.01455652107629301</v>
       </c>
       <c r="P11" t="n">
-        <v>0.01406219564694062</v>
+        <v>0.01406219564694061</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01489462329626536</v>
+        <v>0.01489462329626535</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01492570041945854</v>
+        <v>0.01492570041945852</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01442923654841938</v>
+        <v>0.01442923654841937</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01456628830894507</v>
+        <v>0.01456628830894506</v>
       </c>
       <c r="U11" t="n">
         <v>0.01414765776424249</v>
@@ -3513,19 +3513,19 @@
         <v>0.01478884374133596</v>
       </c>
       <c r="W11" t="n">
-        <v>0.01412638828446437</v>
+        <v>0.01412638828446436</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0143965071327983</v>
+        <v>0.01439650713279831</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01441890715469599</v>
+        <v>0.01441890715469598</v>
       </c>
       <c r="Z11" t="n">
         <v>0.01467008895503836</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.01446494239225564</v>
+        <v>0.01446494239225563</v>
       </c>
       <c r="AB11" t="n">
         <v>0.01358729741042653</v>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01533730858384786</v>
+        <v>0.01533730858384787</v>
       </c>
       <c r="C2" t="n">
         <v>0.01510101801227828</v>
@@ -3709,70 +3709,70 @@
         <v>0.01518163204568197</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01537710649002505</v>
+        <v>0.01537710649002504</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01533730858384786</v>
+        <v>0.01533730858384787</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01533730858384786</v>
+        <v>0.01533730858384787</v>
       </c>
       <c r="J2" t="n">
         <v>0.0153267030203786</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01534267372752947</v>
+        <v>0.01534267372752948</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01533730858384786</v>
+        <v>0.01533730858384787</v>
       </c>
       <c r="M2" t="n">
         <v>0.01531666478030007</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01521344255953003</v>
+        <v>0.01521344255953004</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01533722307175289</v>
+        <v>0.0153372230717529</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0153372977623119</v>
+        <v>0.01533729776231192</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01533730749722984</v>
+        <v>0.01533730749722985</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0153169340707697</v>
+        <v>0.01531693407076972</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01533730858384786</v>
+        <v>0.01533730858384787</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01533721048880214</v>
+        <v>0.01533721048880215</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01533701856373934</v>
+        <v>0.01533701856373935</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0151384952794258</v>
+        <v>0.01513849527942579</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01533730858384786</v>
+        <v>0.01533730858384787</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01521457250431762</v>
+        <v>0.01521457250431764</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01533709724812436</v>
+        <v>0.01533709724812438</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01521339260478751</v>
+        <v>0.01521339260478752</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01533730858384786</v>
+        <v>0.01533730858384787</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01518790024033958</v>
+        <v>0.01518790024033959</v>
       </c>
     </row>
     <row r="3">
@@ -3791,7 +3791,7 @@
         <v>0.01527547237462993</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01209137843294078</v>
+        <v>0.01209137843294079</v>
       </c>
       <c r="F3" t="n">
         <v>0.01528634640723039</v>
@@ -3873,79 +3873,79 @@
         <v>0.06231864446115448</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0215210466600512</v>
+        <v>0.02152104666005121</v>
       </c>
       <c r="D4" t="n">
-        <v>0.09173013394148546</v>
+        <v>0.09173013394148585</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03748928187142741</v>
+        <v>0.03748928187142753</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04594545538430331</v>
+        <v>0.0459454553843032</v>
       </c>
       <c r="G4" t="n">
         <v>0.1112329122858194</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08629813366550676</v>
+        <v>0.08629813366550665</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07505556088829964</v>
+        <v>0.0750555608882997</v>
       </c>
       <c r="J4" t="n">
-        <v>0.08342630451138</v>
+        <v>0.08342630451138006</v>
       </c>
       <c r="K4" t="n">
-        <v>0.08140215624987476</v>
+        <v>0.0814021562498748</v>
       </c>
       <c r="L4" t="n">
         <v>0.1049332913329743</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08557117952668102</v>
+        <v>0.08557117952668107</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1122357871620436</v>
+        <v>0.1122357871620443</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05838313942336345</v>
+        <v>0.05838313942336359</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1161183488887061</v>
+        <v>0.1161183488887071</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04074457060943482</v>
+        <v>0.04074457060943493</v>
       </c>
       <c r="R4" t="n">
         <v>0.04117674714645519</v>
       </c>
       <c r="S4" t="n">
-        <v>0.08000517752071319</v>
+        <v>0.08000517752071333</v>
       </c>
       <c r="T4" t="n">
-        <v>0.07590581134700428</v>
+        <v>0.07590581134700461</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1122357871620435</v>
+        <v>0.1122357871620443</v>
       </c>
       <c r="V4" t="n">
-        <v>0.03959847833925213</v>
+        <v>0.03959847833925224</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1176407518357803</v>
+        <v>0.11764075183578</v>
       </c>
       <c r="X4" t="n">
-        <v>0.128228235450588</v>
+        <v>0.1282282354505886</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1441055808196768</v>
+        <v>0.1441055808196769</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.04923310597925899</v>
+        <v>0.04923310597925897</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.09303611878413741</v>
+        <v>0.09303611878413748</v>
       </c>
       <c r="AB4" t="n">
         <v>0.1614827925633971</v>
@@ -3958,85 +3958,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003221595106635296</v>
+        <v>0.003221595106635287</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003221595106635294</v>
+        <v>0.003221595106635289</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003221595106635294</v>
+        <v>0.003221595106635289</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003221595106635294</v>
+        <v>0.003221595106635289</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003221595106635296</v>
+        <v>0.003221595106635286</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003221595106635294</v>
+        <v>0.003221595106635289</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003221595106635294</v>
+        <v>0.003221595106635289</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003221595106635294</v>
+        <v>0.003221595106635289</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0032180765425761</v>
+        <v>0.003218076542576099</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003221595106635294</v>
+        <v>0.003221595106635289</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003221595106635294</v>
+        <v>0.003221595106635289</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003221595106635294</v>
+        <v>0.003221595106635289</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003221595106635296</v>
+        <v>0.003221595106635286</v>
       </c>
       <c r="O5" t="n">
-        <v>0.003221595106635296</v>
+        <v>0.003221595106635286</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003221595106635296</v>
+        <v>0.003221595106635286</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.003221595106635296</v>
+        <v>0.003221595106635286</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003221595106635294</v>
+        <v>0.003221595106635289</v>
       </c>
       <c r="S5" t="n">
-        <v>0.003221595106635294</v>
+        <v>0.003221595106635289</v>
       </c>
       <c r="T5" t="n">
-        <v>0.003221595106635294</v>
+        <v>0.003221595106635289</v>
       </c>
       <c r="U5" t="n">
-        <v>0.003160180448607132</v>
+        <v>0.003160180448607131</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003199350696129884</v>
+        <v>0.003199350696129878</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003221595106635296</v>
+        <v>0.003221595106635289</v>
       </c>
       <c r="X5" t="n">
-        <v>0.003221595106635296</v>
+        <v>0.003221595106635286</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003160180448607132</v>
+        <v>0.003160180448607131</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.003221595106635294</v>
+        <v>0.003221595106635289</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.003221595106635294</v>
+        <v>0.003221595106635289</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003221595106635296</v>
+        <v>0.003221595106635286</v>
       </c>
     </row>
     <row r="6">
@@ -4046,49 +4046,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.006630070248584648</v>
+        <v>0.004487509713510016</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004487509713510018</v>
+        <v>0.004487509713510016</v>
       </c>
       <c r="D6" t="n">
         <v>0.006630070248584648</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004487509713510018</v>
+        <v>0.004487509713510016</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004487509713510018</v>
+        <v>0.006630070248584648</v>
       </c>
       <c r="G6" t="n">
+        <v>0.004487509713510016</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.004487509713510016</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.004487509713510016</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.006626551684525465</v>
+      </c>
+      <c r="K6" t="n">
         <v>0.006630070248584648</v>
       </c>
-      <c r="H6" t="n">
-        <v>0.004487509713510018</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.006630070248584648</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.006626551684525459</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.004487509713510018</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.006630070248584648</v>
+        <v>0.004487509713510016</v>
       </c>
       <c r="M6" t="n">
         <v>0.006630070248584648</v>
       </c>
       <c r="N6" t="n">
+        <v>0.004499274447113639</v>
+      </c>
+      <c r="O6" t="n">
         <v>0.004499274447113641</v>
       </c>
-      <c r="O6" t="n">
-        <v>0.00664707988812806</v>
-      </c>
       <c r="P6" t="n">
-        <v>0.006647058331619672</v>
+        <v>0.006647058331619664</v>
       </c>
       <c r="Q6" t="n">
         <v>0.006630070248584648</v>
@@ -4097,34 +4097,34 @@
         <v>0.006630070248584648</v>
       </c>
       <c r="S6" t="n">
-        <v>0.004487509713510018</v>
+        <v>0.004487509713510016</v>
       </c>
       <c r="T6" t="n">
-        <v>0.004487509713510018</v>
+        <v>0.004487509713510016</v>
       </c>
       <c r="U6" t="n">
+        <v>0.004487509713510016</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.006607825838079241</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.004626410730767887</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.004487509713510016</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.004588495166823438</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.004487509713510016</v>
+      </c>
+      <c r="AA6" t="n">
         <v>0.006630070248584648</v>
       </c>
-      <c r="V6" t="n">
-        <v>0.006607825838079236</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.006647064694674273</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.004487509713510018</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.004588495166823441</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.006630070248584648</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0.004487509713510018</v>
-      </c>
       <c r="AB6" t="n">
-        <v>0.004523217826831376</v>
+        <v>0.004523217826831377</v>
       </c>
     </row>
     <row r="7">
@@ -4134,85 +4134,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.005042368808868551</v>
+        <v>0.00504236880886855</v>
       </c>
       <c r="C7" t="n">
-        <v>0.005042368808868551</v>
+        <v>0.00504236880886855</v>
       </c>
       <c r="D7" t="n">
-        <v>0.005042368808868551</v>
+        <v>0.00504236880886855</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005042368808868551</v>
+        <v>0.00504236880886855</v>
       </c>
       <c r="F7" t="n">
-        <v>0.005042368808868551</v>
+        <v>0.00504236880886855</v>
       </c>
       <c r="G7" t="n">
-        <v>0.005042368808868551</v>
+        <v>0.00504236880886855</v>
       </c>
       <c r="H7" t="n">
-        <v>0.005042368808868551</v>
+        <v>0.00504236880886855</v>
       </c>
       <c r="I7" t="n">
-        <v>0.005042368808868551</v>
+        <v>0.00504236880886855</v>
       </c>
       <c r="J7" t="n">
-        <v>0.005038850244809363</v>
+        <v>0.00503885024480936</v>
       </c>
       <c r="K7" t="n">
-        <v>0.005042368808868551</v>
+        <v>0.00504236880886855</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005042368808868551</v>
+        <v>0.00504236880886855</v>
       </c>
       <c r="M7" t="n">
-        <v>0.005042368808868551</v>
+        <v>0.00504236880886855</v>
       </c>
       <c r="N7" t="n">
-        <v>0.005042368808868551</v>
+        <v>0.00504236880886855</v>
       </c>
       <c r="O7" t="n">
-        <v>0.005042229543847019</v>
+        <v>0.005042229543847016</v>
       </c>
       <c r="P7" t="n">
-        <v>0.005042229543847019</v>
+        <v>0.005042229543847016</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.005042368808868551</v>
+        <v>0.00504236880886855</v>
       </c>
       <c r="R7" t="n">
-        <v>0.005042368808868551</v>
+        <v>0.00504236880886855</v>
       </c>
       <c r="S7" t="n">
-        <v>0.005042368808868551</v>
+        <v>0.00504236880886855</v>
       </c>
       <c r="T7" t="n">
-        <v>0.005042368808868551</v>
+        <v>0.00504236880886855</v>
       </c>
       <c r="U7" t="n">
-        <v>0.005039810996508944</v>
+        <v>0.005039810996508934</v>
       </c>
       <c r="V7" t="n">
-        <v>0.005020124398363145</v>
+        <v>0.00502012439836314</v>
       </c>
       <c r="W7" t="n">
-        <v>0.005042368808868551</v>
+        <v>0.00504236880886855</v>
       </c>
       <c r="X7" t="n">
-        <v>0.005042368808868551</v>
+        <v>0.00504236880886855</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.005042368808868551</v>
+        <v>0.00504236880886855</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.005042368808868551</v>
+        <v>0.00504236880886855</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.005042368808868551</v>
+        <v>0.00504236880886855</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.005042368808868551</v>
+        <v>0.00504236880886855</v>
       </c>
     </row>
     <row r="8">
@@ -4222,85 +4222,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.007136674374882253</v>
+        <v>0.007136674374882259</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01024705000599072</v>
+        <v>0.01024705000599071</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01024705000599072</v>
+        <v>0.01024705000599071</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01024705000599072</v>
+        <v>0.008590866733779935</v>
       </c>
       <c r="F8" t="n">
-        <v>0.007621234545967464</v>
+        <v>0.007621234545967458</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01024705000599072</v>
+        <v>0.010892006654951</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01024705000599072</v>
+        <v>0.01024705000599071</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01024705000599072</v>
+        <v>0.01024705000599071</v>
       </c>
       <c r="J8" t="n">
         <v>0.01024353144193152</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01024705000599072</v>
+        <v>0.01024705000599071</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01024705000599072</v>
+        <v>0.01024705000599071</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01024705000599072</v>
+        <v>0.01024705000599051</v>
       </c>
       <c r="N8" t="n">
-        <v>0.007835988536183764</v>
+        <v>0.007835988536183759</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00849856916047732</v>
+        <v>0.008498569160477323</v>
       </c>
       <c r="P8" t="n">
-        <v>0.008336154639537486</v>
+        <v>0.008336154639537498</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.006525414573884556</v>
+        <v>0.006525414573884548</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01024705000599072</v>
+        <v>0.01024705000599071</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01024705000599072</v>
+        <v>0.01024705000599071</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01024705000599072</v>
+        <v>0.01024705000599071</v>
       </c>
       <c r="U8" t="n">
-        <v>0.00833132683800588</v>
+        <v>0.008727042856494354</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0102248055954853</v>
+        <v>0.00937262571949994</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01024766127912719</v>
+        <v>0.01024766127912718</v>
       </c>
       <c r="X8" t="n">
-        <v>0.006810486677911758</v>
+        <v>0.006810486677911762</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01333641929054203</v>
+        <v>0.01333641929054204</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01024705000599072</v>
+        <v>0.007078897551142207</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01024705000599072</v>
+        <v>0.01024705000599071</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01349609743347845</v>
+        <v>0.01349609743347847</v>
       </c>
     </row>
     <row r="9">
@@ -4310,85 +4310,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009867419688494018</v>
+        <v>0.009867419688494026</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01197642180769886</v>
+        <v>0.01197642180769884</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01197642180769886</v>
+        <v>0.01197642180769884</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01197642180769886</v>
+        <v>0.01148967381170241</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01197642180769886</v>
+        <v>0.007114594470898735</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01197642180769886</v>
+        <v>0.011976423225597</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01197642180769886</v>
+        <v>0.01197642180769884</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01197642180769886</v>
+        <v>0.01197642180769884</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01197290324363965</v>
+        <v>0.01197290324363966</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01197642180769886</v>
+        <v>0.01197642180769884</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01197642180769886</v>
+        <v>0.01197642180769884</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01197642180769886</v>
+        <v>0.01197642180769884</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01197642180769886</v>
+        <v>0.01197642180769884</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0126753442362885</v>
+        <v>0.01267534423628851</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01282734756464886</v>
+        <v>0.01282734756464885</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01197642322559699</v>
+        <v>0.011976423225597</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01197642180769886</v>
+        <v>0.01197642180769884</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01197642180769886</v>
+        <v>0.01197642180769884</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01197642180769886</v>
+        <v>0.01197642180769884</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01197642180769886</v>
+        <v>0.01197642180769884</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01195417739719345</v>
+        <v>0.01438792094978081</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01197642180769886</v>
+        <v>0.01197642180769884</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01197642180769886</v>
+        <v>0.01197642180769884</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01197642180769886</v>
+        <v>0.01197642180769884</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01197642180769886</v>
+        <v>0.01070488163263573</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01197642180769886</v>
+        <v>0.01197642180769884</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.01197642180769886</v>
+        <v>0.01197642180769884</v>
       </c>
     </row>
     <row r="10">
@@ -4398,22 +4398,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01380154823017061</v>
+        <v>0.01380154823017062</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0148810541763246</v>
+        <v>0.01488105417632461</v>
       </c>
       <c r="D10" t="n">
         <v>0.01330814000643065</v>
       </c>
       <c r="E10" t="n">
-        <v>0.011291648307688</v>
+        <v>0.01129164830768798</v>
       </c>
       <c r="F10" t="n">
         <v>0.01434072907619923</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01245626428142457</v>
+        <v>0.01245626428142458</v>
       </c>
       <c r="H10" t="n">
         <v>0.01353290870777778</v>
@@ -4422,37 +4422,37 @@
         <v>0.0137088935716901</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01332533832149281</v>
+        <v>0.0133253383214928</v>
       </c>
       <c r="K10" t="n">
         <v>0.01333590288724825</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01287996806422951</v>
+        <v>0.01287996806422952</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01348236440798091</v>
+        <v>0.01348236440798092</v>
       </c>
       <c r="N10" t="n">
         <v>0.01407560510008864</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01382658931269044</v>
+        <v>0.01382658931269045</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01242613614249516</v>
+        <v>0.01242613614249515</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01441213572352608</v>
+        <v>0.01441213572352609</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01444330934281671</v>
+        <v>0.01444330934281673</v>
       </c>
       <c r="S10" t="n">
         <v>0.01336510110941501</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01367815479314135</v>
+        <v>0.01367815479314136</v>
       </c>
       <c r="U10" t="n">
         <v>0.01262916910226903</v>
@@ -4464,19 +4464,19 @@
         <v>0.01261938378116488</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01231763552157118</v>
+        <v>0.01231763552157117</v>
       </c>
       <c r="Y10" t="n">
         <v>0.01197692318287197</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01407386617737391</v>
+        <v>0.01407386617737392</v>
       </c>
       <c r="AA10" t="n">
         <v>0.01319446691473578</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.01179905514815082</v>
+        <v>0.01179905514815083</v>
       </c>
     </row>
     <row r="11">
@@ -4489,37 +4489,37 @@
         <v>0.01466666840100131</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01491136169732082</v>
+        <v>0.01491136169732083</v>
       </c>
       <c r="D11" t="n">
         <v>0.0144501865726028</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01164587138364831</v>
+        <v>0.0116458713836483</v>
       </c>
       <c r="F11" t="n">
         <v>0.01475137314655916</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01413914248278293</v>
+        <v>0.01413914248278294</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01454443656220922</v>
+        <v>0.01454443656220924</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01462451023611981</v>
+        <v>0.01462451023611982</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01444421192851732</v>
+        <v>0.01444421192851733</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01445749208375497</v>
+        <v>0.01445749208375498</v>
       </c>
       <c r="L11" t="n">
         <v>0.01424734648859639</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01450083193514199</v>
+        <v>0.014500831935142</v>
       </c>
       <c r="N11" t="n">
         <v>0.01466749912586361</v>
@@ -4531,16 +4531,16 @@
         <v>0.01404084608453171</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01494448711072934</v>
+        <v>0.01494448711072935</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01494844194508671</v>
+        <v>0.01494844194508672</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01446808357018307</v>
+        <v>0.01446808357018308</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0146104747414539</v>
+        <v>0.01461047474145392</v>
       </c>
       <c r="U11" t="n">
         <v>0.01413308654559093</v>
@@ -4549,22 +4549,22 @@
         <v>0.0147091303572688</v>
       </c>
       <c r="W11" t="n">
-        <v>0.01412877980936914</v>
+        <v>0.01412877980936915</v>
       </c>
       <c r="X11" t="n">
         <v>0.01392985889525704</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01383635208031851</v>
+        <v>0.0138363520803185</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.01466593048974781</v>
+        <v>0.01466593048974782</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.01439044446782511</v>
+        <v>0.01439044446782512</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.01368051130659295</v>
+        <v>0.01368051130659296</v>
       </c>
     </row>
   </sheetData>
@@ -4736,7 +4736,7 @@
         <v>0.01509982858846274</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01524176478261852</v>
+        <v>0.01524176478261851</v>
       </c>
       <c r="E2" t="n">
         <v>0.01204395664471219</v>
@@ -4745,7 +4745,7 @@
         <v>0.01521886061420782</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01526404284010404</v>
+        <v>0.01526404284010403</v>
       </c>
       <c r="H2" t="n">
         <v>0.01531306676366089</v>
@@ -4754,25 +4754,25 @@
         <v>0.01531306676366089</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01530793206975433</v>
+        <v>0.01530793206975435</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01531994464858141</v>
+        <v>0.0153199446485814</v>
       </c>
       <c r="L2" t="n">
         <v>0.01531306676366089</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01527840785397661</v>
+        <v>0.0152784078539766</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01515525100535196</v>
+        <v>0.01515525100535195</v>
       </c>
       <c r="O2" t="n">
         <v>0.01531296893886423</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01531253322113761</v>
+        <v>0.0153125332211376</v>
       </c>
       <c r="Q2" t="n">
         <v>0.01531306567704286</v>
@@ -4802,7 +4802,7 @@
         <v>0.01531269597312642</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0151910606807275</v>
+        <v>0.01519106068072749</v>
       </c>
       <c r="AA2" t="n">
         <v>0.01531306676366089</v>
@@ -4818,16 +4818,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01527697731903288</v>
+        <v>0.01527697731903287</v>
       </c>
       <c r="C3" t="n">
         <v>0.01529929567698317</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01527697731903288</v>
+        <v>0.01527697731903287</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01216652018016176</v>
+        <v>0.01216652018016175</v>
       </c>
       <c r="F3" t="n">
         <v>0.01529140920963796</v>
@@ -4836,52 +4836,52 @@
         <v>0.01510822624106285</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01527697731903288</v>
+        <v>0.01527697731903287</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01527697731903288</v>
+        <v>0.01527697731903287</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01527184203869823</v>
+        <v>0.01527184203869824</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01528450376939842</v>
+        <v>0.01528450376939841</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01527697731903288</v>
+        <v>0.01527697731903287</v>
       </c>
       <c r="M3" t="n">
         <v>0.01527676658410373</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01527697731903288</v>
+        <v>0.01527697731903287</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01527687026924492</v>
+        <v>0.01527687026924491</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01527639346300129</v>
+        <v>0.01527639346300128</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.015276976129937</v>
+        <v>0.01527697612993699</v>
       </c>
       <c r="R3" t="n">
         <v>0.01523399795636621</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01527697731903288</v>
+        <v>0.01527697731903287</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01527682315827431</v>
+        <v>0.0152768231582743</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01527683876545398</v>
+        <v>0.01527683876545397</v>
       </c>
       <c r="V3" t="n">
         <v>0.01516910185563828</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01527697731903288</v>
+        <v>0.01527697731903287</v>
       </c>
       <c r="X3" t="n">
         <v>0.01521540281939856</v>
@@ -4893,7 +4893,7 @@
         <v>0.01527855046533962</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01527697731903288</v>
+        <v>0.01527697731903287</v>
       </c>
       <c r="AB3" t="n">
         <v>0.01511347960046277</v>
@@ -4906,85 +4906,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05317827334312791</v>
+        <v>0.05317827334312799</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02048712678886888</v>
+        <v>0.0204871267888689</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06149712247273581</v>
+        <v>0.06149712247273578</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02606768850906323</v>
+        <v>0.02606768850906325</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05364415846965185</v>
+        <v>0.05364415846965179</v>
       </c>
       <c r="G4" t="n">
-        <v>0.09590931459221622</v>
+        <v>0.09590931459221649</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08103873750394602</v>
+        <v>0.08103873750394613</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07171341546786485</v>
+        <v>0.0717134154678649</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07533432659703174</v>
+        <v>0.07533432659703183</v>
       </c>
       <c r="K4" t="n">
-        <v>0.09516461113163191</v>
+        <v>0.09516461113163238</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08622919795956202</v>
+        <v>0.08622919795956209</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07184420408345542</v>
+        <v>0.07184420408345546</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1195590079784536</v>
+        <v>0.1195590079784534</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04883006550072163</v>
+        <v>0.04883006550072154</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1013875742962346</v>
+        <v>0.1013875742962347</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04161045842025973</v>
+        <v>0.04161045842025976</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05049243545857981</v>
+        <v>0.05049243545857991</v>
       </c>
       <c r="S4" t="n">
-        <v>0.07409412394674626</v>
+        <v>0.07409412394674636</v>
       </c>
       <c r="T4" t="n">
-        <v>0.07573329997158509</v>
+        <v>0.07573329997158507</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1195590079784535</v>
+        <v>0.1195590079784534</v>
       </c>
       <c r="V4" t="n">
-        <v>0.05860541481470827</v>
+        <v>0.05860541481470821</v>
       </c>
       <c r="W4" t="n">
         <v>0.1060953029669112</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1350080959263091</v>
+        <v>0.1350080959263098</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2277400707154587</v>
+        <v>0.2277400707154589</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.04159951206288256</v>
+        <v>0.04159951206288258</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.09818257412332773</v>
+        <v>0.09818257412332788</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1457271112953499</v>
+        <v>0.14572711129535</v>
       </c>
     </row>
     <row r="5">
@@ -4994,85 +4994,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003345297102234102</v>
+        <v>0.003345297102234101</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003345297102234102</v>
+        <v>0.0033452971022341</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003345297102234102</v>
+        <v>0.0033452971022341</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003345297102234102</v>
+        <v>0.0033452971022341</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003345297102234102</v>
+        <v>0.003345297102234101</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003345297102234102</v>
+        <v>0.0033452971022341</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003345297102234102</v>
+        <v>0.0033452971022341</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003345297102234102</v>
+        <v>0.0033452971022341</v>
       </c>
       <c r="J5" t="n">
         <v>0.003342854540897313</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003345297102234102</v>
+        <v>0.0033452971022341</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003345297102234102</v>
+        <v>0.0033452971022341</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003345297102234102</v>
+        <v>0.0033452971022341</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003345297102234102</v>
+        <v>0.003345297102234101</v>
       </c>
       <c r="O5" t="n">
-        <v>0.003345297102234102</v>
+        <v>0.003345297102234101</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003345297102234102</v>
+        <v>0.003345297102234101</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.003345297102234102</v>
+        <v>0.003345297102234101</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003345297102234102</v>
+        <v>0.0033452971022341</v>
       </c>
       <c r="S5" t="n">
-        <v>0.003345297102234102</v>
+        <v>0.0033452971022341</v>
       </c>
       <c r="T5" t="n">
-        <v>0.003345297102234102</v>
+        <v>0.0033452971022341</v>
       </c>
       <c r="U5" t="n">
-        <v>0.003301452205560179</v>
+        <v>0.003301452205560181</v>
       </c>
       <c r="V5" t="n">
         <v>0.003329920967910476</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003345297102234102</v>
+        <v>0.003345297102234101</v>
       </c>
       <c r="X5" t="n">
-        <v>0.003345297102234102</v>
+        <v>0.003345297102234101</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003301452205560179</v>
+        <v>0.003301452205560181</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.003345297102234102</v>
+        <v>0.0033452971022341</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.003345297102234102</v>
+        <v>0.0033452971022341</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003345297102234102</v>
+        <v>0.003345297102234101</v>
       </c>
     </row>
     <row r="6">
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.004791901467907598</v>
+        <v>0.007001603899890678</v>
       </c>
       <c r="C6" t="n">
         <v>0.004791901467907598</v>
@@ -5091,76 +5091,76 @@
         <v>0.004791901467907598</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004791901467907598</v>
+        <v>0.007001603899890678</v>
       </c>
       <c r="F6" t="n">
         <v>0.004791901467907598</v>
       </c>
       <c r="G6" t="n">
+        <v>0.007001603899890678</v>
+      </c>
+      <c r="H6" t="n">
         <v>0.004791901467907598</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.007001603899890672</v>
       </c>
       <c r="I6" t="n">
         <v>0.004791901467907598</v>
       </c>
       <c r="J6" t="n">
-        <v>0.004789458906570811</v>
+        <v>0.006999161338553885</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007001603899890672</v>
+        <v>0.007001603899890678</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004791901467907598</v>
+        <v>0.007001603899890678</v>
       </c>
       <c r="M6" t="n">
         <v>0.004791901467907598</v>
       </c>
       <c r="N6" t="n">
-        <v>0.004812180925047949</v>
+        <v>0.004812180925047914</v>
       </c>
       <c r="O6" t="n">
-        <v>0.004812180925047947</v>
+        <v>0.007034665492970694</v>
       </c>
       <c r="P6" t="n">
-        <v>0.00703464008575328</v>
+        <v>0.004665552430907345</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.007001603899890672</v>
+        <v>0.007001603899890678</v>
       </c>
       <c r="R6" t="n">
-        <v>0.007001603899890672</v>
+        <v>0.007001603899890678</v>
       </c>
       <c r="S6" t="n">
-        <v>0.007001603899890672</v>
+        <v>0.007001603899890678</v>
       </c>
       <c r="T6" t="n">
+        <v>0.007001603899890678</v>
+      </c>
+      <c r="U6" t="n">
         <v>0.004791901467907598</v>
       </c>
-      <c r="U6" t="n">
-        <v>0.007001603899890672</v>
-      </c>
       <c r="V6" t="n">
-        <v>0.006986227765567049</v>
+        <v>0.004776525333583972</v>
       </c>
       <c r="W6" t="n">
-        <v>0.007034660393076288</v>
+        <v>0.007034660393076261</v>
       </c>
       <c r="X6" t="n">
         <v>0.004791901467907598</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.004920295674524067</v>
+        <v>0.004920295674524048</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.007001603899890672</v>
+        <v>0.007001603899890678</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.007001603899890672</v>
+        <v>0.007001603899890678</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.004826958740456287</v>
+        <v>0.004826958740456283</v>
       </c>
     </row>
     <row r="7">
@@ -5194,7 +5194,7 @@
         <v>0.005038640649868874</v>
       </c>
       <c r="J7" t="n">
-        <v>0.005036198088532087</v>
+        <v>0.005036198088532085</v>
       </c>
       <c r="K7" t="n">
         <v>0.005038640649868874</v>
@@ -5209,10 +5209,10 @@
         <v>0.005038640649868874</v>
       </c>
       <c r="O7" t="n">
-        <v>0.005038499371971038</v>
+        <v>0.005038499371971039</v>
       </c>
       <c r="P7" t="n">
-        <v>0.005038499371971038</v>
+        <v>0.005038499371971039</v>
       </c>
       <c r="Q7" t="n">
         <v>0.005038640649868874</v>
@@ -5227,10 +5227,10 @@
         <v>0.005038640649868874</v>
       </c>
       <c r="U7" t="n">
-        <v>0.005036224212863456</v>
+        <v>0.005036224212863457</v>
       </c>
       <c r="V7" t="n">
-        <v>0.00502326451554525</v>
+        <v>0.005023264515545247</v>
       </c>
       <c r="W7" t="n">
         <v>0.005038640649868874</v>
@@ -5261,82 +5261,82 @@
         <v>0.007233143456080066</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01041258828354279</v>
+        <v>0.01041258828354277</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01041258828354279</v>
+        <v>0.01041258828354277</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01041258828354279</v>
+        <v>0.008719627701685136</v>
       </c>
       <c r="F8" t="n">
-        <v>0.007728463800726847</v>
+        <v>0.007728463800726844</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01041258828354279</v>
+        <v>0.01107186688031216</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01041258828354279</v>
+        <v>0.01041258828354277</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01041258828354279</v>
+        <v>0.01041258828354277</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01041014572220598</v>
+        <v>0.01041014572220597</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01041258828354279</v>
+        <v>0.01041258828354277</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01041258828354279</v>
+        <v>0.01041258828354277</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01041258828354279</v>
+        <v>0.01041258828354266</v>
       </c>
       <c r="N8" t="n">
-        <v>0.007947986631535566</v>
+        <v>0.007947986631535562</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00862528056278155</v>
+        <v>0.008625280562781546</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00845925945478402</v>
+        <v>0.008459259454784011</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.006608309981567151</v>
+        <v>0.006608309981567154</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01041258828354279</v>
+        <v>0.01041258828354277</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01041258828354279</v>
+        <v>0.01041258828354277</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01041258828354279</v>
+        <v>0.01041258828354277</v>
       </c>
       <c r="U8" t="n">
-        <v>0.008454467870698288</v>
+        <v>0.008858980503521786</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01039721214921915</v>
+        <v>0.009526277185143676</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01041321313075804</v>
+        <v>0.01041321313075802</v>
       </c>
       <c r="X8" t="n">
-        <v>0.006899712414685544</v>
+        <v>0.006899712414685539</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01357082159594219</v>
+        <v>0.01357082159594217</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01041258828354279</v>
+        <v>0.007174083636554591</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01041258828354279</v>
+        <v>0.01041258828354277</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01373378426210199</v>
+        <v>0.01373378426210198</v>
       </c>
     </row>
     <row r="9">
@@ -5346,85 +5346,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009380360398283875</v>
+        <v>0.009380360398283868</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01135804751972759</v>
+        <v>0.01135804751972758</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01135804751972759</v>
+        <v>0.01135804751972758</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01135804751972759</v>
+        <v>0.01090160639547872</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01135804751972759</v>
+        <v>0.006798937251729193</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01135804751972759</v>
+        <v>0.01135804881527645</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01135804751972759</v>
+        <v>0.01135804751972758</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01135804751972759</v>
+        <v>0.01135804751972758</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01135560495839079</v>
+        <v>0.01135560495839078</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01135804751972759</v>
+        <v>0.01135804751972758</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01135804751972759</v>
+        <v>0.01135804751972758</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01135804751972759</v>
+        <v>0.01135804751972758</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01135804751972759</v>
+        <v>0.01135804751972758</v>
       </c>
       <c r="O9" t="n">
         <v>0.01201345216710589</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01215599115130099</v>
+        <v>0.012155991151301</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01135804881527646</v>
+        <v>0.01135804881527645</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01135804751972759</v>
+        <v>0.01135804751972758</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01135804751972759</v>
+        <v>0.01135804751972758</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01135804751972759</v>
+        <v>0.01135804751972758</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01135804751972759</v>
+        <v>0.01135804751972758</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01134267138540396</v>
+        <v>0.01362488046370806</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01135804751972759</v>
+        <v>0.01135804751972758</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01135804751972759</v>
+        <v>0.01135804751972758</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01135804751972759</v>
+        <v>0.01135804751972758</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01135804751972759</v>
+        <v>0.01016567856274567</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01135804751972759</v>
+        <v>0.01135804751972758</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.01135804751972759</v>
+        <v>0.01135804751972758</v>
       </c>
     </row>
     <row r="10">
@@ -5434,85 +5434,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01399320406158588</v>
+        <v>0.01399320406158587</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01490505012543742</v>
+        <v>0.0149050501254374</v>
       </c>
       <c r="D10" t="n">
         <v>0.01393233037882919</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01160919702807327</v>
+        <v>0.01160919702807328</v>
       </c>
       <c r="F10" t="n">
         <v>0.0141637160182888</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01269389868227209</v>
+        <v>0.01269389868227206</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01365036763194867</v>
+        <v>0.01365036763194866</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01375716519092657</v>
+        <v>0.01375716519092655</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01349346246948376</v>
+        <v>0.01349346246948375</v>
       </c>
       <c r="K10" t="n">
         <v>0.01299395613755931</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01324544503253157</v>
+        <v>0.01324544503253153</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01372228399332055</v>
+        <v>0.01372228399332053</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01443553315985158</v>
+        <v>0.01443553315985157</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0140846003918069</v>
+        <v>0.01408460039180688</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01271037083933654</v>
+        <v>0.01271037083933652</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01437178357439985</v>
+        <v>0.01437178357439983</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01422384726386247</v>
+        <v>0.01422384726386246</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01349005877298169</v>
+        <v>0.01349005877298168</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01368528766629822</v>
+        <v>0.0136852876662982</v>
       </c>
       <c r="U10" t="n">
         <v>0.01234642879493632</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01370530390498926</v>
+        <v>0.01370530390498927</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0128934702142691</v>
+        <v>0.01289347021426909</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01214082159766553</v>
+        <v>0.0121408215976655</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.01012310322462013</v>
+        <v>0.01012310322462012</v>
       </c>
       <c r="Z10" t="n">
         <v>0.01422420243444888</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.01308883997951932</v>
+        <v>0.0130888399795193</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.01208646702491941</v>
+        <v>0.0120864670249194</v>
       </c>
     </row>
     <row r="11">
@@ -5528,31 +5528,31 @@
         <v>0.0149204456061234</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0146299461396903</v>
+        <v>0.01462994613969029</v>
       </c>
       <c r="E11" t="n">
         <v>0.01179037283442843</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01470575661839897</v>
+        <v>0.01470575661839898</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01416551610684883</v>
+        <v>0.01416551610684882</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01457295417234008</v>
+        <v>0.01457295417234006</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01462154740201864</v>
+        <v>0.01462154740201863</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01449876369840235</v>
+        <v>0.01449876369840234</v>
       </c>
       <c r="K11" t="n">
         <v>0.01427773817655242</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01438871309919353</v>
+        <v>0.01438871309919352</v>
       </c>
       <c r="M11" t="n">
         <v>0.01457111332132817</v>
@@ -5561,34 +5561,34 @@
         <v>0.01477239123140103</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01477048234509127</v>
+        <v>0.01477048234509126</v>
       </c>
       <c r="P11" t="n">
-        <v>0.01414498474994123</v>
+        <v>0.01414498474994122</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01490120017959595</v>
+        <v>0.01490120017959594</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01481416936371823</v>
+        <v>0.01481416936371822</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01450001313063607</v>
+        <v>0.01450001313063606</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01458877216688373</v>
+        <v>0.01458877216688372</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01397959427457864</v>
+        <v>0.01397959427457863</v>
       </c>
       <c r="V11" t="n">
         <v>0.01448596928614478</v>
       </c>
       <c r="W11" t="n">
-        <v>0.01422856343520691</v>
+        <v>0.0142285634352069</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01385785420208923</v>
+        <v>0.01385785420208921</v>
       </c>
       <c r="Y11" t="n">
         <v>0.01296785145623912</v>
@@ -5600,7 +5600,7 @@
         <v>0.01431745730100226</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.01378635805176366</v>
+        <v>0.01378635805176365</v>
       </c>
     </row>
   </sheetData>
@@ -5769,7 +5769,7 @@
         <v>0.01486135376963004</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01476238867391188</v>
+        <v>0.01476238867391189</v>
       </c>
       <c r="D2" t="n">
         <v>0.0148652425803954</v>
@@ -5781,7 +5781,7 @@
         <v>0.01478838010385856</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01479336727702757</v>
+        <v>0.01479336727702758</v>
       </c>
       <c r="H2" t="n">
         <v>0.01486135376963004</v>
@@ -5790,10 +5790,10 @@
         <v>0.01486135376963004</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01485652024078244</v>
+        <v>0.01485652024078245</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01486513623038037</v>
+        <v>0.01486513623038038</v>
       </c>
       <c r="L2" t="n">
         <v>0.01486135376963004</v>
@@ -5802,7 +5802,7 @@
         <v>0.01489096591478917</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0148985152094738</v>
+        <v>0.01489851520947381</v>
       </c>
       <c r="O2" t="n">
         <v>0.01486127719342785</v>
@@ -5811,7 +5811,7 @@
         <v>0.01486133219591873</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01486135268301201</v>
+        <v>0.01486135268301202</v>
       </c>
       <c r="R2" t="n">
         <v>0.01486206273330818</v>
@@ -5823,19 +5823,19 @@
         <v>0.01486132046054185</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01486147462816506</v>
+        <v>0.01486147462816507</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01478522532512054</v>
+        <v>0.01478522532512052</v>
       </c>
       <c r="W2" t="n">
         <v>0.01486135376963004</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01485107122397734</v>
+        <v>0.01485107122397735</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01486117794371498</v>
+        <v>0.01486117794371499</v>
       </c>
       <c r="Z2" t="n">
         <v>0.01483663785732386</v>
@@ -5857,7 +5857,7 @@
         <v>0.01498674330568567</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01500807808062829</v>
+        <v>0.01500807808062828</v>
       </c>
       <c r="D3" t="n">
         <v>0.01498674330568567</v>
@@ -5869,7 +5869,7 @@
         <v>0.01499444815230835</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01490390956144081</v>
+        <v>0.0149039095614408</v>
       </c>
       <c r="H3" t="n">
         <v>0.01498674330568567</v>
@@ -5878,7 +5878,7 @@
         <v>0.01498674330568567</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01498190922681777</v>
+        <v>0.01498190922681778</v>
       </c>
       <c r="K3" t="n">
         <v>0.01499088241653319</v>
@@ -5887,13 +5887,13 @@
         <v>0.01498674330568567</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01498671324715544</v>
+        <v>0.01498671324715543</v>
       </c>
       <c r="N3" t="n">
         <v>0.01498674330568567</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01498665950823008</v>
+        <v>0.01498665950823007</v>
       </c>
       <c r="P3" t="n">
         <v>0.01498671969767216</v>
@@ -5902,7 +5902,7 @@
         <v>0.01498674211658979</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01498751909246069</v>
+        <v>0.01498751909246068</v>
       </c>
       <c r="S3" t="n">
         <v>0.01498674330568567</v>
@@ -5914,13 +5914,13 @@
         <v>0.01498687556139731</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01498693967952546</v>
+        <v>0.01498693967952545</v>
       </c>
       <c r="W3" t="n">
         <v>0.01498674330568567</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01497549109051452</v>
+        <v>0.01497549109051451</v>
       </c>
       <c r="Y3" t="n">
         <v>0.01498655089919136</v>
@@ -5945,82 +5945,82 @@
         <v>0.01947182554381957</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008655120378387235</v>
+        <v>0.008655120378387225</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04285412240707424</v>
+        <v>0.04285412240707427</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02130405127203754</v>
+        <v>0.02130405127203756</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01938404528497387</v>
+        <v>0.01938404528497392</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03747977730246949</v>
+        <v>0.03747977730246959</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0554379491918793</v>
+        <v>0.05543794919187929</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03405635735912686</v>
+        <v>0.03405635735912683</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03786126709789526</v>
+        <v>0.03786126709789527</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05660359845531954</v>
+        <v>0.05660359845531944</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05080900598094822</v>
+        <v>0.05080900598094829</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04680956367979144</v>
+        <v>0.04680956367979145</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06084019240160619</v>
+        <v>0.06084019240160618</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02252467187719789</v>
+        <v>0.02252467187719785</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0424000510383978</v>
+        <v>0.04240005103839779</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03181792787753266</v>
+        <v>0.03181792787753267</v>
       </c>
       <c r="R4" t="n">
-        <v>0.03218285921376726</v>
+        <v>0.03218285921376721</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03271297921669401</v>
+        <v>0.03271297921669399</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02755048178738101</v>
+        <v>0.02755048178738102</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0608401924016062</v>
+        <v>0.06084019240160618</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0185706898177001</v>
+        <v>0.01857068981770005</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1097428272734106</v>
+        <v>0.1097428272734107</v>
       </c>
       <c r="X4" t="n">
-        <v>0.04946376261895059</v>
+        <v>0.04946376261895062</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02568161890466802</v>
+        <v>0.02568161890466776</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03035998499942074</v>
+        <v>0.03035998499942068</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.05322928152234834</v>
+        <v>0.05322928152234838</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0798223017367562</v>
+        <v>0.07982230173675635</v>
       </c>
     </row>
     <row r="5">
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002642470524259718</v>
+        <v>0.002642470524259719</v>
       </c>
       <c r="C5" t="n">
         <v>0.002642470524259719</v>
@@ -6042,7 +6042,7 @@
         <v>0.002642470524259719</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002642470524259718</v>
+        <v>0.002642470524259719</v>
       </c>
       <c r="G5" t="n">
         <v>0.002642470524259719</v>
@@ -6066,16 +6066,16 @@
         <v>0.002642470524259719</v>
       </c>
       <c r="N5" t="n">
-        <v>0.002642470524259718</v>
+        <v>0.002642470524259719</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002642470524259718</v>
+        <v>0.002642470524259719</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002642470524259718</v>
+        <v>0.002642470524259719</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002642470524259718</v>
+        <v>0.002642470524259719</v>
       </c>
       <c r="R5" t="n">
         <v>0.002642470524259719</v>
@@ -6087,19 +6087,19 @@
         <v>0.002642470524259719</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002610937943739031</v>
+        <v>0.002610937943739033</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002626340522181348</v>
+        <v>0.002626340522181351</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002642470524259718</v>
+        <v>0.002642470524259719</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002642470524259718</v>
+        <v>0.002642470524259719</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.002610937943739031</v>
+        <v>0.002610937943739033</v>
       </c>
       <c r="Z5" t="n">
         <v>0.002642470524259719</v>
@@ -6108,7 +6108,7 @@
         <v>0.002642470524259719</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.002642470524259718</v>
+        <v>0.002642470524259719</v>
       </c>
     </row>
     <row r="6">
@@ -6118,85 +6118,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.003779717658574224</v>
+        <v>0.003779717658574212</v>
       </c>
       <c r="C6" t="n">
-        <v>0.005694947119773741</v>
+        <v>0.005694947119773747</v>
       </c>
       <c r="D6" t="n">
-        <v>0.005694947119773741</v>
+        <v>0.003779717658574212</v>
       </c>
       <c r="E6" t="n">
-        <v>0.005694947119773741</v>
+        <v>0.003779717658574212</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005694947119773741</v>
+        <v>0.005694947119773747</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003779717658574224</v>
+        <v>0.005694947119773747</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003779717658574224</v>
+        <v>0.003779717658574212</v>
       </c>
       <c r="I6" t="n">
-        <v>0.005694947119773741</v>
+        <v>0.003779717658574212</v>
       </c>
       <c r="J6" t="n">
-        <v>0.003777165372356502</v>
+        <v>0.003777165372356475</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005694947119773741</v>
+        <v>0.003779717658574212</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005694947119773741</v>
+        <v>0.003779717658574212</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003779717658574224</v>
+        <v>0.005694947119773747</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003783900811371726</v>
+        <v>0.003783900811371721</v>
       </c>
       <c r="O6" t="n">
-        <v>0.005717416497329697</v>
+        <v>0.005717416497329711</v>
       </c>
       <c r="P6" t="n">
-        <v>0.00571741251890747</v>
+        <v>0.003665281048251791</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.005694947119773741</v>
+        <v>0.005694947119773747</v>
       </c>
       <c r="R6" t="n">
-        <v>0.005694947119773741</v>
+        <v>0.003779717658574212</v>
       </c>
       <c r="S6" t="n">
-        <v>0.005694947119773741</v>
+        <v>0.003779717658574212</v>
       </c>
       <c r="T6" t="n">
-        <v>0.003779717658574224</v>
+        <v>0.005694947119773747</v>
       </c>
       <c r="U6" t="n">
-        <v>0.005694947119773741</v>
+        <v>0.003779717658574212</v>
       </c>
       <c r="V6" t="n">
-        <v>0.003763587656495871</v>
+        <v>0.005678817117695369</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0039129226996285</v>
+        <v>0.003912922699628373</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003779717658574224</v>
+        <v>0.003779717658574212</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.003870705927268619</v>
+        <v>0.003870705927268649</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.003779717658574224</v>
+        <v>0.005694947119773747</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003779717658574224</v>
+        <v>0.005694947119773747</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003797544217947957</v>
+        <v>0.003797544217947958</v>
       </c>
     </row>
     <row r="7">
@@ -6206,85 +6206,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.004385957343647979</v>
+        <v>0.004385957343647981</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004385957343647979</v>
+        <v>0.004385957343647981</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004385957343647979</v>
+        <v>0.004385957343647981</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004385957343647979</v>
+        <v>0.004385957343647981</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004385957343647979</v>
+        <v>0.004385957343647981</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004385957343647979</v>
+        <v>0.004385957343647981</v>
       </c>
       <c r="H7" t="n">
-        <v>0.004385957343647979</v>
+        <v>0.004385957343647981</v>
       </c>
       <c r="I7" t="n">
-        <v>0.004385957343647979</v>
+        <v>0.004385957343647981</v>
       </c>
       <c r="J7" t="n">
-        <v>0.004383405057430243</v>
+        <v>0.004383405057430245</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004385957343647979</v>
+        <v>0.004385957343647981</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004385957343647979</v>
+        <v>0.004385957343647981</v>
       </c>
       <c r="M7" t="n">
-        <v>0.004385957343647979</v>
+        <v>0.004385957343647981</v>
       </c>
       <c r="N7" t="n">
-        <v>0.004385957343647979</v>
+        <v>0.004385957343647981</v>
       </c>
       <c r="O7" t="n">
-        <v>0.004385811846794564</v>
+        <v>0.004385811846794567</v>
       </c>
       <c r="P7" t="n">
-        <v>0.004385811846794564</v>
+        <v>0.004385811846794567</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.004385957343647979</v>
+        <v>0.004385957343647981</v>
       </c>
       <c r="R7" t="n">
-        <v>0.004385957343647979</v>
+        <v>0.004385957343647981</v>
       </c>
       <c r="S7" t="n">
-        <v>0.004385957343647979</v>
+        <v>0.004385957343647981</v>
       </c>
       <c r="T7" t="n">
-        <v>0.004385957343647979</v>
+        <v>0.004385957343647981</v>
       </c>
       <c r="U7" t="n">
-        <v>0.004383482849848596</v>
+        <v>0.004383482849848594</v>
       </c>
       <c r="V7" t="n">
-        <v>0.004369827341569607</v>
+        <v>0.00436982734156961</v>
       </c>
       <c r="W7" t="n">
-        <v>0.004385957343647979</v>
+        <v>0.004385957343647981</v>
       </c>
       <c r="X7" t="n">
-        <v>0.004385957343647979</v>
+        <v>0.004385957343647981</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.004385957343647979</v>
+        <v>0.004385957343647981</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.004385957343647979</v>
+        <v>0.004385957343647981</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.004385957343647979</v>
+        <v>0.004385957343647981</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.004385957343647979</v>
+        <v>0.004385957343647981</v>
       </c>
     </row>
     <row r="8">
@@ -6297,82 +6297,82 @@
         <v>0.00639738032537712</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009378413968271899</v>
+        <v>0.009378413968271892</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009378413968271899</v>
+        <v>0.009378413968271892</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009378413968271899</v>
+        <v>0.007791101489486149</v>
       </c>
       <c r="F8" t="n">
-        <v>0.006861790526321904</v>
+        <v>0.006861790526321894</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009378413968271899</v>
+        <v>0.009996550713371669</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009378413968271899</v>
+        <v>0.009378413968271892</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009378413968271899</v>
+        <v>0.009378413968271892</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009375861682054147</v>
+        <v>0.009375861682054155</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009378413968271899</v>
+        <v>0.009378413968271892</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009378413968271899</v>
+        <v>0.009378413968271892</v>
       </c>
       <c r="M8" t="n">
-        <v>0.009378413968271899</v>
+        <v>0.009378413968271587</v>
       </c>
       <c r="N8" t="n">
-        <v>0.007067614177709916</v>
+        <v>0.007067614177709913</v>
       </c>
       <c r="O8" t="n">
-        <v>0.007702642021858166</v>
+        <v>0.007702642021858161</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00754698135311466</v>
+        <v>0.007546981353114658</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.005811539177219293</v>
+        <v>0.005811539177219286</v>
       </c>
       <c r="R8" t="n">
-        <v>0.009378413968271899</v>
+        <v>0.009378413968271892</v>
       </c>
       <c r="S8" t="n">
-        <v>0.009378413968271899</v>
+        <v>0.009378413968271892</v>
       </c>
       <c r="T8" t="n">
-        <v>0.009378413968271899</v>
+        <v>0.009378413968271892</v>
       </c>
       <c r="U8" t="n">
-        <v>0.007542346290183562</v>
+        <v>0.007921606316119748</v>
       </c>
       <c r="V8" t="n">
-        <v>0.009362283966193511</v>
+        <v>0.008545531751137375</v>
       </c>
       <c r="W8" t="n">
-        <v>0.00937899982174948</v>
+        <v>0.009378999821749463</v>
       </c>
       <c r="X8" t="n">
-        <v>0.006084756830865201</v>
+        <v>0.006084756830865202</v>
       </c>
       <c r="Y8" t="n">
         <v>0.01233930017999122</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.009378413968271899</v>
+        <v>0.006342006095495234</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.009378413968271899</v>
+        <v>0.009378413968271892</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0124923528734321</v>
+        <v>0.01249235287343211</v>
       </c>
     </row>
     <row r="9">
@@ -6382,85 +6382,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008904954591105345</v>
+        <v>0.008904954591105355</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01089594153218317</v>
+        <v>0.01089594153218318</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01089594153218317</v>
+        <v>0.01089594153218318</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01089594153218317</v>
+        <v>0.01043643059744122</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01089594153218317</v>
+        <v>0.00630617200207082</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01089594153218317</v>
+        <v>0.01089594248143842</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01089594153218317</v>
+        <v>0.01089594153218318</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01089594153218317</v>
+        <v>0.01089594153218318</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01089338924596543</v>
+        <v>0.01089338924596544</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01089594153218317</v>
+        <v>0.01089594153218318</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01089594153218317</v>
+        <v>0.01089594153218318</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01089594153218317</v>
+        <v>0.01089594153218318</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01089594153218317</v>
+        <v>0.01089594153218318</v>
       </c>
       <c r="O9" t="n">
         <v>0.01155575326131856</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01169925078549602</v>
+        <v>0.01169925078549601</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01089594248143841</v>
+        <v>0.01089594248143842</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01089594153218317</v>
+        <v>0.01089594153218318</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01089594153218317</v>
+        <v>0.01089594153218318</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01089594153218317</v>
+        <v>0.01089594153218318</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01089594153218317</v>
+        <v>0.01089594153218318</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01087981153010481</v>
+        <v>0.0131773680201953</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01089594153218317</v>
+        <v>0.01089594153218318</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01089594153218317</v>
+        <v>0.01089594153218318</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01089594153218317</v>
+        <v>0.01089594153218318</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01089594153218317</v>
+        <v>0.009695553829118589</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01089594153218317</v>
+        <v>0.01089594153218318</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.01089594153218317</v>
+        <v>0.01089594153218318</v>
       </c>
     </row>
     <row r="10">
@@ -6470,16 +6470,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01459472240772348</v>
+        <v>0.01459472240772346</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01489206492216627</v>
+        <v>0.01489206492216628</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01415419661308047</v>
+        <v>0.01415419661308046</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01151044023394125</v>
+        <v>0.01151044023394126</v>
       </c>
       <c r="F10" t="n">
         <v>0.01465504312123365</v>
@@ -6488,16 +6488,16 @@
         <v>0.0140360608866442</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01394795557278665</v>
+        <v>0.01394795557278666</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01434853543871236</v>
+        <v>0.01434853543871237</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01416437646907911</v>
+        <v>0.01416437646907912</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01376315023226179</v>
+        <v>0.01376315023226178</v>
       </c>
       <c r="L10" t="n">
         <v>0.01381030501335241</v>
@@ -6506,22 +6506,22 @@
         <v>0.01400707038129905</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01395494542059774</v>
+        <v>0.01395494542059775</v>
       </c>
       <c r="O10" t="n">
         <v>0.01451018323307006</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01405939871020509</v>
+        <v>0.01405939871020508</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01434817400278548</v>
+        <v>0.01434817400278549</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0144024982407223</v>
+        <v>0.01440249824072231</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01421073125039104</v>
+        <v>0.01421073125039105</v>
       </c>
       <c r="T10" t="n">
         <v>0.01446020168297981</v>
@@ -6530,7 +6530,7 @@
         <v>0.01365624777108987</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01461702547583977</v>
+        <v>0.01461702547583976</v>
       </c>
       <c r="W10" t="n">
         <v>0.01266961110890114</v>
@@ -6545,7 +6545,7 @@
         <v>0.01431817756054433</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.01389416137183558</v>
+        <v>0.01389416137183559</v>
       </c>
       <c r="AB10" t="n">
         <v>0.01325440508083347</v>
@@ -6561,31 +6561,31 @@
         <v>0.01468298301176076</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01470960231709967</v>
+        <v>0.01470960231709968</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01448643118209115</v>
+        <v>0.01448643118209114</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01158199455742198</v>
+        <v>0.01158199455742199</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01463394973309992</v>
+        <v>0.01463394973309993</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01439849336432549</v>
+        <v>0.01439849336432551</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01438870204074089</v>
+        <v>0.01438870204074091</v>
       </c>
       <c r="I11" t="n">
         <v>0.0145709671563094</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01448454023068904</v>
+        <v>0.01448454023068905</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01430651417398656</v>
+        <v>0.01430651417398657</v>
       </c>
       <c r="L11" t="n">
         <v>0.01432607059753201</v>
@@ -6597,28 +6597,28 @@
         <v>0.01442904388361404</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01464447896979025</v>
+        <v>0.01464447896979026</v>
       </c>
       <c r="P11" t="n">
-        <v>0.01443939819142456</v>
+        <v>0.01443939819142457</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01457080215623521</v>
+        <v>0.01457080215623522</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01459587638141637</v>
+        <v>0.01459587638141638</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01450826581146728</v>
+        <v>0.01450826581146729</v>
       </c>
       <c r="T11" t="n">
         <v>0.01462175892919005</v>
       </c>
       <c r="U11" t="n">
-        <v>0.014256034743116</v>
+        <v>0.01425603474311601</v>
       </c>
       <c r="V11" t="n">
-        <v>0.01461691318359692</v>
+        <v>0.01461691318359691</v>
       </c>
       <c r="W11" t="n">
         <v>0.0138070512358309</v>
@@ -6630,7 +6630,7 @@
         <v>0.01463546260117365</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.01453200567363817</v>
+        <v>0.01453200567363819</v>
       </c>
       <c r="AA11" t="n">
         <v>0.01436422550787621</v>
@@ -6814,10 +6814,10 @@
         <v>0.01171651055769504</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01474020501818923</v>
+        <v>0.01474020501818922</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01464704290242095</v>
+        <v>0.01464704290242096</v>
       </c>
       <c r="H2" t="n">
         <v>0.01474909074313076</v>
@@ -6826,7 +6826,7 @@
         <v>0.01474909074313076</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01474727899729403</v>
+        <v>0.01474727899729404</v>
       </c>
       <c r="K2" t="n">
         <v>0.01475445588681237</v>
@@ -6838,7 +6838,7 @@
         <v>0.01471020473688112</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01475241384419704</v>
+        <v>0.01475241384419703</v>
       </c>
       <c r="O2" t="n">
         <v>0.01474900523103579</v>
@@ -6862,7 +6862,7 @@
         <v>0.01474880072302224</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01473385387105343</v>
+        <v>0.01473385387105342</v>
       </c>
       <c r="W2" t="n">
         <v>0.01474909074313076</v>
@@ -6880,7 +6880,7 @@
         <v>0.01474909074313076</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01459968239962249</v>
+        <v>0.01459968239962248</v>
       </c>
     </row>
     <row r="3">
@@ -6899,10 +6899,10 @@
         <v>0.01493515353015579</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01188122556018747</v>
+        <v>0.01188122556018748</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01494602756275625</v>
+        <v>0.01494602756275626</v>
       </c>
       <c r="G3" t="n">
         <v>0.01483672639657165</v>
@@ -6914,16 +6914,16 @@
         <v>0.01493515353015579</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01493334158090045</v>
+        <v>0.01493334158090046</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01494102457908922</v>
+        <v>0.01494102457908923</v>
       </c>
       <c r="L3" t="n">
         <v>0.01493515353015579</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01493507222531147</v>
+        <v>0.01493507222531148</v>
       </c>
       <c r="N3" t="n">
         <v>0.01493515353015579</v>
@@ -6932,7 +6932,7 @@
         <v>0.01493505995413004</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01493514168817954</v>
+        <v>0.01493514168817955</v>
       </c>
       <c r="Q3" t="n">
         <v>0.01493515234105991</v>
@@ -6944,7 +6944,7 @@
         <v>0.01493515353015579</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01493504618458197</v>
+        <v>0.01493504618458198</v>
       </c>
       <c r="U3" t="n">
         <v>0.01493483616085348</v>
@@ -6978,85 +6978,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01040045880253185</v>
+        <v>0.01040045880253183</v>
       </c>
       <c r="C4" t="n">
-        <v>0.013172819586515</v>
+        <v>0.01317281958651502</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01615291675876779</v>
+        <v>0.01615291675876778</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01548091495022847</v>
+        <v>0.01548091495022848</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01760223868915683</v>
+        <v>0.01760223868915686</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01703157356608409</v>
+        <v>0.01703157356608408</v>
       </c>
       <c r="H4" t="n">
         <v>0.03071373223940065</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02002910566211428</v>
+        <v>0.02002910566211437</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0207141204955303</v>
+        <v>0.02071412049553031</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01579627940211265</v>
+        <v>0.01579627940211266</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01499271159598997</v>
+        <v>0.01499271159598998</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0123283186189882</v>
+        <v>0.01232831861898822</v>
       </c>
       <c r="N4" t="n">
-        <v>0.00994487305000093</v>
+        <v>0.009944873050000948</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01977158740248724</v>
+        <v>0.01977158740248722</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01639147303905551</v>
+        <v>0.0163914730390555</v>
       </c>
       <c r="Q4" t="n">
         <v>0.01167193997632008</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02740225017261188</v>
+        <v>0.02740225017261186</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02070053736244219</v>
+        <v>0.0207005373624422</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01286783795647928</v>
+        <v>0.01286783795647927</v>
       </c>
       <c r="U4" t="n">
-        <v>0.009944873050000925</v>
+        <v>0.009944873050000944</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01938955071027063</v>
+        <v>0.01938955071027065</v>
       </c>
       <c r="W4" t="n">
         <v>0.06408558435316322</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06654998945965797</v>
+        <v>0.066549989459658</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02889065481256525</v>
+        <v>0.02889065481256517</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02384078984388635</v>
+        <v>0.02384078984388638</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.04534211246444456</v>
+        <v>0.04534211246444445</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.007788997315558531</v>
+        <v>0.007788997315558524</v>
       </c>
     </row>
     <row r="5">
@@ -7066,85 +7066,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002403014868902449</v>
+        <v>0.002403014868902465</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002403014868902464</v>
+        <v>0.002403014868902463</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002403014868902464</v>
+        <v>0.002403014868902463</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002403014868902464</v>
+        <v>0.002403014868902463</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002403014868902449</v>
+        <v>0.002403014868902465</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002403014868902464</v>
+        <v>0.002403014868902463</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002403014868902464</v>
+        <v>0.002403014868902463</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002403014868902464</v>
+        <v>0.002403014868902463</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002401323656415475</v>
+        <v>0.002401323656415474</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002403014868902464</v>
+        <v>0.002403014868902463</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002403014868902464</v>
+        <v>0.002403014868902463</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002403014868902464</v>
+        <v>0.002403014868902463</v>
       </c>
       <c r="N5" t="n">
-        <v>0.002403014868902449</v>
+        <v>0.002403014868902465</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002403014868902449</v>
+        <v>0.002403014868902465</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002403014868902449</v>
+        <v>0.002403014868902465</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002403014868902449</v>
+        <v>0.002403014868902465</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002403014868902464</v>
+        <v>0.002403014868902463</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002403014868902464</v>
+        <v>0.002403014868902463</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002403014868902464</v>
+        <v>0.002403014868902463</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002387552574113855</v>
+        <v>0.002387552574113858</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002392416527991427</v>
+        <v>0.002392416527991433</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002403014868902449</v>
+        <v>0.002403014868902465</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002403014868902449</v>
+        <v>0.002403014868902465</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.002387552574113855</v>
+        <v>0.002387552574113858</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002403014868902464</v>
+        <v>0.002403014868902463</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002403014868902464</v>
+        <v>0.002403014868902463</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.002403014868902449</v>
+        <v>0.002403014868902465</v>
       </c>
     </row>
     <row r="6">
@@ -7154,85 +7154,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.003525639605160005</v>
+        <v>0.003525639605159996</v>
       </c>
       <c r="C6" t="n">
-        <v>0.005239422259253749</v>
+        <v>0.003525639605159996</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003525639605160005</v>
+        <v>0.003525639605159996</v>
       </c>
       <c r="E6" t="n">
-        <v>0.005239422259253749</v>
+        <v>0.005239422259253742</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005239422259253749</v>
+        <v>0.005239422259253742</v>
       </c>
       <c r="G6" t="n">
-        <v>0.005239422259253749</v>
+        <v>0.003525639605159996</v>
       </c>
       <c r="H6" t="n">
-        <v>0.005239422259253749</v>
+        <v>0.003525639605159996</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003525639605160005</v>
+        <v>0.003525639605159996</v>
       </c>
       <c r="J6" t="n">
-        <v>0.005237731046766771</v>
+        <v>0.003523948392673013</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003525639605160005</v>
+        <v>0.003525639605159996</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005239422259253749</v>
+        <v>0.005239422259253742</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003525639605160005</v>
+        <v>0.005239422259253742</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003526883548151163</v>
+        <v>0.003526883548151142</v>
       </c>
       <c r="O6" t="n">
-        <v>0.003526883548151163</v>
+        <v>0.003526883548151156</v>
       </c>
       <c r="P6" t="n">
-        <v>0.005255887835758814</v>
+        <v>0.003413860855692473</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.005239422259253749</v>
+        <v>0.003525639605159996</v>
       </c>
       <c r="R6" t="n">
-        <v>0.005239422259253749</v>
+        <v>0.005239422259253742</v>
       </c>
       <c r="S6" t="n">
-        <v>0.005239422259253749</v>
+        <v>0.003525639605159996</v>
       </c>
       <c r="T6" t="n">
-        <v>0.005239422259253749</v>
+        <v>0.005239422259253742</v>
       </c>
       <c r="U6" t="n">
-        <v>0.003525639605160005</v>
+        <v>0.003525639605159996</v>
       </c>
       <c r="V6" t="n">
-        <v>0.003515041264248968</v>
+        <v>0.005228823918342718</v>
       </c>
       <c r="W6" t="n">
-        <v>0.003642171555549537</v>
+        <v>0.003642171555549495</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003525639605160005</v>
+        <v>0.003525639605159996</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.003612356024890065</v>
+        <v>0.003612356024890059</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.005239422259253749</v>
+        <v>0.005239422259253742</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003525639605160005</v>
+        <v>0.005239422259253742</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003522948043049522</v>
+        <v>0.003522948043049534</v>
       </c>
     </row>
     <row r="7">
@@ -7242,85 +7242,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.003891919624408889</v>
+        <v>0.003891919624408878</v>
       </c>
       <c r="C7" t="n">
-        <v>0.003891919624408889</v>
+        <v>0.003891919624408878</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003891919624408889</v>
+        <v>0.003891919624408878</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003891919624408889</v>
+        <v>0.003891919624408878</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003891919624408889</v>
+        <v>0.003891919624408878</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003891919624408889</v>
+        <v>0.003891919624408878</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003891919624408889</v>
+        <v>0.003891919624408878</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003891919624408889</v>
+        <v>0.003891919624408878</v>
       </c>
       <c r="J7" t="n">
-        <v>0.003890228411921887</v>
+        <v>0.003890228411921888</v>
       </c>
       <c r="K7" t="n">
-        <v>0.003891919624408889</v>
+        <v>0.003891919624408878</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003891919624408889</v>
+        <v>0.003891919624408878</v>
       </c>
       <c r="M7" t="n">
-        <v>0.003891919624408889</v>
+        <v>0.003891919624408878</v>
       </c>
       <c r="N7" t="n">
-        <v>0.003891919624408889</v>
+        <v>0.003891919624408878</v>
       </c>
       <c r="O7" t="n">
-        <v>0.003891784536525012</v>
+        <v>0.003891784536525006</v>
       </c>
       <c r="P7" t="n">
-        <v>0.003891784536525012</v>
+        <v>0.003891784536525006</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.003891919624408889</v>
+        <v>0.003891919624408878</v>
       </c>
       <c r="R7" t="n">
-        <v>0.003891919624408889</v>
+        <v>0.003891919624408878</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003891919624408889</v>
+        <v>0.003891919624408878</v>
       </c>
       <c r="T7" t="n">
-        <v>0.003891919624408889</v>
+        <v>0.003891919624408878</v>
       </c>
       <c r="U7" t="n">
-        <v>0.003889734110821845</v>
+        <v>0.003889734110821838</v>
       </c>
       <c r="V7" t="n">
-        <v>0.00388132128349785</v>
+        <v>0.003881321283497848</v>
       </c>
       <c r="W7" t="n">
-        <v>0.003891919624408889</v>
+        <v>0.003891919624408878</v>
       </c>
       <c r="X7" t="n">
-        <v>0.003891919624408889</v>
+        <v>0.003891919624408878</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.003891919624408889</v>
+        <v>0.003891919624408878</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.003891919624408889</v>
+        <v>0.003891919624408878</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.003891919624408889</v>
+        <v>0.003891919624408878</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.003891919624408889</v>
+        <v>0.003891919624408878</v>
       </c>
     </row>
     <row r="8">
@@ -7330,85 +7330,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.005683683235696247</v>
+        <v>0.005683683235696244</v>
       </c>
       <c r="C8" t="n">
-        <v>0.008309227629730994</v>
+        <v>0.008309227629730982</v>
       </c>
       <c r="D8" t="n">
-        <v>0.008309227629730994</v>
+        <v>0.008309227629730982</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008309227629730994</v>
+        <v>0.006911202689609207</v>
       </c>
       <c r="F8" t="n">
-        <v>0.006092712366400543</v>
+        <v>0.006092712366400536</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008309227629730994</v>
+        <v>0.008853651363310892</v>
       </c>
       <c r="H8" t="n">
-        <v>0.008309227629730994</v>
+        <v>0.008309227629730982</v>
       </c>
       <c r="I8" t="n">
-        <v>0.008309227629730994</v>
+        <v>0.008309227629730982</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008307536417244002</v>
+        <v>0.008307536417244004</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008309227629730994</v>
+        <v>0.008309227629730982</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008309227629730994</v>
+        <v>0.008309227629730982</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008309227629730994</v>
+        <v>0.008309227629730506</v>
       </c>
       <c r="N8" t="n">
-        <v>0.006273991479184907</v>
+        <v>0.006273991479184901</v>
       </c>
       <c r="O8" t="n">
-        <v>0.006833292042571625</v>
+        <v>0.006833292042571622</v>
       </c>
       <c r="P8" t="n">
-        <v>0.006696193960149739</v>
+        <v>0.00669619396014974</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.005167703838481507</v>
+        <v>0.005167703838481498</v>
       </c>
       <c r="R8" t="n">
-        <v>0.008309227629730994</v>
+        <v>0.008309227629730982</v>
       </c>
       <c r="S8" t="n">
-        <v>0.008309227629730994</v>
+        <v>0.008309227629730982</v>
       </c>
       <c r="T8" t="n">
-        <v>0.008309227629730994</v>
+        <v>0.008309227629730982</v>
       </c>
       <c r="U8" t="n">
-        <v>0.006692112239579067</v>
+        <v>0.007026145421382243</v>
       </c>
       <c r="V8" t="n">
-        <v>0.008298629288819952</v>
+        <v>0.00757927576162737</v>
       </c>
       <c r="W8" t="n">
-        <v>0.008309743619757955</v>
+        <v>0.008309743619757951</v>
       </c>
       <c r="X8" t="n">
-        <v>0.005408340196331346</v>
+        <v>0.005408340196331354</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01091702829079481</v>
+        <v>0.01091702829079482</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.008309227629730994</v>
+        <v>0.005634912401085171</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.008309227629730994</v>
+        <v>0.008309227629730982</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0110518282892823</v>
+        <v>0.01105182828928227</v>
       </c>
     </row>
     <row r="9">
@@ -7418,85 +7418,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.007452779624306848</v>
+        <v>0.007452779624306838</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009084808677496536</v>
+        <v>0.009084808677496514</v>
       </c>
       <c r="D9" t="n">
-        <v>0.009084808677496536</v>
+        <v>0.009084808677496514</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009084808677496536</v>
+        <v>0.008708143852824091</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009084808677496536</v>
+        <v>0.005322534888855241</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009084808677496536</v>
+        <v>0.009084809748575746</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009084808677496536</v>
+        <v>0.009084808677496514</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009084808677496536</v>
+        <v>0.009084808677496514</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009083117465009539</v>
+        <v>0.009083117465009519</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009084808677496536</v>
+        <v>0.009084808677496514</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009084808677496536</v>
+        <v>0.009084808677496514</v>
       </c>
       <c r="M9" t="n">
-        <v>0.009084808677496536</v>
+        <v>0.009084808677496514</v>
       </c>
       <c r="N9" t="n">
-        <v>0.009084808677496536</v>
+        <v>0.009084808677496514</v>
       </c>
       <c r="O9" t="n">
-        <v>0.009625662394797353</v>
+        <v>0.009625662394797341</v>
       </c>
       <c r="P9" t="n">
-        <v>0.009743288565881903</v>
+        <v>0.009743288565881889</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.009084809748575761</v>
+        <v>0.009084809748575746</v>
       </c>
       <c r="R9" t="n">
-        <v>0.009084808677496536</v>
+        <v>0.009084808677496514</v>
       </c>
       <c r="S9" t="n">
-        <v>0.009084808677496536</v>
+        <v>0.009084808677496514</v>
       </c>
       <c r="T9" t="n">
-        <v>0.009084808677496536</v>
+        <v>0.009084808677496514</v>
       </c>
       <c r="U9" t="n">
-        <v>0.009084808677496536</v>
+        <v>0.009084808677496514</v>
       </c>
       <c r="V9" t="n">
-        <v>0.009074210336585491</v>
+        <v>0.01095753788710732</v>
       </c>
       <c r="W9" t="n">
-        <v>0.009084808677496536</v>
+        <v>0.009084808677496514</v>
       </c>
       <c r="X9" t="n">
-        <v>0.009084808677496536</v>
+        <v>0.009084808677496514</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.009084808677496536</v>
+        <v>0.009084808677496514</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.009084808677496536</v>
+        <v>0.008100840709422628</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.009084808677496536</v>
+        <v>0.009084808677496514</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.009084808677496536</v>
+        <v>0.009084808677496514</v>
       </c>
     </row>
     <row r="10">
@@ -7527,10 +7527,10 @@
         <v>0.01433379121237218</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01454591627666605</v>
+        <v>0.01454591627666607</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01447854939133543</v>
+        <v>0.01447854939133544</v>
       </c>
       <c r="K10" t="n">
         <v>0.01462601123021893</v>
@@ -7539,46 +7539,46 @@
         <v>0.01460506118752619</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01471275598348732</v>
+        <v>0.01471275598348733</v>
       </c>
       <c r="N10" t="n">
         <v>0.01446317937866731</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01448602181511996</v>
+        <v>0.01448602181511997</v>
       </c>
       <c r="P10" t="n">
         <v>0.01458583028488735</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0147130039200808</v>
+        <v>0.01471300392008079</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01436802582084708</v>
+        <v>0.01436802582084707</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0144410840462444</v>
+        <v>0.01444108404624441</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01470326537998953</v>
+        <v>0.01470326537998954</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01475729683370966</v>
+        <v>0.01475729683370965</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01448623446867599</v>
+        <v>0.01448623446867597</v>
       </c>
       <c r="W10" t="n">
-        <v>0.01341551265410155</v>
+        <v>0.01341551265410154</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01325713300459926</v>
+        <v>0.01325713300459927</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.01432565266504097</v>
+        <v>0.01432565266504098</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01437564303519049</v>
+        <v>0.0143756430351905</v>
       </c>
       <c r="AA10" t="n">
         <v>0.01393960356465717</v>
@@ -7600,28 +7600,28 @@
         <v>0.01462409653611841</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01458362019224907</v>
+        <v>0.01458362019224909</v>
       </c>
       <c r="E11" t="n">
         <v>0.01157893539632964</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01458614711777138</v>
+        <v>0.01458614711777137</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01447169537513228</v>
+        <v>0.01447169537513229</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01447546897211123</v>
+        <v>0.01447546897211122</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01457198655236739</v>
+        <v>0.0145719865523674</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01454034710170524</v>
+        <v>0.01454034710170522</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01461112380918841</v>
+        <v>0.0146111238091884</v>
       </c>
       <c r="L11" t="n">
         <v>0.01459889767529241</v>
@@ -7639,25 +7639,25 @@
         <v>0.01459014211990746</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01464801141702224</v>
+        <v>0.01464801141702223</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0144808160207266</v>
+        <v>0.01448081602072661</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01452428755344506</v>
+        <v>0.01452428755344507</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01464353164335389</v>
+        <v>0.01464353164335388</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01466801976338752</v>
+        <v>0.01466801976338753</v>
       </c>
       <c r="V11" t="n">
-        <v>0.01453498756529342</v>
+        <v>0.01453498756529341</v>
       </c>
       <c r="W11" t="n">
-        <v>0.01405764930171796</v>
+        <v>0.01405764930171795</v>
       </c>
       <c r="X11" t="n">
         <v>0.01392396156208608</v>
@@ -7669,7 +7669,7 @@
         <v>0.01451275039020538</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0142961123361994</v>
+        <v>0.01429611233619939</v>
       </c>
       <c r="AB11" t="n">
         <v>0.01455104135501457</v>
@@ -7838,40 +7838,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01474884421267951</v>
+        <v>0.0147488442126795</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01474233235223519</v>
+        <v>0.01474233235223518</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01473661943735325</v>
+        <v>0.01473661943735323</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01185051034554304</v>
+        <v>0.01185051034554302</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01474752580840771</v>
+        <v>0.0147475258084077</v>
       </c>
       <c r="G2" t="n">
         <v>0.01457393880927764</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01474884421267951</v>
+        <v>0.0147488442126795</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01474884421267951</v>
+        <v>0.0147488442126795</v>
       </c>
       <c r="J2" t="n">
         <v>0.01474829313028387</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01475572209760003</v>
+        <v>0.01475572209760002</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01474884421267951</v>
+        <v>0.0147488442126795</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01472219733504469</v>
+        <v>0.01472219733504468</v>
       </c>
       <c r="N2" t="n">
         <v>0.01474093493137188</v>
@@ -7886,22 +7886,22 @@
         <v>0.01474884312606148</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01470956859698531</v>
+        <v>0.0147095685969853</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01474884421267951</v>
+        <v>0.0147488442126795</v>
       </c>
       <c r="T2" t="n">
         <v>0.01474870333667415</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01474871759884527</v>
+        <v>0.01474871759884526</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01464977371809696</v>
+        <v>0.01464977371809692</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01474884421267951</v>
+        <v>0.0147488442126795</v>
       </c>
       <c r="X2" t="n">
         <v>0.01469257590510537</v>
@@ -7910,10 +7910,10 @@
         <v>0.01474847342214503</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01475531211573181</v>
+        <v>0.01475531211573179</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01474884421267951</v>
+        <v>0.0147488442126795</v>
       </c>
       <c r="AB2" t="n">
         <v>0.01459943586917123</v>
@@ -7926,85 +7926,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0149421379579226</v>
+        <v>0.01494213795792263</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0149644563158729</v>
+        <v>0.01496445631587292</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0149421379579226</v>
+        <v>0.01494213795792263</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01199819820935884</v>
+        <v>0.01199819820935883</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01495656984852769</v>
+        <v>0.01495656984852771</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01477338687995258</v>
+        <v>0.0147733868799526</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0149421379579226</v>
+        <v>0.01494213795792263</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0149421379579226</v>
+        <v>0.01494213795792263</v>
       </c>
       <c r="J3" t="n">
         <v>0.01494158681633228</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01494966440828814</v>
+        <v>0.01494966440828816</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0149421379579226</v>
+        <v>0.01494213795792263</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01494192722299346</v>
+        <v>0.01494192722299348</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0149421379579226</v>
+        <v>0.01494213795792263</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01494203090813464</v>
+        <v>0.01494203090813466</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01494155410189101</v>
+        <v>0.01494155410189103</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01494213676882672</v>
+        <v>0.01494213676882674</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01489915859525594</v>
+        <v>0.01489915859525596</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0149421379579226</v>
+        <v>0.01494213795792263</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01494198379716403</v>
+        <v>0.01494198379716405</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0149419994043437</v>
+        <v>0.01494199940434372</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01482335602278588</v>
+        <v>0.01482335602278585</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0149421379579226</v>
+        <v>0.01494213795792263</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01488056345828829</v>
+        <v>0.01488056345828831</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01494173220143986</v>
+        <v>0.01494173220143988</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01494371110422935</v>
+        <v>0.01494371110422937</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0149421379579226</v>
+        <v>0.01494213795792263</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0147786402393525</v>
+        <v>0.01477864023935252</v>
       </c>
     </row>
     <row r="4">
@@ -8014,55 +8014,55 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01391948222798902</v>
+        <v>0.01391948222798903</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01339583896720903</v>
+        <v>0.01339583896720904</v>
       </c>
       <c r="D4" t="n">
         <v>0.01714360165850092</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01914072290871519</v>
+        <v>0.01914072290871517</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01691158796017466</v>
+        <v>0.01691158796017471</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0138178365179016</v>
+        <v>0.01381783651790152</v>
       </c>
       <c r="H4" t="n">
         <v>0.02313848638353905</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0159384694218771</v>
+        <v>0.01593846942187709</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01921751394557413</v>
+        <v>0.0192175139455741</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01326796594718795</v>
+        <v>0.01326796594718792</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01652058374239866</v>
+        <v>0.01652058374239867</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01365890428546847</v>
+        <v>0.01365890428546846</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01194054715834053</v>
+        <v>0.01194054715834051</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02078170718071135</v>
+        <v>0.02078170718071138</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01785498002886347</v>
+        <v>0.01785498002886346</v>
       </c>
       <c r="Q4" t="n">
         <v>0.01176098564290754</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02983125908553113</v>
+        <v>0.02983125908553112</v>
       </c>
       <c r="S4" t="n">
         <v>0.01924438062257642</v>
@@ -8071,25 +8071,25 @@
         <v>0.01314789413538284</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01194054715834052</v>
+        <v>0.01194054715834051</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02266797676832045</v>
+        <v>0.02266797676832048</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05439678192909204</v>
+        <v>0.05439678192909203</v>
       </c>
       <c r="X4" t="n">
-        <v>0.07995840215004935</v>
+        <v>0.07995840215004912</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02686560451463689</v>
+        <v>0.02686560451463695</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01900556308559446</v>
+        <v>0.01900556308559447</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.04912694340589089</v>
+        <v>0.04912694340589085</v>
       </c>
       <c r="AB4" t="n">
         <v>0.01149651931713884</v>
@@ -8102,85 +8102,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002567426996191064</v>
+        <v>0.002567426996191073</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002567426996191063</v>
+        <v>0.002567426996191073</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002567426996191063</v>
+        <v>0.002567426996191073</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002567426996191063</v>
+        <v>0.002567426996191073</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002567426996191064</v>
+        <v>0.002567426996191073</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002567426996191063</v>
+        <v>0.002567426996191073</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002567426996191063</v>
+        <v>0.002567426996191073</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002567426996191063</v>
+        <v>0.002567426996191073</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002565919448661285</v>
+        <v>0.002565919448661283</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002567426996191063</v>
+        <v>0.002567426996191073</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002567426996191063</v>
+        <v>0.002567426996191073</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002567426996191063</v>
+        <v>0.002567426996191073</v>
       </c>
       <c r="N5" t="n">
-        <v>0.002567426996191064</v>
+        <v>0.002567426996191073</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002567426996191064</v>
+        <v>0.002567426996191073</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002567426996191064</v>
+        <v>0.002567426996191073</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002567426996191064</v>
+        <v>0.002567426996191073</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002567426996191063</v>
+        <v>0.002567426996191073</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002567426996191063</v>
+        <v>0.002567426996191073</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002567426996191063</v>
+        <v>0.002567426996191073</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0025656570156432</v>
+        <v>0.002565657015643204</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002557992813312053</v>
+        <v>0.002557992813312057</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002567426996191064</v>
+        <v>0.002567426996191073</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002567426996191064</v>
+        <v>0.002567426996191073</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0025656570156432</v>
+        <v>0.002565657015643204</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002567426996191063</v>
+        <v>0.002567426996191073</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002567426996191063</v>
+        <v>0.002567426996191073</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.002567426996191064</v>
+        <v>0.002567426996191073</v>
       </c>
     </row>
     <row r="6">
@@ -8190,85 +8190,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00570532431129296</v>
+        <v>0.005705324311292954</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00570532431129296</v>
+        <v>0.005705324311292954</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00570532431129296</v>
+        <v>0.005705324311292954</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00570532431129296</v>
+        <v>0.005705324311292954</v>
       </c>
       <c r="F6" t="n">
-        <v>0.003878984531808926</v>
+        <v>0.005705324311292954</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003878984531808926</v>
+        <v>0.005705324311292954</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003878984531808926</v>
+        <v>0.003878984531808924</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00570532431129296</v>
+        <v>0.003878984531808924</v>
       </c>
       <c r="J6" t="n">
-        <v>0.005703816763763186</v>
+        <v>0.003877476984279143</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003878984531808926</v>
+        <v>0.005705324311292954</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00570532431129296</v>
+        <v>0.005705324311292954</v>
       </c>
       <c r="M6" t="n">
-        <v>0.00570532431129296</v>
+        <v>0.005705324311292954</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003879110267300897</v>
+        <v>0.003879110267300884</v>
       </c>
       <c r="O6" t="n">
-        <v>0.003879110267300871</v>
+        <v>0.005712874079824554</v>
       </c>
       <c r="P6" t="n">
-        <v>0.005712856266639144</v>
+        <v>0.005712856266639147</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.00570532431129296</v>
+        <v>0.005705324311292954</v>
       </c>
       <c r="R6" t="n">
-        <v>0.00570532431129296</v>
+        <v>0.003878984531808924</v>
       </c>
       <c r="S6" t="n">
-        <v>0.003878984531808926</v>
+        <v>0.003878984531808924</v>
       </c>
       <c r="T6" t="n">
-        <v>0.00570532431129296</v>
+        <v>0.005705324311292954</v>
       </c>
       <c r="U6" t="n">
-        <v>0.00570532431129296</v>
+        <v>0.005705324311292954</v>
       </c>
       <c r="V6" t="n">
-        <v>0.003869550348929915</v>
+        <v>0.003869550348929913</v>
       </c>
       <c r="W6" t="n">
-        <v>0.005712892762697672</v>
+        <v>0.005712892762697665</v>
       </c>
       <c r="X6" t="n">
-        <v>0.00570532431129296</v>
+        <v>0.003878984531808924</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.003979571905102538</v>
+        <v>0.003979571905102533</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.00570532431129296</v>
+        <v>0.003878984531808924</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.00570532431129296</v>
+        <v>0.003878984531808924</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003875923966302088</v>
+        <v>0.003875923966302085</v>
       </c>
     </row>
     <row r="7">
@@ -8278,85 +8278,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.003942657221177421</v>
+        <v>0.003942657221177417</v>
       </c>
       <c r="C7" t="n">
-        <v>0.003942657221177421</v>
+        <v>0.003942657221177417</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003942657221177421</v>
+        <v>0.003942657221177417</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003942657221177421</v>
+        <v>0.003942657221177417</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003942657221177421</v>
+        <v>0.003942657221177417</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003942657221177421</v>
+        <v>0.003942657221177417</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003942657221177421</v>
+        <v>0.003942657221177417</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003942657221177421</v>
+        <v>0.003942657221177417</v>
       </c>
       <c r="J7" t="n">
-        <v>0.003941149673647643</v>
+        <v>0.003941149673647639</v>
       </c>
       <c r="K7" t="n">
-        <v>0.003942657221177421</v>
+        <v>0.003942657221177417</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003942657221177421</v>
+        <v>0.003942657221177417</v>
       </c>
       <c r="M7" t="n">
-        <v>0.003942657221177421</v>
+        <v>0.003942657221177417</v>
       </c>
       <c r="N7" t="n">
-        <v>0.003942657221177421</v>
+        <v>0.003942657221177417</v>
       </c>
       <c r="O7" t="n">
-        <v>0.003942519554800205</v>
+        <v>0.003942519554800203</v>
       </c>
       <c r="P7" t="n">
-        <v>0.003942519554800205</v>
+        <v>0.003942519554800201</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.003942657221177421</v>
+        <v>0.003942657221177417</v>
       </c>
       <c r="R7" t="n">
-        <v>0.003942657221177421</v>
+        <v>0.003942657221177417</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003942657221177421</v>
+        <v>0.003942657221177417</v>
       </c>
       <c r="T7" t="n">
-        <v>0.003942657221177421</v>
+        <v>0.003942657221177417</v>
       </c>
       <c r="U7" t="n">
-        <v>0.003940680381759091</v>
+        <v>0.003940680381759089</v>
       </c>
       <c r="V7" t="n">
-        <v>0.003933223038298411</v>
+        <v>0.003933223038298408</v>
       </c>
       <c r="W7" t="n">
-        <v>0.003942657221177421</v>
+        <v>0.003942657221177417</v>
       </c>
       <c r="X7" t="n">
-        <v>0.003942657221177421</v>
+        <v>0.003942657221177417</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.003942657221177421</v>
+        <v>0.003942657221177417</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.003942657221177421</v>
+        <v>0.003942657221177417</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.003942657221177421</v>
+        <v>0.003942657221177417</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.003942657221177421</v>
+        <v>0.003942657221177417</v>
       </c>
     </row>
     <row r="8">
@@ -8366,40 +8366,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.005846807209462404</v>
+        <v>0.005846807209462398</v>
       </c>
       <c r="C8" t="n">
-        <v>0.008555400806867825</v>
+        <v>0.008555400806867812</v>
       </c>
       <c r="D8" t="n">
-        <v>0.008555400806867825</v>
+        <v>0.008555400806867812</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008555400806867825</v>
+        <v>0.007113154615741161</v>
       </c>
       <c r="F8" t="n">
-        <v>0.006268774435437313</v>
+        <v>0.006268774435437315</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008555400806867825</v>
+        <v>0.009117045333785214</v>
       </c>
       <c r="H8" t="n">
-        <v>0.008555400806867825</v>
+        <v>0.008555400806867812</v>
       </c>
       <c r="I8" t="n">
-        <v>0.008555400806867825</v>
+        <v>0.008555400806867812</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008553893259338051</v>
+        <v>0.008553893259338035</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008555400806867825</v>
+        <v>0.008555400806867812</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008555400806867825</v>
+        <v>0.008555400806867812</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008555400806867825</v>
+        <v>0.008555400806867291</v>
       </c>
       <c r="N8" t="n">
         <v>0.006455787629887523</v>
@@ -8408,43 +8408,43 @@
         <v>0.007032779559133001</v>
       </c>
       <c r="P8" t="n">
-        <v>0.006891344895453747</v>
+        <v>0.006891344895453726</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.005314506748267504</v>
+        <v>0.005314506748267494</v>
       </c>
       <c r="R8" t="n">
-        <v>0.008555400806867825</v>
+        <v>0.008555400806867812</v>
       </c>
       <c r="S8" t="n">
-        <v>0.008555400806867825</v>
+        <v>0.008555400806867812</v>
       </c>
       <c r="T8" t="n">
-        <v>0.008555400806867825</v>
+        <v>0.008555400806867812</v>
       </c>
       <c r="U8" t="n">
-        <v>0.006887334987773597</v>
+        <v>0.007231947106445984</v>
       </c>
       <c r="V8" t="n">
-        <v>0.008545966623988819</v>
+        <v>0.007804095070849963</v>
       </c>
       <c r="W8" t="n">
-        <v>0.008555933118476668</v>
+        <v>0.008555933118476647</v>
       </c>
       <c r="X8" t="n">
-        <v>0.005562754730649265</v>
+        <v>0.005562754730649253</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01124605547033992</v>
+        <v>0.01124605547033988</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.008555400806867825</v>
+        <v>0.005796493693255723</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.008555400806867825</v>
+        <v>0.008555400806867812</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01138475330383738</v>
+        <v>0.01138475330383736</v>
       </c>
     </row>
     <row r="9">
@@ -8454,85 +8454,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.007172098407443843</v>
+        <v>0.007172098407443841</v>
       </c>
       <c r="C9" t="n">
-        <v>0.008717538416678893</v>
+        <v>0.008717538416678897</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008717538416678893</v>
+        <v>0.008717538416678897</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008717538416678893</v>
+        <v>0.008360857933710457</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008717538416678893</v>
+        <v>0.005154876102536806</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008717538416678893</v>
+        <v>0.00871753941436997</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008717538416678893</v>
+        <v>0.008717538416678897</v>
       </c>
       <c r="I9" t="n">
-        <v>0.008717538416678893</v>
+        <v>0.008717538416678897</v>
       </c>
       <c r="J9" t="n">
-        <v>0.008716030869149126</v>
+        <v>0.00871603086914912</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008717538416678893</v>
+        <v>0.008717538416678897</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008717538416678893</v>
+        <v>0.008717538416678897</v>
       </c>
       <c r="M9" t="n">
-        <v>0.008717538416678893</v>
+        <v>0.008717538416678897</v>
       </c>
       <c r="N9" t="n">
-        <v>0.008717538416678893</v>
+        <v>0.008717538416678897</v>
       </c>
       <c r="O9" t="n">
-        <v>0.009229696540482977</v>
+        <v>0.009229696540482986</v>
       </c>
       <c r="P9" t="n">
-        <v>0.009341081928276106</v>
+        <v>0.009341081928276103</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.008717539414369972</v>
+        <v>0.00871753941436997</v>
       </c>
       <c r="R9" t="n">
-        <v>0.008717538416678893</v>
+        <v>0.008717538416678897</v>
       </c>
       <c r="S9" t="n">
-        <v>0.008717538416678893</v>
+        <v>0.008717538416678897</v>
       </c>
       <c r="T9" t="n">
-        <v>0.008717538416678893</v>
+        <v>0.008717538416678897</v>
       </c>
       <c r="U9" t="n">
-        <v>0.008717538416678893</v>
+        <v>0.008717538416678897</v>
       </c>
       <c r="V9" t="n">
-        <v>0.008708104233799892</v>
+        <v>0.01049150978159705</v>
       </c>
       <c r="W9" t="n">
-        <v>0.008717538416678893</v>
+        <v>0.008717538416678897</v>
       </c>
       <c r="X9" t="n">
-        <v>0.008717538416678893</v>
+        <v>0.008717538416678897</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.008717538416678893</v>
+        <v>0.008717538416678897</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.008717538416678893</v>
+        <v>0.007785775913169815</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.008717538416678893</v>
+        <v>0.008717538416678897</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.008717538416678893</v>
+        <v>0.008717538416678897</v>
       </c>
     </row>
     <row r="10">
@@ -8545,16 +8545,16 @@
         <v>0.01465885717801043</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01472032485634424</v>
+        <v>0.01472032485634423</v>
       </c>
       <c r="D10" t="n">
         <v>0.01461229035754453</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0115917170174101</v>
+        <v>0.01159171701741008</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01464164338724426</v>
+        <v>0.01464164338724427</v>
       </c>
       <c r="G10" t="n">
         <v>0.01448890429509207</v>
@@ -8566,34 +8566,34 @@
         <v>0.01464941955023072</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01453681665258399</v>
+        <v>0.014536816652584</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01470545549659492</v>
+        <v>0.01470545549659491</v>
       </c>
       <c r="L10" t="n">
         <v>0.01458400976350886</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0146963730185836</v>
+        <v>0.01469637301858361</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01458550090521165</v>
+        <v>0.01458550090521166</v>
       </c>
       <c r="O10" t="n">
         <v>0.0144689696295836</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01454784949948703</v>
+        <v>0.01454784949948704</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0147273693409158</v>
+        <v>0.01472736934091579</v>
       </c>
       <c r="R10" t="n">
         <v>0.01430732636115357</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01451382971183537</v>
+        <v>0.01451382971183536</v>
       </c>
       <c r="T10" t="n">
         <v>0.01470838375298172</v>
@@ -8602,19 +8602,19 @@
         <v>0.01471245417023033</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01430875757177045</v>
+        <v>0.01430875757177044</v>
       </c>
       <c r="W10" t="n">
         <v>0.01368875645871192</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01298275792958526</v>
+        <v>0.01298275792958527</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.01438669126096864</v>
+        <v>0.01438669126096865</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01450650347281459</v>
+        <v>0.0145065034728146</v>
       </c>
       <c r="AA10" t="n">
         <v>0.01386325576118714</v>
@@ -8630,25 +8630,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01461995055505719</v>
+        <v>0.01461995055505718</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01463125176014884</v>
+        <v>0.01463125176014883</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01458653772801929</v>
+        <v>0.01458653772801928</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01166556010782767</v>
+        <v>0.01166556010782765</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01460423326491267</v>
+        <v>0.01460423326491266</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01444449832657391</v>
+        <v>0.0144444983265739</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01454879728037975</v>
+        <v>0.01454879728037974</v>
       </c>
       <c r="I11" t="n">
         <v>0.01461565640434147</v>
@@ -8657,58 +8657,58 @@
         <v>0.01456412141585243</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01464460626453199</v>
+        <v>0.01464460626453198</v>
       </c>
       <c r="L11" t="n">
         <v>0.01458589474293442</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01461046938950339</v>
+        <v>0.01461046938950338</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01457866393585354</v>
+        <v>0.01457866393585353</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01453350199858527</v>
+        <v>0.01453350199858526</v>
       </c>
       <c r="P11" t="n">
         <v>0.01456917382140029</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01465112326193882</v>
+        <v>0.01465112326193881</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01444028304441131</v>
+        <v>0.0144402830444113</v>
       </c>
       <c r="S11" t="n">
         <v>0.01455396259577241</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01464241457213203</v>
+        <v>0.01464241457213202</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01464427378580642</v>
+        <v>0.0146442737858064</v>
       </c>
       <c r="V11" t="n">
-        <v>0.01441562978295699</v>
+        <v>0.01441562978295695</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0141785516362488</v>
+        <v>0.01417855163624879</v>
       </c>
       <c r="X11" t="n">
         <v>0.01382906834159813</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0144959280254201</v>
+        <v>0.01449592802542009</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.01455638125014004</v>
+        <v>0.01455638125014002</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0142579493749713</v>
+        <v>0.01425794937497129</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.01451450731835451</v>
+        <v>0.0145145073183545</v>
       </c>
     </row>
   </sheetData>
@@ -8874,10 +8874,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01525125548001049</v>
+        <v>0.01525125548001048</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01499627986911876</v>
+        <v>0.01499627986911875</v>
       </c>
       <c r="D2" t="n">
         <v>0.01514655600655794</v>
@@ -8889,28 +8889,28 @@
         <v>0.01505472707086618</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01532316406255578</v>
+        <v>0.01532316406255577</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01525125548001049</v>
+        <v>0.01525125548001048</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01525125548001049</v>
+        <v>0.01525125548001048</v>
       </c>
       <c r="J2" t="n">
         <v>0.01523901183559104</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01525503794076082</v>
+        <v>0.01525503794076081</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01525125548001049</v>
+        <v>0.01525125548001048</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01537855097346025</v>
+        <v>0.01537855097346023</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01525296095530717</v>
+        <v>0.01525296095530716</v>
       </c>
       <c r="O2" t="n">
         <v>0.01525117890380829</v>
@@ -8919,40 +8919,40 @@
         <v>0.01525123390629917</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01525125439339246</v>
+        <v>0.01525125439339245</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01525196444368863</v>
+        <v>0.01525196444368862</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01525125548001049</v>
+        <v>0.01525125548001048</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0152512221709223</v>
+        <v>0.01525122217092229</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01525137633854551</v>
+        <v>0.0152513763385455</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01502623040350629</v>
+        <v>0.01502623040350628</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01525125548001049</v>
+        <v>0.01525125548001048</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01524097293435779</v>
+        <v>0.01524097293435778</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01525107965409543</v>
+        <v>0.01525107965409542</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01511787529966566</v>
+        <v>0.01511787529966565</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01525125548001049</v>
+        <v>0.01525125548001048</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01510184713650221</v>
+        <v>0.0151018471365022</v>
       </c>
     </row>
     <row r="3">
@@ -8962,58 +8962,58 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0151977815291559</v>
+        <v>0.01519778152915589</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01521911630409851</v>
+        <v>0.0152191163040985</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0151977815291559</v>
+        <v>0.01519778152915589</v>
       </c>
       <c r="E3" t="n">
         <v>0.01203110231707745</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01520548637577857</v>
+        <v>0.01520548637577856</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01511494778491103</v>
+        <v>0.01511494778491102</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0151977815291559</v>
+        <v>0.01519778152915589</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0151977815291559</v>
+        <v>0.01519778152915589</v>
       </c>
       <c r="J3" t="n">
         <v>0.01518553648457109</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01520192064000341</v>
+        <v>0.0152019206400034</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0151977815291559</v>
+        <v>0.01519778152915589</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01519775147062566</v>
+        <v>0.01519775147062565</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0151977815291559</v>
+        <v>0.01519778152915589</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0151976977317003</v>
+        <v>0.01519769773170029</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01519775792114238</v>
+        <v>0.01519775792114237</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01519778034006002</v>
+        <v>0.01519778034006001</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01519855731593091</v>
+        <v>0.0151985573159309</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0151977815291559</v>
+        <v>0.01519778152915589</v>
       </c>
       <c r="T3" t="n">
         <v>0.01519774507893215</v>
@@ -9025,19 +9025,19 @@
         <v>0.01518008987299914</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0151977815291559</v>
+        <v>0.01519778152915589</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01518652931398474</v>
+        <v>0.01518652931398473</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01519758912266158</v>
+        <v>0.01519758912266157</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01519873237755938</v>
+        <v>0.01519873237755937</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0151977815291559</v>
+        <v>0.01519778152915589</v>
       </c>
       <c r="AB3" t="n">
         <v>0.01503428381058579</v>
@@ -9050,85 +9050,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05299192156433962</v>
+        <v>0.05299192156433957</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01595220015695348</v>
+        <v>0.01595220015695343</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06448494928345895</v>
+        <v>0.06448494928345888</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02863102407300062</v>
+        <v>0.02863102407300065</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03606087005906697</v>
+        <v>0.03606087005906686</v>
       </c>
       <c r="G4" t="n">
         <v>0.1180398131449608</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09468422408268407</v>
+        <v>0.09468422408268391</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06070124816058632</v>
+        <v>0.06070124816058629</v>
       </c>
       <c r="J4" t="n">
-        <v>0.08491012368944241</v>
+        <v>0.08491012368944245</v>
       </c>
       <c r="K4" t="n">
-        <v>0.08328584629663582</v>
+        <v>0.08328584629663566</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1152669705080627</v>
+        <v>0.1152669705080626</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1210560505488719</v>
+        <v>0.121056050548872</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1078814197660554</v>
+        <v>0.1078814197660559</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04990672434111586</v>
+        <v>0.04990672434111584</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09781681235218789</v>
+        <v>0.09781681235218731</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04350052735599419</v>
+        <v>0.04350052735599415</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05261558523169556</v>
+        <v>0.05261558523169563</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06128354161378351</v>
+        <v>0.06128354161378348</v>
       </c>
       <c r="T4" t="n">
-        <v>0.06514808618050327</v>
+        <v>0.06514808618050325</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1078814197660554</v>
+        <v>0.1078814197660559</v>
       </c>
       <c r="V4" t="n">
-        <v>0.03127119458932633</v>
+        <v>0.0312711945893263</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1045104221204804</v>
+        <v>0.1045104221204803</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1134416113405982</v>
+        <v>0.1134416113405983</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.08737373839489167</v>
+        <v>0.08737373839489149</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.04993135757383726</v>
+        <v>0.04993135757383724</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.08588490010073659</v>
+        <v>0.08588490010073642</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1622805681944653</v>
+        <v>0.162280568194465</v>
       </c>
     </row>
     <row r="5">
@@ -9138,85 +9138,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003210629904584829</v>
+        <v>0.003210629904584799</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003210629904584831</v>
+        <v>0.003210629904584798</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003210629904584831</v>
+        <v>0.003210629904584798</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003210629904584831</v>
+        <v>0.003210629904584798</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003210629904584829</v>
+        <v>0.003210629904584799</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003210629904584831</v>
+        <v>0.003210629904584798</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003210629904584831</v>
+        <v>0.003210629904584798</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003210629904584831</v>
+        <v>0.003210629904584798</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003206532733288222</v>
+        <v>0.003206532733288206</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003210629904584831</v>
+        <v>0.003210629904584798</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003210629904584831</v>
+        <v>0.003210629904584798</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003210629904584831</v>
+        <v>0.003210629904584798</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003210629904584829</v>
+        <v>0.003210629904584799</v>
       </c>
       <c r="O5" t="n">
-        <v>0.003210629904584829</v>
+        <v>0.003210629904584799</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003210629904584829</v>
+        <v>0.003210629904584799</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.003210629904584829</v>
+        <v>0.003210629904584799</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003210629904584831</v>
+        <v>0.003210629904584798</v>
       </c>
       <c r="S5" t="n">
-        <v>0.003210629904584831</v>
+        <v>0.003210629904584798</v>
       </c>
       <c r="T5" t="n">
-        <v>0.003210629904584831</v>
+        <v>0.003210629904584798</v>
       </c>
       <c r="U5" t="n">
-        <v>0.003141024796417014</v>
+        <v>0.003141024796416956</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003184638811958797</v>
+        <v>0.003184638811958796</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003210629904584829</v>
+        <v>0.003210629904584799</v>
       </c>
       <c r="X5" t="n">
-        <v>0.003210629904584829</v>
+        <v>0.003210629904584799</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003141024796417014</v>
+        <v>0.003141024796416956</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.003210629904584831</v>
+        <v>0.003210629904584798</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.003210629904584831</v>
+        <v>0.003210629904584798</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003210629904584829</v>
+        <v>0.003210629904584799</v>
       </c>
     </row>
     <row r="6">
@@ -9226,85 +9226,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.006654336658799571</v>
+        <v>0.006654336658799504</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004391149302752725</v>
+        <v>0.004391149302752685</v>
       </c>
       <c r="D6" t="n">
-        <v>0.006654336658799571</v>
+        <v>0.006654336658799504</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006654336658799571</v>
+        <v>0.006654336658799504</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006654336658799571</v>
+        <v>0.006654336658799504</v>
       </c>
       <c r="G6" t="n">
-        <v>0.004391149302752725</v>
+        <v>0.004391149302752685</v>
       </c>
       <c r="H6" t="n">
-        <v>0.006654336658799571</v>
+        <v>0.006654336658799504</v>
       </c>
       <c r="I6" t="n">
-        <v>0.004391149302752725</v>
+        <v>0.004391149302752685</v>
       </c>
       <c r="J6" t="n">
-        <v>0.006650239487502923</v>
+        <v>0.004387052131456095</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004391149302752725</v>
+        <v>0.004391149302752685</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004391149302752725</v>
+        <v>0.006654336658799504</v>
       </c>
       <c r="M6" t="n">
-        <v>0.006654336658799571</v>
+        <v>0.006654336658799504</v>
       </c>
       <c r="N6" t="n">
-        <v>0.004402677296501767</v>
+        <v>0.004402677296501717</v>
       </c>
       <c r="O6" t="n">
-        <v>0.004402677296501762</v>
+        <v>0.004402677296501717</v>
       </c>
       <c r="P6" t="n">
-        <v>0.006681004830199312</v>
+        <v>0.006681004830199255</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.004391149302752725</v>
+        <v>0.006654336658799504</v>
       </c>
       <c r="R6" t="n">
-        <v>0.006654336658799571</v>
+        <v>0.006654336658799504</v>
       </c>
       <c r="S6" t="n">
-        <v>0.006654336658799571</v>
+        <v>0.006654336658799504</v>
       </c>
       <c r="T6" t="n">
-        <v>0.006654336658799571</v>
+        <v>0.004391149302752685</v>
       </c>
       <c r="U6" t="n">
-        <v>0.006654336658799571</v>
+        <v>0.006654336658799504</v>
       </c>
       <c r="V6" t="n">
-        <v>0.004365158210126683</v>
+        <v>0.006628345566173499</v>
       </c>
       <c r="W6" t="n">
-        <v>0.004526851129379793</v>
+        <v>0.004526851129379774</v>
       </c>
       <c r="X6" t="n">
-        <v>0.006654336658799571</v>
+        <v>0.004391149302752685</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0044881227074395</v>
+        <v>0.004488122707439594</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.004391149302752725</v>
+        <v>0.004391149302752685</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.006654336658799571</v>
+        <v>0.006654336658799504</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.004430393371399212</v>
+        <v>0.004430393371399177</v>
       </c>
     </row>
     <row r="7">
@@ -9314,85 +9314,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.005175462683855101</v>
+        <v>0.005175462683855053</v>
       </c>
       <c r="C7" t="n">
-        <v>0.005175462683855101</v>
+        <v>0.005175462683855053</v>
       </c>
       <c r="D7" t="n">
-        <v>0.005175462683855101</v>
+        <v>0.005175462683855053</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005175462683855101</v>
+        <v>0.005175462683855053</v>
       </c>
       <c r="F7" t="n">
-        <v>0.005175462683855101</v>
+        <v>0.005175462683855053</v>
       </c>
       <c r="G7" t="n">
-        <v>0.005175462683855101</v>
+        <v>0.005175462683855053</v>
       </c>
       <c r="H7" t="n">
-        <v>0.005175462683855101</v>
+        <v>0.005175462683855053</v>
       </c>
       <c r="I7" t="n">
-        <v>0.005175462683855101</v>
+        <v>0.005175462683855053</v>
       </c>
       <c r="J7" t="n">
-        <v>0.005171365512558491</v>
+        <v>0.005171365512558458</v>
       </c>
       <c r="K7" t="n">
-        <v>0.005175462683855101</v>
+        <v>0.005175462683855053</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005175462683855101</v>
+        <v>0.005175462683855053</v>
       </c>
       <c r="M7" t="n">
-        <v>0.005175462683855101</v>
+        <v>0.005175462683855053</v>
       </c>
       <c r="N7" t="n">
-        <v>0.005175462683855101</v>
+        <v>0.005175462683855053</v>
       </c>
       <c r="O7" t="n">
-        <v>0.00517531435493605</v>
+        <v>0.005175314354936002</v>
       </c>
       <c r="P7" t="n">
-        <v>0.00517531435493605</v>
+        <v>0.005175314354936002</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.005175462683855101</v>
+        <v>0.005175462683855053</v>
       </c>
       <c r="R7" t="n">
-        <v>0.005175462683855101</v>
+        <v>0.005175462683855053</v>
       </c>
       <c r="S7" t="n">
-        <v>0.005175462683855101</v>
+        <v>0.005175462683855053</v>
       </c>
       <c r="T7" t="n">
-        <v>0.005175462683855101</v>
+        <v>0.005175462683855053</v>
       </c>
       <c r="U7" t="n">
-        <v>0.005172663530640211</v>
+        <v>0.005172663530640127</v>
       </c>
       <c r="V7" t="n">
-        <v>0.00514947159122905</v>
+        <v>0.005149471591229054</v>
       </c>
       <c r="W7" t="n">
-        <v>0.005175462683855101</v>
+        <v>0.005175462683855053</v>
       </c>
       <c r="X7" t="n">
-        <v>0.005175462683855101</v>
+        <v>0.005175462683855053</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.005175462683855101</v>
+        <v>0.005175462683855053</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.005175462683855101</v>
+        <v>0.005175462683855053</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.005175462683855101</v>
+        <v>0.005175462683855053</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.005175462683855101</v>
+        <v>0.005175462683855053</v>
       </c>
     </row>
     <row r="8">
@@ -9402,85 +9402,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.007379989308953409</v>
+        <v>0.007379989308953359</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01068146060655123</v>
+        <v>0.01068146060655117</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01068146060655123</v>
+        <v>0.01068146060655117</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01068146060655123</v>
+        <v>0.008923524528974616</v>
       </c>
       <c r="F8" t="n">
-        <v>0.007894319951457694</v>
+        <v>0.00789431995145764</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01068146060655123</v>
+        <v>0.01136604218680474</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01068146060655123</v>
+        <v>0.01068146060655117</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01068146060655123</v>
+        <v>0.01068146060655117</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01067736343525458</v>
+        <v>0.01067736343525456</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01068146060655123</v>
+        <v>0.01068146060655117</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01068146060655123</v>
+        <v>0.01068146060655117</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01068146060655123</v>
+        <v>0.01068146060655089</v>
       </c>
       <c r="N8" t="n">
-        <v>0.008122268025521091</v>
+        <v>0.00812226802552103</v>
       </c>
       <c r="O8" t="n">
-        <v>0.008825556365202363</v>
+        <v>0.008825556365202302</v>
       </c>
       <c r="P8" t="n">
-        <v>0.008653163399603802</v>
+        <v>0.008653163399603734</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0067311748480402</v>
+        <v>0.006731174848040107</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01068146060655123</v>
+        <v>0.01068146060655117</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01068146060655123</v>
+        <v>0.01068146060655117</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01068146060655123</v>
+        <v>0.01068146060655117</v>
       </c>
       <c r="U8" t="n">
-        <v>0.008647978089507303</v>
+        <v>0.009068002203623679</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01065546951392516</v>
+        <v>0.009750861766120993</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01068210943512112</v>
+        <v>0.01068210943512105</v>
       </c>
       <c r="X8" t="n">
-        <v>0.007033761249403653</v>
+        <v>0.0070337612494036</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01396052401965277</v>
+        <v>0.01396052401965274</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01068146060655123</v>
+        <v>0.007318662785131638</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01068146060655123</v>
+        <v>0.01068146060655117</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01413012343652455</v>
+        <v>0.01413012343652451</v>
       </c>
     </row>
     <row r="9">
@@ -9493,82 +9493,82 @@
         <v>0.0108491546317406</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01324554616860043</v>
+        <v>0.01324554616860038</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01324554616860043</v>
+        <v>0.01324554616860038</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01324554616860043</v>
+        <v>0.01269246944666328</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01324554616860043</v>
+        <v>0.007721208501790026</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01324554616860043</v>
+        <v>0.0132455470397178</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01324554616860043</v>
+        <v>0.01324554616860038</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01324554616860043</v>
+        <v>0.01324554616860038</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01324144899730381</v>
+        <v>0.01324144899730379</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01324554616860043</v>
+        <v>0.01324554616860038</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01324554616860043</v>
+        <v>0.01324554616860038</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01324554616860043</v>
+        <v>0.01324554616860038</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01324554616860043</v>
+        <v>0.01324554616860038</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01403970834591337</v>
+        <v>0.01403970834591334</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01421242480449759</v>
+        <v>0.01421242480449757</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01324554703971785</v>
+        <v>0.0132455470397178</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01324554616860043</v>
+        <v>0.01324554616860038</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01324554616860043</v>
+        <v>0.01324554616860038</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01324554616860043</v>
+        <v>0.01324554616860038</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01324554616860043</v>
+        <v>0.01324554616860038</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01321955507597436</v>
+        <v>0.0159849385799612</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01324554616860043</v>
+        <v>0.01324554616860038</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01324554616860043</v>
+        <v>0.01324554616860038</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01324554616860043</v>
+        <v>0.01324554616860038</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01324554616860043</v>
+        <v>0.01180073551323487</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01324554616860043</v>
+        <v>0.01324554616860038</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.01324554616860043</v>
+        <v>0.01324554616860038</v>
       </c>
     </row>
     <row r="10">
@@ -9584,7 +9584,7 @@
         <v>0.0149586311753745</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01394315312883777</v>
+        <v>0.01394315312883775</v>
       </c>
       <c r="E10" t="n">
         <v>0.01147855494699738</v>
@@ -9596,16 +9596,16 @@
         <v>0.01234120174242381</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01339521255047933</v>
+        <v>0.01339521255047932</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01402304857009681</v>
+        <v>0.01402304857009682</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01329842408436879</v>
+        <v>0.01329842408436878</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01336446643388322</v>
+        <v>0.01336446643388323</v>
       </c>
       <c r="L10" t="n">
         <v>0.01265946325510919</v>
@@ -9620,40 +9620,40 @@
         <v>0.01406220719030941</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01300008211385399</v>
+        <v>0.013000082113854</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01433144930725633</v>
+        <v>0.01433144930725632</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01421532737264577</v>
+        <v>0.01421532737264575</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01377866135571778</v>
+        <v>0.01377866135571779</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01392717320885774</v>
+        <v>0.01392717320885773</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01284438451032871</v>
+        <v>0.0128443845103287</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01451491742444912</v>
+        <v>0.01451491742444913</v>
       </c>
       <c r="W10" t="n">
         <v>0.01300631856024294</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0128775983406431</v>
+        <v>0.01287759834064308</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.01335531970310749</v>
+        <v>0.01335531970310748</v>
       </c>
       <c r="Z10" t="n">
         <v>0.01410145536773328</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.01340689038232953</v>
+        <v>0.01340689038232952</v>
       </c>
       <c r="AB10" t="n">
         <v>0.01190806731072353</v>
@@ -9666,31 +9666,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01471403007808331</v>
+        <v>0.0147140300780833</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0148777583054325</v>
+        <v>0.01487775830543249</v>
       </c>
       <c r="D11" t="n">
         <v>0.01457569608614971</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01165656763791836</v>
+        <v>0.01165656763791837</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01474887946933863</v>
+        <v>0.01474887946933862</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01406110077381995</v>
+        <v>0.01406110077381994</v>
       </c>
       <c r="H11" t="n">
         <v>0.01443108085026614</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0147167482399868</v>
+        <v>0.01471674823998679</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01438036967962861</v>
+        <v>0.0143803696796286</v>
       </c>
       <c r="K11" t="n">
         <v>0.01441899042135701</v>
@@ -9699,28 +9699,28 @@
         <v>0.01409631257617885</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01419382288241461</v>
+        <v>0.0141938228824146</v>
       </c>
       <c r="N11" t="n">
         <v>0.0143948918567593</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01473452708888178</v>
+        <v>0.01473452708888177</v>
       </c>
       <c r="P11" t="n">
         <v>0.01425128441040571</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0148570710126336</v>
+        <v>0.01485707101263358</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01480459168612596</v>
+        <v>0.01480459168612595</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01460555127862848</v>
+        <v>0.01460555127862847</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01467310792096613</v>
+        <v>0.01467310792096612</v>
       </c>
       <c r="U11" t="n">
         <v>0.01418051301837756</v>
@@ -9729,16 +9729,16 @@
         <v>0.0147235748196372</v>
       </c>
       <c r="W11" t="n">
-        <v>0.01425413284537697</v>
+        <v>0.01425413284537698</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01419040198336092</v>
+        <v>0.01419040198336091</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01441284119723403</v>
+        <v>0.01441284119723402</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.01461861076338044</v>
+        <v>0.01461861076338043</v>
       </c>
       <c r="AA11" t="n">
         <v>0.01443639430097303</v>
@@ -9910,82 +9910,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01500516955264798</v>
+        <v>0.01500516955264799</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01487211939323884</v>
+        <v>0.01487211939323886</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01487739067082904</v>
+        <v>0.01487739067082903</v>
       </c>
       <c r="E2" t="n">
         <v>0.01180247504616437</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01486635398215779</v>
+        <v>0.01486635398215781</v>
       </c>
       <c r="G2" t="n">
         <v>0.0151072770384837</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01500516955264798</v>
+        <v>0.01500516955264799</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01500516955264798</v>
+        <v>0.01500516955264799</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01499553097417153</v>
+        <v>0.01499553097417151</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01501053469632959</v>
+        <v>0.0150105346963296</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01500516955264798</v>
+        <v>0.01500516955264799</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01487893485394145</v>
+        <v>0.01487893485394146</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01490528959976438</v>
+        <v>0.01490528959976437</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01500508404055301</v>
+        <v>0.01500508404055302</v>
       </c>
       <c r="P2" t="n">
         <v>0.01500515873111203</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01500516846602996</v>
+        <v>0.01500516846602997</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01498479503956983</v>
+        <v>0.01498479503956984</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01500516955264798</v>
+        <v>0.01500516955264799</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01500507145760226</v>
+        <v>0.01500507145760227</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01500487953253946</v>
+        <v>0.01500487953253947</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01484809650288164</v>
+        <v>0.01484809650288165</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01500516955264798</v>
+        <v>0.01500516955264799</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01488243347311775</v>
+        <v>0.01488243347311776</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01500495821692449</v>
+        <v>0.0150049582169245</v>
       </c>
       <c r="Z2" t="n">
         <v>0.01489601966869609</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01500516955264798</v>
+        <v>0.01500516955264799</v>
       </c>
       <c r="AB2" t="n">
         <v>0.01485576120913971</v>
@@ -10007,13 +10007,13 @@
         <v>0.01507585190923669</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01196680505559095</v>
+        <v>0.01196680505559094</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01508672594183715</v>
+        <v>0.01508672594183716</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01497742477565255</v>
+        <v>0.01497742477565256</v>
       </c>
       <c r="H3" t="n">
         <v>0.01507585190923669</v>
@@ -10022,10 +10022,10 @@
         <v>0.01507585190923669</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01506621223012753</v>
+        <v>0.01506621223012752</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01508172295817012</v>
+        <v>0.01508172295817013</v>
       </c>
       <c r="L3" t="n">
         <v>0.01507585190923669</v>
@@ -10040,22 +10040,22 @@
         <v>0.01507575833321094</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01507584006726044</v>
+        <v>0.01507584006726045</v>
       </c>
       <c r="Q3" t="n">
         <v>0.01507585072014081</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01505355600882916</v>
+        <v>0.01505355600882917</v>
       </c>
       <c r="S3" t="n">
         <v>0.01507585190923669</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01507574456366287</v>
+        <v>0.01507574456366288</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01507553453993438</v>
+        <v>0.01507553453993439</v>
       </c>
       <c r="V3" t="n">
         <v>0.01503155706748806</v>
@@ -10086,85 +10086,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008829833095284808</v>
+        <v>0.008829833095284775</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01329809056640837</v>
+        <v>0.01329809056640834</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02004772870885041</v>
+        <v>0.02004772870885042</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01601060969692528</v>
+        <v>0.01601060969692525</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01471790249187925</v>
+        <v>0.01471790249187922</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08757162658567536</v>
+        <v>0.08757162658567456</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05931291010189665</v>
+        <v>0.05931291010189654</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01863129875740095</v>
+        <v>0.0186312987574009</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04773878550333941</v>
+        <v>0.04773878550333929</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02549107129581743</v>
+        <v>0.02549107129581742</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04647732878893057</v>
+        <v>0.04647732878893053</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01996363225565005</v>
+        <v>0.01996363225565</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02238964157300559</v>
+        <v>0.02238964157300555</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01717271070229937</v>
+        <v>0.01717271070229942</v>
       </c>
       <c r="P4" t="n">
-        <v>0.05386355356151018</v>
+        <v>0.05386355356151015</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02173852695497001</v>
+        <v>0.02173852695496998</v>
       </c>
       <c r="R4" t="n">
-        <v>0.03349926044722343</v>
+        <v>0.03349926044722334</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02488785582770354</v>
+        <v>0.02488785582770358</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01718733754278679</v>
+        <v>0.01718733754278676</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02238964157300559</v>
+        <v>0.02238964157300555</v>
       </c>
       <c r="V4" t="n">
         <v>0.02148692212571761</v>
       </c>
       <c r="W4" t="n">
-        <v>0.08344916525237886</v>
+        <v>0.0834491652523788</v>
       </c>
       <c r="X4" t="n">
-        <v>0.08704389554631094</v>
+        <v>0.08704389554631088</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1074258888780572</v>
+        <v>0.107425888878057</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02174959849171589</v>
+        <v>0.02174959849171585</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0383117886361183</v>
+        <v>0.03831178863611837</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2862590064725867</v>
+        <v>0.2862590064725862</v>
       </c>
     </row>
     <row r="5">
@@ -10174,85 +10174,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002794679060820479</v>
+        <v>0.002794679060820441</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002794679060820465</v>
+        <v>0.00279467906082044</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002794679060820465</v>
+        <v>0.00279467906082044</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002794679060820465</v>
+        <v>0.00279467906082044</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002794679060820479</v>
+        <v>0.002794679060820441</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002794679060820465</v>
+        <v>0.00279467906082044</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002794679060820465</v>
+        <v>0.00279467906082044</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002794679060820465</v>
+        <v>0.00279467906082044</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002791365762659756</v>
+        <v>0.002791365762659747</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002794679060820465</v>
+        <v>0.00279467906082044</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002794679060820465</v>
+        <v>0.00279467906082044</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002794679060820465</v>
+        <v>0.00279467906082044</v>
       </c>
       <c r="N5" t="n">
-        <v>0.002794679060820479</v>
+        <v>0.002794679060820441</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002794679060820479</v>
+        <v>0.002794679060820441</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002794679060820479</v>
+        <v>0.002794679060820441</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002794679060820479</v>
+        <v>0.002794679060820441</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002794679060820465</v>
+        <v>0.00279467906082044</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002794679060820465</v>
+        <v>0.00279467906082044</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002794679060820465</v>
+        <v>0.00279467906082044</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002738000149691379</v>
+        <v>0.002738000149691361</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002773717627536943</v>
+        <v>0.002773717627536935</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002794679060820479</v>
+        <v>0.002794679060820441</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002794679060820479</v>
+        <v>0.002794679060820441</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.002738000149691379</v>
+        <v>0.002738000149691361</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002794679060820465</v>
+        <v>0.00279467906082044</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002794679060820465</v>
+        <v>0.00279467906082044</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.002794679060820479</v>
+        <v>0.002794679060820441</v>
       </c>
     </row>
     <row r="6">
@@ -10262,85 +10262,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0059965974717168</v>
+        <v>0.003942323703437302</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0059965974717168</v>
+        <v>0.005996597471716799</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003942323703437296</v>
+        <v>0.003942323703437302</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003942323703437296</v>
+        <v>0.005996597471716799</v>
       </c>
       <c r="F6" t="n">
-        <v>0.003942323703437296</v>
+        <v>0.005996597471716799</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0059965974717168</v>
+        <v>0.003942323703437302</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003942323703437296</v>
+        <v>0.005996597471716799</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003942323703437296</v>
+        <v>0.005996597471716799</v>
       </c>
       <c r="J6" t="n">
-        <v>0.005993284173556106</v>
+        <v>0.003939010405276609</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003942323703437296</v>
+        <v>0.005996597471716799</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0059965974717168</v>
+        <v>0.003942323703437302</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003942323703437296</v>
+        <v>0.005996597471716799</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003947539362807343</v>
+        <v>0.003947539362807297</v>
       </c>
       <c r="O6" t="n">
-        <v>0.006019062715131563</v>
+        <v>0.003947539362807262</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003828820735019326</v>
+        <v>0.003828820735019215</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.003942323703437296</v>
+        <v>0.005996597471716799</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0059965974717168</v>
+        <v>0.005996597471716799</v>
       </c>
       <c r="S6" t="n">
-        <v>0.003942323703437296</v>
+        <v>0.003942323703437302</v>
       </c>
       <c r="T6" t="n">
-        <v>0.003942323703437296</v>
+        <v>0.003942323703437302</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0059965974717168</v>
+        <v>0.003942323703437302</v>
       </c>
       <c r="V6" t="n">
-        <v>0.005975636038433299</v>
+        <v>0.005975636038433291</v>
       </c>
       <c r="W6" t="n">
-        <v>0.00406876837414365</v>
+        <v>0.004068768374143616</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0059965974717168</v>
+        <v>0.003942323703437302</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.004030287686210037</v>
+        <v>0.004030287686210106</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.003942323703437296</v>
+        <v>0.003942323703437302</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0059965974717168</v>
+        <v>0.005996597471716799</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.004024993855425613</v>
+        <v>0.004024993855425593</v>
       </c>
     </row>
     <row r="7">
@@ -10350,85 +10350,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00442001792061118</v>
+        <v>0.004420017920611137</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00442001792061118</v>
+        <v>0.004420017920611137</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00442001792061118</v>
+        <v>0.004420017920611137</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00442001792061118</v>
+        <v>0.004420017920611137</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00442001792061118</v>
+        <v>0.004420017920611137</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00442001792061118</v>
+        <v>0.004420017920611137</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00442001792061118</v>
+        <v>0.004420017920611137</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00442001792061118</v>
+        <v>0.004420017920611137</v>
       </c>
       <c r="J7" t="n">
-        <v>0.004416704622450428</v>
+        <v>0.004416704622450443</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00442001792061118</v>
+        <v>0.004420017920611137</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00442001792061118</v>
+        <v>0.004420017920611137</v>
       </c>
       <c r="M7" t="n">
-        <v>0.00442001792061118</v>
+        <v>0.004420017920611137</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00442001792061118</v>
+        <v>0.004420017920611137</v>
       </c>
       <c r="O7" t="n">
-        <v>0.004419881463463145</v>
+        <v>0.004419881463463142</v>
       </c>
       <c r="P7" t="n">
-        <v>0.004419881463463145</v>
+        <v>0.004419881463463142</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.00442001792061118</v>
+        <v>0.004420017920611137</v>
       </c>
       <c r="R7" t="n">
-        <v>0.00442001792061118</v>
+        <v>0.004420017920611137</v>
       </c>
       <c r="S7" t="n">
-        <v>0.00442001792061118</v>
+        <v>0.004420017920611137</v>
       </c>
       <c r="T7" t="n">
-        <v>0.00442001792061118</v>
+        <v>0.004420017920611137</v>
       </c>
       <c r="U7" t="n">
-        <v>0.004417071298656264</v>
+        <v>0.004417071298656256</v>
       </c>
       <c r="V7" t="n">
-        <v>0.004399056487327633</v>
+        <v>0.004399056487327632</v>
       </c>
       <c r="W7" t="n">
-        <v>0.00442001792061118</v>
+        <v>0.004420017920611137</v>
       </c>
       <c r="X7" t="n">
-        <v>0.00442001792061118</v>
+        <v>0.004420017920611137</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.00442001792061118</v>
+        <v>0.004420017920611137</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.00442001792061118</v>
+        <v>0.004420017920611137</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00442001792061118</v>
+        <v>0.004420017920611137</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.00442001792061118</v>
+        <v>0.004420017920611137</v>
       </c>
     </row>
     <row r="8">
@@ -10438,82 +10438,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.006363254629526763</v>
+        <v>0.006363254629526755</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009218896940322751</v>
+        <v>0.009218896940322739</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009218896940322751</v>
+        <v>0.009218896940322739</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009218896940322751</v>
+        <v>0.007698351647010139</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00680813032644113</v>
+        <v>0.006808130326441135</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009218896940322751</v>
+        <v>0.009811032975884298</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009218896940322751</v>
+        <v>0.009218896940322739</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009218896940322751</v>
+        <v>0.009218896940322739</v>
       </c>
       <c r="J8" t="n">
         <v>0.009215583642162043</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009218896940322751</v>
+        <v>0.009218896940322739</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009218896940322751</v>
+        <v>0.009218896940322739</v>
       </c>
       <c r="M8" t="n">
-        <v>0.009218896940322751</v>
+        <v>0.00921889694032243</v>
       </c>
       <c r="N8" t="n">
-        <v>0.007005296409719893</v>
+        <v>0.00700529640971992</v>
       </c>
       <c r="O8" t="n">
-        <v>0.007613613053407867</v>
+        <v>0.007613613053407855</v>
       </c>
       <c r="P8" t="n">
-        <v>0.007464499945314732</v>
+        <v>0.007464499945314755</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.005802055739967682</v>
+        <v>0.005802055739967685</v>
       </c>
       <c r="R8" t="n">
-        <v>0.009218896940322751</v>
+        <v>0.009218896940322739</v>
       </c>
       <c r="S8" t="n">
-        <v>0.009218896940322751</v>
+        <v>0.009218896940322739</v>
       </c>
       <c r="T8" t="n">
-        <v>0.009218896940322751</v>
+        <v>0.009218896940322739</v>
       </c>
       <c r="U8" t="n">
-        <v>0.007459638417818113</v>
+        <v>0.007822918230672838</v>
       </c>
       <c r="V8" t="n">
-        <v>0.009197935507039236</v>
+        <v>0.008415043343505802</v>
       </c>
       <c r="W8" t="n">
-        <v>0.00921945815108679</v>
+        <v>0.009219458151086773</v>
       </c>
       <c r="X8" t="n">
-        <v>0.006063781029040349</v>
+        <v>0.006063781029040352</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01205447149279466</v>
+        <v>0.01205447149279465</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.009218896940322751</v>
+        <v>0.006310209607989364</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.009218896940322751</v>
+        <v>0.009218896940322739</v>
       </c>
       <c r="AB8" t="n">
         <v>0.01220185411431328</v>
@@ -10526,85 +10526,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008768131094627154</v>
+        <v>0.008768131094627159</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01067613915118229</v>
+        <v>0.01067613915118226</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01067613915118229</v>
+        <v>0.01067613915118226</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01067613915118229</v>
+        <v>0.01023577960687916</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01067613915118229</v>
+        <v>0.006277658253600842</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01067613915118229</v>
+        <v>0.01067614036350904</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01067613915118229</v>
+        <v>0.01067613915118226</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01067613915118229</v>
+        <v>0.01067613915118226</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0106728258530216</v>
+        <v>0.01067282585302157</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01067613915118229</v>
+        <v>0.01067613915118226</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01067613915118229</v>
+        <v>0.01067613915118226</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01067613915118229</v>
+        <v>0.01067613915118226</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01067613915118229</v>
+        <v>0.01067613915118226</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01130845213689153</v>
+        <v>0.01130845213689152</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01144596909895925</v>
+        <v>0.01144596909895923</v>
       </c>
       <c r="Q9" t="n">
         <v>0.01067614036350904</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01067613915118229</v>
+        <v>0.01067613915118226</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01067613915118229</v>
+        <v>0.01067613915118226</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01067613915118229</v>
+        <v>0.01067613915118226</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01067613915118229</v>
+        <v>0.01067613915118226</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01065517771789876</v>
+        <v>0.01285697888298656</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01067613915118229</v>
+        <v>0.01067613915118226</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01067613915118229</v>
+        <v>0.01067613915118226</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01067613915118229</v>
+        <v>0.01067613915118226</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01067613915118229</v>
+        <v>0.009525780441177363</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01067613915118229</v>
+        <v>0.01067613915118226</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.01067613915118229</v>
+        <v>0.01067613915118226</v>
       </c>
     </row>
     <row r="10">
@@ -10617,34 +10617,34 @@
         <v>0.0149327418647354</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01486506487513425</v>
+        <v>0.01486506487513424</v>
       </c>
       <c r="D10" t="n">
         <v>0.0146921209342143</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01166119376857237</v>
+        <v>0.01166119376857234</v>
       </c>
       <c r="F10" t="n">
         <v>0.01482713282068138</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01268619878977796</v>
+        <v>0.01268619878977799</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01389163603038803</v>
+        <v>0.01389163603038801</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01473452587058053</v>
+        <v>0.01473452587058055</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01392113678720012</v>
+        <v>0.01392113678720011</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0145281162516346</v>
+        <v>0.01452811625163459</v>
       </c>
       <c r="L10" t="n">
-        <v>0.013958206209742</v>
+        <v>0.01395820620974201</v>
       </c>
       <c r="M10" t="n">
         <v>0.01468405976486806</v>
@@ -10656,7 +10656,7 @@
         <v>0.01470957554089881</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0137728028432395</v>
+        <v>0.01377280284323949</v>
       </c>
       <c r="Q10" t="n">
         <v>0.0146156679891644</v>
@@ -10668,7 +10668,7 @@
         <v>0.01450229567128362</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01476189049502891</v>
+        <v>0.0147618904950289</v>
       </c>
       <c r="U10" t="n">
         <v>0.01459052322278448</v>
@@ -10680,19 +10680,19 @@
         <v>0.01320486768050722</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0129837655866377</v>
+        <v>0.01298376558663771</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.01261895280301869</v>
+        <v>0.01261895280301868</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01458609454357552</v>
+        <v>0.01458609454357553</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.01425591073904713</v>
+        <v>0.01425591073904715</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.008774059250143448</v>
+        <v>0.008774059250143447</v>
       </c>
     </row>
     <row r="11">
@@ -10705,67 +10705,67 @@
         <v>0.01494005402633524</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01476601584319153</v>
+        <v>0.01476601584319152</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01470279185431579</v>
+        <v>0.01470279185431578</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01166342093664553</v>
+        <v>0.01166342093664552</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01474823828475774</v>
+        <v>0.01474823828475772</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01406476191320681</v>
+        <v>0.0140647619132068</v>
       </c>
       <c r="H11" t="n">
         <v>0.01446634755389974</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01484986511731792</v>
+        <v>0.01484986511731789</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01447451799850062</v>
+        <v>0.01447451799850061</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01475864188061606</v>
+        <v>0.01475864188061602</v>
       </c>
       <c r="L11" t="n">
         <v>0.01449663719765239</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01470070517364951</v>
+        <v>0.0147007051736495</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01465527729884263</v>
+        <v>0.01465527729884262</v>
       </c>
       <c r="O11" t="n">
         <v>0.01483846970309568</v>
       </c>
       <c r="P11" t="n">
-        <v>0.01441227264164927</v>
+        <v>0.01441227264164924</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01479578385692032</v>
+        <v>0.01479578385692033</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01468594616848918</v>
+        <v>0.01468594616848917</v>
       </c>
       <c r="S11" t="n">
         <v>0.01474419963656405</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01486226685618024</v>
+        <v>0.01486226685618022</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01478419783759689</v>
+        <v>0.0147841978375969</v>
       </c>
       <c r="V11" t="n">
-        <v>0.01463071836141135</v>
+        <v>0.01463071836141136</v>
       </c>
       <c r="W11" t="n">
-        <v>0.01415386576610312</v>
+        <v>0.0141538657661031</v>
       </c>
       <c r="X11" t="n">
         <v>0.01399163911439958</v>
@@ -10774,10 +10774,10 @@
         <v>0.01388716652021896</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.01467245104055967</v>
+        <v>0.01467245104055968</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.01463209370721426</v>
+        <v>0.01463209370721427</v>
       </c>
       <c r="AB11" t="n">
         <v>0.01206281744961637</v>

--- a/Results/Phase 2/Hydrogen/hydrogen photochemical ozone formation results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen photochemical ozone formation results.xlsx
@@ -886,7 +886,7 @@
         <v>0.002347892823991598</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1187620068051895</v>
+        <v>0.002347892823991603</v>
       </c>
       <c r="O5" t="n">
         <v>0.002347892823991603</v>
@@ -974,7 +974,7 @@
         <v>0.005919581235705173</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1187620068051895</v>
+        <v>0.003620558384359512</v>
       </c>
       <c r="O6" t="n">
         <v>0.003620552613492412</v>
@@ -1062,7 +1062,7 @@
         <v>0.004552792437108952</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1187620068051895</v>
+        <v>0.004552792437108952</v>
       </c>
       <c r="O7" t="n">
         <v>0.004552631736606745</v>
@@ -1150,7 +1150,7 @@
         <v>0.01067311886583013</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1187620068051895</v>
+        <v>0.007838802192322001</v>
       </c>
       <c r="O8" t="n">
         <v>0.008617697021330412</v>
@@ -1238,7 +1238,7 @@
         <v>0.01363463266959801</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1187620068051895</v>
+        <v>0.01363463266959801</v>
       </c>
       <c r="O9" t="n">
         <v>0.01452291152033632</v>
@@ -1922,7 +1922,7 @@
         <v>0.001887243234114928</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0199811132414302</v>
+        <v>0.001887243234114926</v>
       </c>
       <c r="O5" t="n">
         <v>0.001887243234114926</v>
@@ -2010,7 +2010,7 @@
         <v>0.002907124152755205</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0199811132414302</v>
+        <v>0.002921705632947665</v>
       </c>
       <c r="O6" t="n">
         <v>0.004643504649948301</v>
@@ -2098,7 +2098,7 @@
         <v>0.003412186881694523</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0199811132414302</v>
+        <v>0.003412186881694523</v>
       </c>
       <c r="O7" t="n">
         <v>0.003412052891290207</v>
@@ -2186,7 +2186,7 @@
         <v>0.007806365946355918</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0199811132414302</v>
+        <v>0.005780610614389919</v>
       </c>
       <c r="O8" t="n">
         <v>0.006337305766547319</v>
@@ -2274,7 +2274,7 @@
         <v>0.008079896459163008</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0199811132414302</v>
+        <v>0.008079896459163008</v>
       </c>
       <c r="O9" t="n">
         <v>0.008582445324192899</v>
@@ -2958,7 +2958,7 @@
         <v>0.002120935994656356</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0798783163693931</v>
+        <v>0.002120935994656351</v>
       </c>
       <c r="O5" t="n">
         <v>0.002120935994656351</v>
@@ -3046,7 +3046,7 @@
         <v>0.005258659190380573</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0798783163693931</v>
+        <v>0.003228720616431338</v>
       </c>
       <c r="O6" t="n">
         <v>0.003224701231487115</v>
@@ -3134,7 +3134,7 @@
         <v>0.004076948606474613</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0798783163693931</v>
+        <v>0.004076948606474613</v>
       </c>
       <c r="O7" t="n">
         <v>0.004076803106064005</v>
@@ -3222,7 +3222,7 @@
         <v>0.009538074929039386</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0798783163693931</v>
+        <v>0.007011611530298273</v>
       </c>
       <c r="O8" t="n">
         <v>0.007705905606543928</v>
@@ -3310,7 +3310,7 @@
         <v>0.01122799925783298</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0798783163693931</v>
+        <v>0.01122799925783298</v>
       </c>
       <c r="O9" t="n">
         <v>0.01195159715104362</v>
@@ -3694,16 +3694,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01502266312620228</v>
+        <v>0.01502266312620227</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0149275691874522</v>
+        <v>0.01492756918745221</v>
       </c>
       <c r="D2" t="n">
         <v>0.01512745266808718</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01186080404576721</v>
+        <v>0.0118608040457672</v>
       </c>
       <c r="F2" t="n">
         <v>0.01496564687641237</v>
@@ -3718,13 +3718,13 @@
         <v>0.01513637137671681</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01511020305018138</v>
+        <v>0.01511020305018139</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0151549207630467</v>
+        <v>0.01515492076304671</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01506325449488666</v>
+        <v>0.01506325449488667</v>
       </c>
       <c r="M2" t="n">
         <v>0.01554845016704028</v>
@@ -3733,22 +3733,22 @@
         <v>0.0150301576115651</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01500132015052278</v>
+        <v>0.01500132015052277</v>
       </c>
       <c r="P2" t="n">
         <v>0.01506484516257103</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01496130002985538</v>
+        <v>0.01496130002985539</v>
       </c>
       <c r="R2" t="n">
         <v>0.0150608340843593</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01507440825484101</v>
+        <v>0.015074408254841</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01510958335052926</v>
+        <v>0.01510958335052925</v>
       </c>
       <c r="U2" t="n">
         <v>0.01513076935610414</v>
@@ -3760,10 +3760,10 @@
         <v>0.01527268617439097</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01508482298313871</v>
+        <v>0.01508482298313872</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01525099323233117</v>
+        <v>0.01525099323233118</v>
       </c>
       <c r="Z2" t="n">
         <v>0.01500334714972174</v>
@@ -3772,7 +3772,7 @@
         <v>0.01520313640286985</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01512985652027875</v>
+        <v>0.01512985652027877</v>
       </c>
     </row>
     <row r="3">
@@ -3782,46 +3782,46 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01510746362363656</v>
+        <v>0.01510746362363655</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01512986957174378</v>
+        <v>0.01512986957174377</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01510746362363656</v>
+        <v>0.01510746362363655</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0119682584023093</v>
+        <v>0.01196825840230932</v>
       </c>
       <c r="F3" t="n">
         <v>0.01511833765623702</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01500903649005242</v>
+        <v>0.01500903649005241</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01510746362363656</v>
+        <v>0.01510746362363655</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01510746362363656</v>
+        <v>0.01510746362363655</v>
       </c>
       <c r="J3" t="n">
         <v>0.01510231461490752</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01511333467256999</v>
+        <v>0.01511333467256998</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01510746362363656</v>
+        <v>0.01510746362363655</v>
       </c>
       <c r="M3" t="n">
         <v>0.01510738231879224</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01510746362363656</v>
+        <v>0.01510746362363655</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01510737004761081</v>
+        <v>0.0151073700476108</v>
       </c>
       <c r="P3" t="n">
         <v>0.01510745178166031</v>
@@ -3833,22 +3833,22 @@
         <v>0.01508516772322903</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01510746362363656</v>
+        <v>0.01510746362363655</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01510735627806274</v>
+        <v>0.01510735627806273</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01510714625433425</v>
+        <v>0.01510714625433424</v>
       </c>
       <c r="V3" t="n">
         <v>0.01509757985623475</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01510746362363656</v>
+        <v>0.01510746362363655</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01497315338819353</v>
+        <v>0.01497315338819352</v>
       </c>
       <c r="Y3" t="n">
         <v>0.01510723235867048</v>
@@ -3857,7 +3857,7 @@
         <v>0.01510906243880436</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01510746362363656</v>
+        <v>0.01510746362363655</v>
       </c>
       <c r="AB3" t="n">
         <v>0.01494396590506645</v>
@@ -3870,82 +3870,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04532655936265429</v>
+        <v>0.04532655936265442</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01890958605047837</v>
+        <v>0.01890958605047835</v>
       </c>
       <c r="D4" t="n">
-        <v>0.07742311848532349</v>
+        <v>0.07742311848532353</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02996252522576102</v>
+        <v>0.02996252522576092</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03223452897618286</v>
+        <v>0.03223452897618285</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05749820857269047</v>
+        <v>0.0574982085726906</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08505145848536529</v>
+        <v>0.0850514584853652</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08104079068253509</v>
+        <v>0.08104079068253489</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07081144251941629</v>
+        <v>0.07081144251941621</v>
       </c>
       <c r="K4" t="n">
-        <v>0.07461413023242743</v>
+        <v>0.07461413023242741</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05780942878954436</v>
+        <v>0.0578094287895434</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1909309926053192</v>
+        <v>0.1909309926053188</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05102278727025401</v>
+        <v>0.05102278727025397</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03850049650093186</v>
+        <v>0.03850049650093196</v>
       </c>
       <c r="P4" t="n">
-        <v>0.05495498036763215</v>
+        <v>0.05495498036763203</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03266516585476091</v>
+        <v>0.03266516585476086</v>
       </c>
       <c r="R4" t="n">
-        <v>0.06736786146985647</v>
+        <v>0.06736786146985642</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0576528801972189</v>
+        <v>0.0576528801972187</v>
       </c>
       <c r="T4" t="n">
-        <v>0.07346757734910107</v>
+        <v>0.07346757734910116</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07276692321816743</v>
+        <v>0.07276692321816819</v>
       </c>
       <c r="V4" t="n">
-        <v>0.03362036230889883</v>
+        <v>0.03362036230889897</v>
       </c>
       <c r="W4" t="n">
         <v>0.1116666509031556</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0971248014528143</v>
+        <v>0.0971248014528146</v>
       </c>
       <c r="Y4" t="n">
         <v>0.1052389131762308</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03857325646377217</v>
+        <v>0.03857325646377205</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.09406018060001603</v>
+        <v>0.09406018060001595</v>
       </c>
       <c r="AB4" t="n">
         <v>0.1245659978372142</v>
@@ -3958,85 +3958,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002046763092603469</v>
+        <v>0.002046763092603458</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002046763092603474</v>
+        <v>0.002046763092603453</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002046763092603474</v>
+        <v>0.002046763092603453</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002046763092603474</v>
+        <v>0.002046763092603453</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00204676309260347</v>
+        <v>0.002046763092603456</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002046763092603474</v>
+        <v>0.002046763092603453</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002046763092603474</v>
+        <v>0.002046763092603453</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002046763092603474</v>
+        <v>0.002046763092603453</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002044383655924467</v>
+        <v>0.002044383655924454</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002046763092603474</v>
+        <v>0.002046763092603453</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002046763092603474</v>
+        <v>0.002046763092603455</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002046763092603474</v>
+        <v>0.002046763092603453</v>
       </c>
       <c r="N5" t="n">
-        <v>0.05102278727025401</v>
+        <v>0.002046763092603456</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00204676309260347</v>
+        <v>0.002046763092603456</v>
       </c>
       <c r="P5" t="n">
-        <v>0.00204676309260347</v>
+        <v>0.002046763092603456</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.00204676309260347</v>
+        <v>0.002046763092603456</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002046763092603474</v>
+        <v>0.002046763092603453</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002046763092603474</v>
+        <v>0.002046763092603453</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002046763092603474</v>
+        <v>0.002046763092603453</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001961392023306635</v>
+        <v>0.00196139202330662</v>
       </c>
       <c r="V5" t="n">
         <v>0.002031782572055082</v>
       </c>
       <c r="W5" t="n">
-        <v>0.00204676309260347</v>
+        <v>0.002046763092603456</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002046763092603469</v>
+        <v>0.002046763092603458</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001961392023306635</v>
+        <v>0.00196139202330662</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002046763092603474</v>
+        <v>0.002046763092603453</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002046763092603474</v>
+        <v>0.002046763092603453</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.00204676309260347</v>
+        <v>0.002046763092603456</v>
       </c>
     </row>
     <row r="6">
@@ -4046,85 +4046,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005029198083844098</v>
+        <v>0.005029198083844069</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003141482320607484</v>
+        <v>0.003141482320607457</v>
       </c>
       <c r="D6" t="n">
-        <v>0.005029198083844096</v>
+        <v>0.00502919808384407</v>
       </c>
       <c r="E6" t="n">
-        <v>0.005029198083844096</v>
+        <v>0.00502919808384407</v>
       </c>
       <c r="F6" t="n">
-        <v>0.003141482320607484</v>
+        <v>0.003141482320607457</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003141482320607484</v>
+        <v>0.003141482320607457</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003141482320607484</v>
+        <v>0.003141482320607457</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003141482320607484</v>
+        <v>0.003141482320607457</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00502681864716509</v>
+        <v>0.005026818647165076</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005029198083844096</v>
+        <v>0.00502919808384407</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005029198083844098</v>
+        <v>0.005029198083844069</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003141482320607484</v>
+        <v>0.003141482320607457</v>
       </c>
       <c r="N6" t="n">
-        <v>0.05102278727025401</v>
+        <v>0.003157791034171003</v>
       </c>
       <c r="O6" t="n">
-        <v>0.005051548216310156</v>
+        <v>0.005051548216310127</v>
       </c>
       <c r="P6" t="n">
-        <v>0.005054117057331357</v>
+        <v>0.00505411705733133</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.005029198083844096</v>
+        <v>0.00502919808384407</v>
       </c>
       <c r="R6" t="n">
-        <v>0.003141482320607484</v>
+        <v>0.003141482320607457</v>
       </c>
       <c r="S6" t="n">
-        <v>0.005029198083844096</v>
+        <v>0.00502919808384407</v>
       </c>
       <c r="T6" t="n">
-        <v>0.003141482320607484</v>
+        <v>0.003141482320607457</v>
       </c>
       <c r="U6" t="n">
-        <v>0.003141482320607484</v>
+        <v>0.003141482320607457</v>
       </c>
       <c r="V6" t="n">
-        <v>0.005014217563295712</v>
+        <v>0.005014217563295708</v>
       </c>
       <c r="W6" t="n">
-        <v>0.005051263910964772</v>
+        <v>0.005051263910964746</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003141482320607484</v>
+        <v>0.003141482320607457</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.003236901666821819</v>
+        <v>0.003236901666821851</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.005029198083844096</v>
+        <v>0.00502919808384407</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.005029198083844096</v>
+        <v>0.00502919808384407</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003172625519708981</v>
+        <v>0.00317262551970897</v>
       </c>
     </row>
     <row r="7">
@@ -4134,85 +4134,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00380952838251794</v>
+        <v>0.003809528382517937</v>
       </c>
       <c r="C7" t="n">
+        <v>0.003809528382517935</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.003809528382517935</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.003809528382517935</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.003809528382517935</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.003809528382517935</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.003809528382517935</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.003809528382517935</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.003807148945838935</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.003809528382517935</v>
+      </c>
+      <c r="L7" t="n">
         <v>0.003809528382517937</v>
       </c>
-      <c r="D7" t="n">
+      <c r="M7" t="n">
+        <v>0.003809528382517935</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.003809528382517935</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.003809392166168201</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.003809392166168201</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.003809528382517935</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.003809528382517935</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.003809528382517935</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.003809528382517935</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.003807448142013273</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.003794547861969566</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.003809528382517935</v>
+      </c>
+      <c r="X7" t="n">
         <v>0.003809528382517937</v>
       </c>
-      <c r="E7" t="n">
-        <v>0.003809528382517937</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.003809528382517937</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.003809528382517937</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.003809528382517937</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.003809528382517937</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.003807148945838956</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.003809528382517937</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.00380952838251794</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.003809528382517937</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.05102278727025401</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.003809392166168212</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.003809392166168212</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.003809528382517937</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.003809528382517937</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.003809528382517937</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.003809528382517937</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.003807448142013284</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.003794547861969564</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.003809528382517937</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.00380952838251794</v>
-      </c>
       <c r="Y7" t="n">
-        <v>0.003809528382517937</v>
+        <v>0.003809528382517935</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.003809528382517937</v>
+        <v>0.003809528382517935</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.003809528382517937</v>
+        <v>0.003809528382517935</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.003809528382517937</v>
+        <v>0.003809528382517935</v>
       </c>
     </row>
     <row r="8">
@@ -4225,79 +4225,79 @@
         <v>0.005807551203601279</v>
       </c>
       <c r="C8" t="n">
-        <v>0.008757351084545333</v>
+        <v>0.008757351084545313</v>
       </c>
       <c r="D8" t="n">
-        <v>0.008757351084545333</v>
+        <v>0.008757351084545313</v>
       </c>
       <c r="E8" t="n">
-        <v>0.007186669662590079</v>
+        <v>0.007186669662590063</v>
       </c>
       <c r="F8" t="n">
-        <v>0.006267095549509514</v>
+        <v>0.0062670955495095</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009369011305662834</v>
+        <v>0.009369011305662815</v>
       </c>
       <c r="H8" t="n">
-        <v>0.008757351084545333</v>
+        <v>0.008757351084545313</v>
       </c>
       <c r="I8" t="n">
-        <v>0.008757351084545333</v>
+        <v>0.008757351084545313</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00875497164786633</v>
+        <v>0.008754971647866323</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008757351084545333</v>
+        <v>0.008757351084545313</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008757351084545336</v>
+        <v>0.008757351084545315</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008757351084546366</v>
+        <v>0.008757351084546353</v>
       </c>
       <c r="N8" t="n">
-        <v>0.05102278727025401</v>
+        <v>0.006470762684876623</v>
       </c>
       <c r="O8" t="n">
-        <v>0.007099137028761763</v>
+        <v>0.007099137028761753</v>
       </c>
       <c r="P8" t="n">
-        <v>0.006945107293684885</v>
+        <v>0.00694510729368487</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.005227848202448106</v>
+        <v>0.005227848202448095</v>
       </c>
       <c r="R8" t="n">
-        <v>0.008757351084545333</v>
+        <v>0.008757351084545313</v>
       </c>
       <c r="S8" t="n">
-        <v>0.008757351084545333</v>
+        <v>0.008757351084545313</v>
       </c>
       <c r="T8" t="n">
-        <v>0.008757351084545333</v>
+        <v>0.008757351084545313</v>
       </c>
       <c r="U8" t="n">
-        <v>0.007316086559396444</v>
+        <v>0.007316086559396449</v>
       </c>
       <c r="V8" t="n">
         <v>0.007934484072443125</v>
       </c>
       <c r="W8" t="n">
-        <v>0.008757930800037084</v>
+        <v>0.008757930800037079</v>
       </c>
       <c r="X8" t="n">
-        <v>0.005498203219960406</v>
+        <v>0.005498203219960404</v>
       </c>
       <c r="Y8" t="n">
         <v>0.01168769265835533</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.005752757156851802</v>
+        <v>0.005752757156851799</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.008757351084545333</v>
+        <v>0.008757351084545313</v>
       </c>
       <c r="AB8" t="n">
         <v>0.01183866371394839</v>
@@ -4310,85 +4310,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.007924711835052103</v>
+        <v>0.007924711835052075</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009794134834657398</v>
+        <v>0.00979413483465737</v>
       </c>
       <c r="D9" t="n">
-        <v>0.009794134834657398</v>
+        <v>0.00979413483465737</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009362679179437077</v>
+        <v>0.009362679179437059</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005484605373881465</v>
+        <v>0.005484605373881448</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009794134246843351</v>
+        <v>0.009794134246843321</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009794134834657398</v>
+        <v>0.00979413483465737</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009794134834657398</v>
+        <v>0.00979413483465737</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009791755397978384</v>
+        <v>0.009791755397978365</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009794134834657398</v>
+        <v>0.00979413483465737</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009794134834657398</v>
+        <v>0.009794134834657376</v>
       </c>
       <c r="M9" t="n">
-        <v>0.009794134834657398</v>
+        <v>0.00979413483465737</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05102278727025401</v>
+        <v>0.00979413483465737</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01041365838631124</v>
+        <v>0.01041365838631122</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01054839425740134</v>
+        <v>0.01054839425740133</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.009794134246843351</v>
+        <v>0.009794134246843321</v>
       </c>
       <c r="R9" t="n">
-        <v>0.009794134834657398</v>
+        <v>0.00979413483465737</v>
       </c>
       <c r="S9" t="n">
-        <v>0.009794134834657398</v>
+        <v>0.00979413483465737</v>
       </c>
       <c r="T9" t="n">
-        <v>0.009794134834657398</v>
+        <v>0.00979413483465737</v>
       </c>
       <c r="U9" t="n">
-        <v>0.009794134834657398</v>
+        <v>0.00979413483465737</v>
       </c>
       <c r="V9" t="n">
         <v>0.01193642501953673</v>
       </c>
       <c r="W9" t="n">
-        <v>0.009794134834657398</v>
+        <v>0.00979413483465737</v>
       </c>
       <c r="X9" t="n">
-        <v>0.009794134834657398</v>
+        <v>0.009794134834657376</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.009794134834657398</v>
+        <v>0.00979413483465737</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.008667038768060149</v>
+        <v>0.008667038768060121</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.009794134834657398</v>
+        <v>0.00979413483465737</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.009794134834657398</v>
+        <v>0.00979413483465737</v>
       </c>
     </row>
     <row r="10">
@@ -4398,16 +4398,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01403155640750922</v>
+        <v>0.01403155640750921</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01474707339012438</v>
+        <v>0.01474707339012439</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01343435566469709</v>
+        <v>0.0134343556646971</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01131930929896767</v>
+        <v>0.01131930929896768</v>
       </c>
       <c r="F10" t="n">
         <v>0.01445448478989294</v>
@@ -4416,7 +4416,7 @@
         <v>0.01361924576158737</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01336764679925969</v>
+        <v>0.0133676467992597</v>
       </c>
       <c r="I10" t="n">
         <v>0.01338534787153967</v>
@@ -4428,43 +4428,43 @@
         <v>0.01330819940164876</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01379835244107295</v>
+        <v>0.01379835244107296</v>
       </c>
       <c r="M10" t="n">
         <v>0.01098355067456365</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01399958804314592</v>
+        <v>0.01399958804314593</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01415689080513135</v>
+        <v>0.01415689080513134</v>
       </c>
       <c r="P10" t="n">
         <v>0.01377790264594004</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0144057971340809</v>
+        <v>0.01440579713408091</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01368846978376541</v>
+        <v>0.01368846978376542</v>
       </c>
       <c r="S10" t="n">
         <v>0.01372799469942676</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01353934146405632</v>
+        <v>0.0135393414640563</v>
       </c>
       <c r="U10" t="n">
         <v>0.01339547426634607</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01428123894530146</v>
+        <v>0.01428123894530145</v>
       </c>
       <c r="W10" t="n">
-        <v>0.01256447969293174</v>
+        <v>0.01256447969293175</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0128287561393957</v>
+        <v>0.01282875613939571</v>
       </c>
       <c r="Y10" t="n">
         <v>0.01269493764953757</v>
@@ -4492,16 +4492,16 @@
         <v>0.01475339570491634</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01436618321489103</v>
+        <v>0.01436618321489104</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01156553013566868</v>
+        <v>0.01156553013566867</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01466359170665226</v>
+        <v>0.01466359170665227</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01435324977039012</v>
+        <v>0.01435324977039014</v>
       </c>
       <c r="H11" t="n">
         <v>0.01434923830068071</v>
@@ -4510,7 +4510,7 @@
         <v>0.01435280322145548</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01437662526270041</v>
+        <v>0.01437662526270042</v>
       </c>
       <c r="K11" t="n">
         <v>0.01433357846215279</v>
@@ -4519,13 +4519,13 @@
         <v>0.01446760473493042</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01367209362704458</v>
+        <v>0.01367209362704457</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01452607069185186</v>
+        <v>0.01452607069185188</v>
       </c>
       <c r="O11" t="n">
-        <v>0.014568849066197</v>
+        <v>0.01456884906619701</v>
       </c>
       <c r="P11" t="n">
         <v>0.0144598960687966</v>
@@ -4540,7 +4540,7 @@
         <v>0.01444674549821891</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01439613161318959</v>
+        <v>0.0143961316131896</v>
       </c>
       <c r="U11" t="n">
         <v>0.01435195314679454</v>
@@ -4552,16 +4552,16 @@
         <v>0.01411562038191132</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01410911540114715</v>
+        <v>0.01410911540114717</v>
       </c>
       <c r="Y11" t="n">
         <v>0.0141533914521486</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.01457052826063835</v>
+        <v>0.01457052826063837</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.01423363030551128</v>
+        <v>0.01423363030551129</v>
       </c>
       <c r="AB11" t="n">
         <v>0.01396424406679623</v>
@@ -4730,85 +4730,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01482329569039123</v>
+        <v>0.01482329569039124</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01474780946811987</v>
+        <v>0.01474780946811988</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01485848340217643</v>
+        <v>0.01485848340217646</v>
       </c>
       <c r="E2" t="n">
         <v>0.0117981094404065</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01481124337918021</v>
+        <v>0.01481124337918022</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01472318318154745</v>
+        <v>0.01472318318154748</v>
       </c>
       <c r="H2" t="n">
         <v>0.01494298119261768</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01493079699016386</v>
+        <v>0.01493079699016388</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01492298478570867</v>
+        <v>0.01492298478570869</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01503363856839562</v>
+        <v>0.01503363856839565</v>
       </c>
       <c r="L2" t="n">
         <v>0.01486236043254226</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01525483401110639</v>
+        <v>0.01525483401110641</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0148000712386271</v>
+        <v>0.01480007123862711</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01482112483973913</v>
+        <v>0.01482112483973915</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01486602175473995</v>
+        <v>0.01486602175473996</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01478478944273648</v>
+        <v>0.01478478944273649</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01487975921287949</v>
+        <v>0.0148797592128795</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01488360855938838</v>
+        <v>0.01488360855938841</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01494642757031576</v>
+        <v>0.01494642757031578</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01496877430686018</v>
+        <v>0.01496877430686019</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01475761697382478</v>
+        <v>0.0147576169738248</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0150407570688655</v>
+        <v>0.01504075706886551</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01501877467903831</v>
+        <v>0.01501877467903832</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01526267805029639</v>
+        <v>0.0152626780502964</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01480307840613611</v>
+        <v>0.01480307840613612</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01503445062739495</v>
+        <v>0.01503445062739496</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01491506854743797</v>
+        <v>0.01491506854743799</v>
       </c>
     </row>
     <row r="3">
@@ -4818,85 +4818,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01492930794052339</v>
+        <v>0.01492930794052341</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01495162629847369</v>
+        <v>0.01495162629847371</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01492930794052339</v>
+        <v>0.01492930794052341</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01193910245516512</v>
+        <v>0.01193910245516514</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01494373983112848</v>
+        <v>0.0149437398311285</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01476055686255337</v>
+        <v>0.01476055686255339</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01492930794052339</v>
+        <v>0.01492930794052341</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01492930794052339</v>
+        <v>0.01492930794052341</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01492759461797794</v>
+        <v>0.01492759461797796</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01493683439088893</v>
+        <v>0.01493683439088895</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01492930794052339</v>
+        <v>0.01492930794052341</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01492909720559425</v>
+        <v>0.01492909720559427</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01492930794052339</v>
+        <v>0.01492930794052341</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01492920089073543</v>
+        <v>0.01492920089073545</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0149287240844918</v>
+        <v>0.01492872408449183</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01492930675142751</v>
+        <v>0.01492930675142753</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01488632857785673</v>
+        <v>0.01488632857785675</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01492930794052339</v>
+        <v>0.01492930794052341</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01492915377976482</v>
+        <v>0.01492915377976484</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01492916938694449</v>
+        <v>0.01492916938694452</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01482726416306045</v>
+        <v>0.01482726416306042</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01492930794052339</v>
+        <v>0.01492930794052341</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01486773344088908</v>
+        <v>0.0148677334408891</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01492890218404065</v>
+        <v>0.01492890218404067</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01493088108683014</v>
+        <v>0.01493088108683016</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01492930794052339</v>
+        <v>0.01492930794052341</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01476581022195329</v>
+        <v>0.01476581022195331</v>
       </c>
     </row>
     <row r="4">
@@ -4906,85 +4906,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03851139415107899</v>
+        <v>0.03851139415107916</v>
       </c>
       <c r="C4" t="n">
         <v>0.01773764480647229</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05089079045859253</v>
+        <v>0.0508907904585927</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02053935251235052</v>
+        <v>0.02053935251235058</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03653173798799984</v>
+        <v>0.03653173798799972</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05055134312375239</v>
+        <v>0.05055134312375235</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07905492284203057</v>
+        <v>0.07905492284203067</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07169978093036609</v>
+        <v>0.07169978093036611</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06549886180580453</v>
+        <v>0.06549886180580439</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0868811628774086</v>
+        <v>0.08688116287740875</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04962588692795038</v>
+        <v>0.04962588692795045</v>
       </c>
       <c r="M4" t="n">
         <v>0.1526400878269775</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03696125958467312</v>
+        <v>0.03696125958467313</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03745279111798577</v>
+        <v>0.03745279111798575</v>
       </c>
       <c r="P4" t="n">
-        <v>0.04799659970015995</v>
+        <v>0.04799659970015978</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03165025241360638</v>
+        <v>0.03165025241360637</v>
       </c>
       <c r="R4" t="n">
-        <v>0.07092327459208785</v>
+        <v>0.07092327459208796</v>
       </c>
       <c r="S4" t="n">
-        <v>0.05328023882262267</v>
+        <v>0.05328023882262273</v>
       </c>
       <c r="T4" t="n">
-        <v>0.07678594710664005</v>
+        <v>0.07678594710664027</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07337353094615055</v>
+        <v>0.07337353094615059</v>
       </c>
       <c r="V4" t="n">
-        <v>0.04534154883288279</v>
+        <v>0.04534154883288261</v>
       </c>
       <c r="W4" t="n">
-        <v>0.09745756465962419</v>
+        <v>0.097457564659624</v>
       </c>
       <c r="X4" t="n">
-        <v>0.104855821290987</v>
+        <v>0.1048558212909867</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1553187362441718</v>
+        <v>0.1553187362441719</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03146715997090001</v>
+        <v>0.03146715997090008</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.09627553756038837</v>
+        <v>0.09627553756038831</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1119033573747458</v>
+        <v>0.1119033573747456</v>
       </c>
     </row>
     <row r="5">
@@ -4994,85 +4994,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002077500884399383</v>
+        <v>0.00207750088439941</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002077500884399379</v>
+        <v>0.002077500884399415</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002077500884399379</v>
+        <v>0.002077500884399415</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002077500884399379</v>
+        <v>0.002077500884399415</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002077500884399377</v>
+        <v>0.002077500884399394</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002077500884399379</v>
+        <v>0.002077500884399415</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002077500884399379</v>
+        <v>0.002077500884399415</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002077500884399379</v>
+        <v>0.002077500884399415</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002075748678973627</v>
+        <v>0.002075748678973643</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002077500884399379</v>
+        <v>0.002077500884399415</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002077500884399382</v>
+        <v>0.002077500884399417</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002077500884399379</v>
+        <v>0.002077500884399415</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03696125958467312</v>
+        <v>0.002077500884399394</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002077500884399377</v>
+        <v>0.002077500884399394</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002077500884399377</v>
+        <v>0.002077500884399394</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002077500884399377</v>
+        <v>0.002077500884399394</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002077500884399379</v>
+        <v>0.002077500884399415</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002077500884399379</v>
+        <v>0.002077500884399415</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002077500884399379</v>
+        <v>0.002077500884399415</v>
       </c>
       <c r="U5" t="n">
-        <v>0.00202010231135729</v>
+        <v>0.002020102311357319</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002066510624606595</v>
+        <v>0.002066510624606573</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002077500884399377</v>
+        <v>0.002077500884399394</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002077500884399383</v>
+        <v>0.002077500884399394</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.00202010231135729</v>
+        <v>0.002020102311357319</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002077500884399379</v>
+        <v>0.002077500884399415</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002077500884399379</v>
+        <v>0.002077500884399415</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.002077500884399377</v>
+        <v>0.002077500884399394</v>
       </c>
     </row>
     <row r="6">
@@ -5082,85 +5082,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.003211926363609324</v>
+        <v>0.003211926363609326</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003211926363609324</v>
+        <v>0.003211926363609326</v>
       </c>
       <c r="D6" t="n">
-        <v>0.005075514687823212</v>
+        <v>0.005075514687823266</v>
       </c>
       <c r="E6" t="n">
-        <v>0.005075514687823212</v>
+        <v>0.005075514687823266</v>
       </c>
       <c r="F6" t="n">
-        <v>0.003211926363609324</v>
+        <v>0.003211926363609326</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003211926363609324</v>
+        <v>0.003211926363609326</v>
       </c>
       <c r="H6" t="n">
-        <v>0.005075514687823212</v>
+        <v>0.005075514687823266</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003211926363609324</v>
+        <v>0.003211926363609326</v>
       </c>
       <c r="J6" t="n">
-        <v>0.005073762482397451</v>
+        <v>0.00507376248239746</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005075514687823212</v>
+        <v>0.005075514687823266</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003211926363609324</v>
+        <v>0.003211926363609326</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003211926363609324</v>
+        <v>0.003211926363609326</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03696125958467312</v>
+        <v>0.003236546961140033</v>
       </c>
       <c r="O6" t="n">
-        <v>0.003512707192045795</v>
+        <v>0.003512707192045812</v>
       </c>
       <c r="P6" t="n">
-        <v>0.005107957223510093</v>
+        <v>0.005107957223510128</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.005075514687823212</v>
+        <v>0.005075514687823266</v>
       </c>
       <c r="R6" t="n">
-        <v>0.005075514687823212</v>
+        <v>0.005075514687823266</v>
       </c>
       <c r="S6" t="n">
-        <v>0.003211926363609324</v>
+        <v>0.003211926363609326</v>
       </c>
       <c r="T6" t="n">
-        <v>0.005075514687823212</v>
+        <v>0.005075514687823266</v>
       </c>
       <c r="U6" t="n">
-        <v>0.005075514687823212</v>
+        <v>0.005075514687823266</v>
       </c>
       <c r="V6" t="n">
-        <v>0.003200936103816541</v>
+        <v>0.00320093610381649</v>
       </c>
       <c r="W6" t="n">
-        <v>0.00334955058904302</v>
+        <v>0.003349550589043034</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003211926363609324</v>
+        <v>0.003211926363609326</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.003352718126980268</v>
+        <v>0.003352718126980214</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.003211926363609324</v>
+        <v>0.003211926363609326</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.005075514687823212</v>
+        <v>0.005075514687823266</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003238756344402246</v>
+        <v>0.003238756344402279</v>
       </c>
     </row>
     <row r="7">
@@ -5170,85 +5170,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.003812477391489739</v>
+        <v>0.003812477391489761</v>
       </c>
       <c r="C7" t="n">
-        <v>0.003812477391489733</v>
+        <v>0.00381247739148976</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003812477391489733</v>
+        <v>0.00381247739148976</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003812477391489733</v>
+        <v>0.00381247739148976</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003812477391489733</v>
+        <v>0.00381247739148976</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003812477391489733</v>
+        <v>0.00381247739148976</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003812477391489733</v>
+        <v>0.00381247739148976</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003812477391489733</v>
+        <v>0.00381247739148976</v>
       </c>
       <c r="J7" t="n">
-        <v>0.003810725186063978</v>
+        <v>0.00381072518606399</v>
       </c>
       <c r="K7" t="n">
-        <v>0.003812477391489733</v>
+        <v>0.00381247739148976</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003812477391489739</v>
+        <v>0.003812477391489761</v>
       </c>
       <c r="M7" t="n">
-        <v>0.003812477391489733</v>
+        <v>0.00381247739148976</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03696125958467312</v>
+        <v>0.00381247739148976</v>
       </c>
       <c r="O7" t="n">
-        <v>0.003812340256907019</v>
+        <v>0.003812340256907042</v>
       </c>
       <c r="P7" t="n">
-        <v>0.003812340256907019</v>
+        <v>0.003812340256907042</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.003812477391489733</v>
+        <v>0.00381247739148976</v>
       </c>
       <c r="R7" t="n">
-        <v>0.003812477391489733</v>
+        <v>0.00381247739148976</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003812477391489733</v>
+        <v>0.00381247739148976</v>
       </c>
       <c r="T7" t="n">
-        <v>0.003812477391489733</v>
+        <v>0.00381247739148976</v>
       </c>
       <c r="U7" t="n">
-        <v>0.003810429414981242</v>
+        <v>0.003810429414981244</v>
       </c>
       <c r="V7" t="n">
-        <v>0.003801487131696954</v>
+        <v>0.003801487131696917</v>
       </c>
       <c r="W7" t="n">
-        <v>0.003812477391489733</v>
+        <v>0.00381247739148976</v>
       </c>
       <c r="X7" t="n">
-        <v>0.003812477391489739</v>
+        <v>0.003812477391489761</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.003812477391489733</v>
+        <v>0.00381247739148976</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.003812477391489733</v>
+        <v>0.00381247739148976</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.003812477391489733</v>
+        <v>0.00381247739148976</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.003812477391489733</v>
+        <v>0.00381247739148976</v>
       </c>
     </row>
     <row r="8">
@@ -5258,85 +5258,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.005779273428680686</v>
+        <v>0.005779273428680692</v>
       </c>
       <c r="C8" t="n">
-        <v>0.008684175640668397</v>
+        <v>0.00868417564066841</v>
       </c>
       <c r="D8" t="n">
-        <v>0.008684175640668397</v>
+        <v>0.00868417564066841</v>
       </c>
       <c r="E8" t="n">
-        <v>0.007137400903030897</v>
+        <v>0.007137400903030912</v>
       </c>
       <c r="F8" t="n">
-        <v>0.006231823242497537</v>
+        <v>0.006231823242497542</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009286526037647352</v>
+        <v>0.009286526037647356</v>
       </c>
       <c r="H8" t="n">
-        <v>0.008684175640668397</v>
+        <v>0.00868417564066841</v>
       </c>
       <c r="I8" t="n">
-        <v>0.008684175640668397</v>
+        <v>0.00868417564066841</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00868242343524264</v>
+        <v>0.008682423435242639</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008684175640668397</v>
+        <v>0.00868417564066841</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008684175640668401</v>
+        <v>0.008684175640668411</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008684175640669848</v>
+        <v>0.008684175640669858</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03696125958467312</v>
+        <v>0.006432390445661072</v>
       </c>
       <c r="O8" t="n">
-        <v>0.007051200566721626</v>
+        <v>0.007051200566721639</v>
       </c>
       <c r="P8" t="n">
-        <v>0.006899515253762017</v>
+        <v>0.006899515253762033</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.005208393844212802</v>
+        <v>0.005208393844212829</v>
       </c>
       <c r="R8" t="n">
-        <v>0.008684175640668397</v>
+        <v>0.00868417564066841</v>
       </c>
       <c r="S8" t="n">
-        <v>0.008684175640668397</v>
+        <v>0.00868417564066841</v>
       </c>
       <c r="T8" t="n">
-        <v>0.008684175640668397</v>
+        <v>0.00868417564066841</v>
       </c>
       <c r="U8" t="n">
-        <v>0.007264850783916286</v>
+        <v>0.007264850783916282</v>
       </c>
       <c r="V8" t="n">
-        <v>0.007877598462578869</v>
+        <v>0.007877598462578864</v>
       </c>
       <c r="W8" t="n">
-        <v>0.00868474653249646</v>
+        <v>0.008684746532496465</v>
       </c>
       <c r="X8" t="n">
-        <v>0.005474633901161308</v>
+        <v>0.00547463390116133</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01156992047576788</v>
+        <v>0.01156992047576789</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.005725313379181385</v>
+        <v>0.005725313379181413</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.008684175640668397</v>
+        <v>0.00868417564066841</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0117185889005783</v>
+        <v>0.01171858890057832</v>
       </c>
     </row>
     <row r="9">
@@ -5346,85 +5346,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.007505480251263606</v>
+        <v>0.007505480251263617</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009247240978848353</v>
+        <v>0.009247240978848392</v>
       </c>
       <c r="D9" t="n">
-        <v>0.009247240978848353</v>
+        <v>0.009247240978848392</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008845249363965845</v>
+        <v>0.008845249363965871</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005232007712998268</v>
+        <v>0.005232007712998291</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009247240532323722</v>
+        <v>0.009247240532323725</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009247240978848353</v>
+        <v>0.009247240978848392</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009247240978848353</v>
+        <v>0.009247240978848392</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009245488773422616</v>
+        <v>0.009245488773422607</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009247240978848353</v>
+        <v>0.009247240978848392</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009247240978848353</v>
+        <v>0.009247240978848392</v>
       </c>
       <c r="M9" t="n">
-        <v>0.009247240978848353</v>
+        <v>0.009247240978848392</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03696125958467312</v>
+        <v>0.009247240978848392</v>
       </c>
       <c r="O9" t="n">
-        <v>0.009824457608826612</v>
+        <v>0.009824457608826626</v>
       </c>
       <c r="P9" t="n">
         <v>0.009949992419588789</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.009247240532323722</v>
+        <v>0.009247240532323725</v>
       </c>
       <c r="R9" t="n">
-        <v>0.009247240978848353</v>
+        <v>0.009247240978848392</v>
       </c>
       <c r="S9" t="n">
-        <v>0.009247240978848353</v>
+        <v>0.009247240978848392</v>
       </c>
       <c r="T9" t="n">
-        <v>0.009247240978848353</v>
+        <v>0.009247240978848392</v>
       </c>
       <c r="U9" t="n">
-        <v>0.009247240978848353</v>
+        <v>0.009247240978848392</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01124620263133362</v>
+        <v>0.01124620263133356</v>
       </c>
       <c r="W9" t="n">
-        <v>0.009247240978848353</v>
+        <v>0.009247240978848392</v>
       </c>
       <c r="X9" t="n">
-        <v>0.009247240978848353</v>
+        <v>0.009247240978848392</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.009247240978848353</v>
+        <v>0.009247240978848392</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.008197113966211783</v>
+        <v>0.008197113966211799</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.009247240978848353</v>
+        <v>0.009247240978848392</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.009247240978848353</v>
+        <v>0.009247240978848392</v>
       </c>
     </row>
     <row r="10">
@@ -5434,85 +5434,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01399746581811066</v>
+        <v>0.01399746581811069</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01459538477583588</v>
+        <v>0.01459538477583591</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01380574057330124</v>
+        <v>0.01380574057330129</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01149239198098598</v>
+        <v>0.011492391980986</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01417789935456665</v>
+        <v>0.01417789935456668</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01350758365522901</v>
+        <v>0.01350758365522902</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01332172217803655</v>
+        <v>0.01332172217803657</v>
       </c>
       <c r="I10" t="n">
         <v>0.01338506166996187</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01340785180861226</v>
+        <v>0.01340785180861228</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01282458419197046</v>
+        <v>0.01282458419197048</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0137723828471339</v>
+        <v>0.01377238284713392</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01149585251266514</v>
+        <v>0.01149585251266516</v>
       </c>
       <c r="N10" t="n">
         <v>0.01414457660233143</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01400868780710186</v>
+        <v>0.01400868780710188</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01373716623617393</v>
+        <v>0.01373716623617395</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01423562281206363</v>
+        <v>0.01423562281206365</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01341391271549316</v>
+        <v>0.01341391271549317</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01364264567113271</v>
+        <v>0.01364264567113274</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01329066790343415</v>
+        <v>0.01329066790343416</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01314060814424814</v>
+        <v>0.01314060814424815</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01368866390163825</v>
+        <v>0.01368866390163823</v>
       </c>
       <c r="W10" t="n">
-        <v>0.01272142420463365</v>
+        <v>0.01272142420463367</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01247335765992783</v>
+        <v>0.01247335765992784</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.01141474544120177</v>
+        <v>0.0114147454412018</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01412875954585167</v>
+        <v>0.01412875954585168</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.01276041086799108</v>
+        <v>0.0127604108679911</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.01243616145037352</v>
+        <v>0.01243616145037353</v>
       </c>
     </row>
     <row r="11">
@@ -5522,85 +5522,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01439930455508879</v>
+        <v>0.0143993045550888</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01458571844004532</v>
+        <v>0.01458571844004533</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0143472566694936</v>
+        <v>0.01434725666949362</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01159485475107318</v>
+        <v>0.01159485475107319</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01446278352175579</v>
+        <v>0.01446278352175582</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01415307637922619</v>
+        <v>0.01415307637922621</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0142115245476143</v>
+        <v>0.01421152454761431</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0142281600158375</v>
+        <v>0.01422816001583751</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01423149696431432</v>
+        <v>0.01423149696431433</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01407255799654574</v>
+        <v>0.01407255799654576</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01433595582814853</v>
+        <v>0.01433595582814855</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01369269673472197</v>
+        <v>0.01369269673472198</v>
       </c>
       <c r="N11" t="n">
         <v>0.01444301597895936</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0144022884531847</v>
+        <v>0.01440228845318473</v>
       </c>
       <c r="P11" t="n">
-        <v>0.01432385913648576</v>
+        <v>0.01432385913648577</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01446916103968637</v>
+        <v>0.01446916103968639</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01420980530319312</v>
+        <v>0.01420980530319313</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01429817312646627</v>
+        <v>0.01429817312646629</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01420091127504064</v>
+        <v>0.01420091127504067</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01415497324162685</v>
+        <v>0.01415497324162687</v>
       </c>
       <c r="V11" t="n">
-        <v>0.01423955022637396</v>
+        <v>0.01423955022637397</v>
       </c>
       <c r="W11" t="n">
         <v>0.01403616293292768</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01392932606827808</v>
+        <v>0.0139293260682781</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01366372553335164</v>
+        <v>0.01366372553335165</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.01443811054878122</v>
+        <v>0.01443811054878124</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.01404759554752789</v>
+        <v>0.01404759554752791</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.01385507093221904</v>
+        <v>0.01385507093221906</v>
       </c>
     </row>
   </sheetData>
@@ -6066,7 +6066,7 @@
         <v>0.001960855897600812</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04921252722493448</v>
+        <v>0.001960855897600818</v>
       </c>
       <c r="O5" t="n">
         <v>0.001960855897600818</v>
@@ -6154,7 +6154,7 @@
         <v>0.004796500664090021</v>
       </c>
       <c r="N6" t="n">
-        <v>0.04921252722493448</v>
+        <v>0.002994506879989262</v>
       </c>
       <c r="O6" t="n">
         <v>0.004844652437926765</v>
@@ -6242,7 +6242,7 @@
         <v>0.003672438444028841</v>
       </c>
       <c r="N7" t="n">
-        <v>0.04921252722493448</v>
+        <v>0.003672438444028841</v>
       </c>
       <c r="O7" t="n">
         <v>0.003672296704946088</v>
@@ -6330,7 +6330,7 @@
         <v>0.008586248738889996</v>
       </c>
       <c r="N8" t="n">
-        <v>0.04921252722493448</v>
+        <v>0.006321172602777357</v>
       </c>
       <c r="O8" t="n">
         <v>0.006943635189699836</v>
@@ -6418,7 +6418,7 @@
         <v>0.009876492498674679</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04921252722493448</v>
+        <v>0.009876492498674679</v>
       </c>
       <c r="O9" t="n">
         <v>0.01050908605837788</v>
@@ -6853,7 +6853,7 @@
         <v>0.01467301257570373</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01468286090883302</v>
+        <v>0.01468286090883301</v>
       </c>
       <c r="T2" t="n">
         <v>0.01465793264977557</v>
@@ -6950,7 +6950,7 @@
         <v>0.01486631342883351</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01485389144510181</v>
+        <v>0.01485389144510182</v>
       </c>
       <c r="W3" t="n">
         <v>0.01486663079813582</v>
@@ -7053,7 +7053,7 @@
         <v>0.02315367168000727</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0452478425054798</v>
+        <v>0.04524784250547981</v>
       </c>
       <c r="AB4" t="n">
         <v>0.007158553952097387</v>
@@ -7102,7 +7102,7 @@
         <v>0.001870106528912957</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02176779031444049</v>
+        <v>0.001870106528912952</v>
       </c>
       <c r="O5" t="n">
         <v>0.001870106528912952</v>
@@ -7190,7 +7190,7 @@
         <v>0.004518621970085927</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02176779031444049</v>
+        <v>0.00287707749848027</v>
       </c>
       <c r="O6" t="n">
         <v>0.004550457788019486</v>
@@ -7278,7 +7278,7 @@
         <v>0.003374882034672509</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02176779031444049</v>
+        <v>0.003374882034672509</v>
       </c>
       <c r="O7" t="n">
         <v>0.003374748941304667</v>
@@ -7366,7 +7366,7 @@
         <v>0.007724645276980741</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02176779031444049</v>
+        <v>0.005719744626054038</v>
       </c>
       <c r="O8" t="n">
         <v>0.006270708730779109</v>
@@ -7402,7 +7402,7 @@
         <v>0.01029397390851761</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.005090191117324314</v>
+        <v>0.005090191117324313</v>
       </c>
       <c r="AA8" t="n">
         <v>0.007724645276981024</v>
@@ -7454,7 +7454,7 @@
         <v>0.008491558200263453</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02176779031444049</v>
+        <v>0.008491558200263453</v>
       </c>
       <c r="O9" t="n">
         <v>0.009024558064980306</v>
@@ -7545,7 +7545,7 @@
         <v>0.01439877492578189</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01441931502162321</v>
+        <v>0.01441931502162322</v>
       </c>
       <c r="P10" t="n">
         <v>0.01450001051412481</v>
@@ -8050,7 +8050,7 @@
         <v>0.01270639473611442</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01703527514673334</v>
+        <v>0.01703527514673335</v>
       </c>
       <c r="O4" t="n">
         <v>0.02862854351444533</v>
@@ -8138,7 +8138,7 @@
         <v>0.001871288949439491</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01703527514673335</v>
+        <v>0.001871288949439497</v>
       </c>
       <c r="O5" t="n">
         <v>0.001871288949439497</v>
@@ -8226,7 +8226,7 @@
         <v>0.004540652626964973</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01703527514673334</v>
+        <v>0.002900629706759018</v>
       </c>
       <c r="O6" t="n">
         <v>0.003176930001974847</v>
@@ -8314,7 +8314,7 @@
         <v>0.003353774503127769</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01703527514673334</v>
+        <v>0.003353774503127769</v>
       </c>
       <c r="O7" t="n">
         <v>0.003353640888224373</v>
@@ -8402,7 +8402,7 @@
         <v>0.007647843942282309</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01703527514673334</v>
+        <v>0.005668926925824927</v>
       </c>
       <c r="O8" t="n">
         <v>0.006212750502199213</v>
@@ -8490,7 +8490,7 @@
         <v>0.007981005199212243</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01703527514673334</v>
+        <v>0.007981005199212243</v>
       </c>
       <c r="O9" t="n">
         <v>0.008476669667727492</v>
@@ -9174,7 +9174,7 @@
         <v>0.002076588312473238</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0873225832696008</v>
+        <v>0.002076588312473239</v>
       </c>
       <c r="O5" t="n">
         <v>0.002076588312473239</v>
@@ -9262,7 +9262,7 @@
         <v>0.003141656298093669</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0873225832696008</v>
+        <v>0.0031550150544542</v>
       </c>
       <c r="O6" t="n">
         <v>0.005190257502206409</v>
@@ -9350,7 +9350,7 @@
         <v>0.00394360764614151</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0873225832696008</v>
+        <v>0.00394360764614151</v>
       </c>
       <c r="O7" t="n">
         <v>0.003943463606734844</v>
@@ -9438,7 +9438,7 @@
         <v>0.009212318969463345</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0873225832696008</v>
+        <v>0.006778254804009744</v>
       </c>
       <c r="O8" t="n">
         <v>0.007447156768657264</v>
@@ -9526,7 +9526,7 @@
         <v>0.01096661574301863</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0873225832696008</v>
+        <v>0.01096661574301863</v>
       </c>
       <c r="O9" t="n">
         <v>0.01167280859795378</v>
@@ -10210,7 +10210,7 @@
         <v>0.001937703789982629</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02654541252911471</v>
+        <v>0.001937703789982629</v>
       </c>
       <c r="O5" t="n">
         <v>0.001937703789982629</v>
@@ -10298,7 +10298,7 @@
         <v>0.002943743844225772</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02654541252911471</v>
+        <v>0.002955505869915252</v>
       </c>
       <c r="O6" t="n">
         <v>0.004819836688972465</v>
@@ -10386,7 +10386,7 @@
         <v>0.003535020975200229</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02654541252911471</v>
+        <v>0.003535020975200229</v>
       </c>
       <c r="O7" t="n">
         <v>0.003534886691862156</v>
@@ -10474,7 +10474,7 @@
         <v>0.008131906802266022</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02654541252911471</v>
+        <v>0.00601313978652835</v>
       </c>
       <c r="O8" t="n">
         <v>0.006595395356959166</v>
@@ -10562,7 +10562,7 @@
         <v>0.009155238574217977</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02654541252911471</v>
+        <v>0.009155238574217977</v>
       </c>
       <c r="O9" t="n">
         <v>0.009733791742792102</v>

--- a/Results/Phase 2/Hydrogen/hydrogen photochemical ozone formation results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen photochemical ozone formation results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01530378598199597</v>
+        <v>0.01530378598199596</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01508256886567774</v>
+        <v>0.01508256886567773</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01529400785761019</v>
+        <v>0.01529400785761018</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01192710517157435</v>
+        <v>0.01192710517157437</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01521612464380034</v>
+        <v>0.01521612464380032</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01527447810804685</v>
+        <v>0.01527447810804684</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01546110718722978</v>
+        <v>0.01546110718722979</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01532821777022707</v>
+        <v>0.01532821777022706</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01530619031499761</v>
+        <v>0.01530619031499759</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01555665814902901</v>
+        <v>0.015556658149029</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0153218841569593</v>
+        <v>0.01532188415695928</v>
       </c>
       <c r="M2" t="n">
         <v>0.01589982871939944</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01540327707475968</v>
+        <v>0.01540327707475966</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01529147399167292</v>
+        <v>0.01529147399167291</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01522750232765749</v>
+        <v>0.01522750232765748</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01520860633250296</v>
+        <v>0.01520860633250294</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01531803872015662</v>
+        <v>0.01531803872015661</v>
       </c>
       <c r="S2" t="n">
         <v>0.01527995881772454</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01543426909400806</v>
+        <v>0.01543426909400805</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01546610352298897</v>
+        <v>0.01546610352298896</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01525771503392689</v>
+        <v>0.01525771503392688</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01541736265809591</v>
+        <v>0.0154173626580959</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01523152831227799</v>
+        <v>0.01523152831227798</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01529926653876313</v>
+        <v>0.01529926653876312</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01521235749708627</v>
+        <v>0.01521235749708626</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01542484918503667</v>
+        <v>0.01542484918503665</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01550450747516449</v>
+        <v>0.01550450747516448</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01527800440070882</v>
+        <v>0.0152780044007088</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01527800440070882</v>
+        <v>0.0152780044007088</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01527800440070882</v>
+        <v>0.0152780044007088</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01203476883136883</v>
+        <v>0.01203476883136885</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01527800440070882</v>
+        <v>0.0152780044007088</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01527800440070882</v>
+        <v>0.0152780044007088</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01527800440070882</v>
+        <v>0.0152780044007088</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01527800440070882</v>
+        <v>0.0152780044007088</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01527272726318449</v>
+        <v>0.01527272726318448</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01527800440070882</v>
+        <v>0.0152780044007088</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01527800440070882</v>
+        <v>0.0152780044007088</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01527800440070882</v>
+        <v>0.0152780044007088</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01527800440070882</v>
+        <v>0.0152780044007088</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01527800440070882</v>
+        <v>0.0152780044007088</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01527800440070882</v>
+        <v>0.0152780044007088</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01527800440070882</v>
+        <v>0.0152780044007088</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01527800440070882</v>
+        <v>0.0152780044007088</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01527800440070882</v>
+        <v>0.0152780044007088</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01527800440070882</v>
+        <v>0.0152780044007088</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01527800440070882</v>
+        <v>0.0152780044007088</v>
       </c>
       <c r="V3" t="n">
         <v>0.01535639172582086</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01527800440070882</v>
+        <v>0.0152780044007088</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01527800440070882</v>
+        <v>0.0152780044007088</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01527800440070882</v>
+        <v>0.0152780044007088</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01527800440070882</v>
+        <v>0.0152780044007088</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01527800440070882</v>
+        <v>0.0152780044007088</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01527800440070882</v>
+        <v>0.0152780044007088</v>
       </c>
     </row>
     <row r="4">
@@ -762,82 +762,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08161611370377675</v>
+        <v>0.0816161137037765</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0242569933735703</v>
+        <v>0.02425699337357032</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08884024412673586</v>
+        <v>0.088840244126736</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03422652335168194</v>
+        <v>0.03422652335168189</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06649120094640201</v>
+        <v>0.06649120094640196</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07577617408227698</v>
+        <v>0.07577617408227692</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1450685405011857</v>
+        <v>0.1450685405011856</v>
       </c>
       <c r="I4" t="n">
         <v>0.1003057945820664</v>
       </c>
       <c r="J4" t="n">
-        <v>0.08934244378449133</v>
+        <v>0.0893424437844913</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1675063758541146</v>
+        <v>0.1675063758541144</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09245044916174727</v>
+        <v>0.09245044916174514</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2757258466819039</v>
+        <v>0.2757258466819042</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1187620068051895</v>
+        <v>0.1187620068051897</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07659370840619169</v>
+        <v>0.07659370840619187</v>
       </c>
       <c r="P4" t="n">
-        <v>0.06212856709802995</v>
+        <v>0.06212856709802979</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.06162435212510493</v>
+        <v>0.06162435212510477</v>
       </c>
       <c r="R4" t="n">
-        <v>0.09834123829477752</v>
+        <v>0.09834123829477744</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0774090172090999</v>
+        <v>0.07740901720909975</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1319963029965943</v>
+        <v>0.1319963029965948</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1315422794553987</v>
+        <v>0.1315422794553986</v>
       </c>
       <c r="V4" t="n">
-        <v>0.04899618214232631</v>
+        <v>0.0489961821423261</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1209000731044013</v>
+        <v>0.1209000731044012</v>
       </c>
       <c r="X4" t="n">
         <v>0.06894944315384444</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.08653040090870812</v>
+        <v>0.08653040090870821</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.05852354798682671</v>
+        <v>0.05852354798682687</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1238820345535785</v>
+        <v>0.1238820345535783</v>
       </c>
       <c r="AB4" t="n">
         <v>0.1601122246824773</v>
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007016725355051115</v>
+        <v>0.007016725355051118</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01067311886583001</v>
+        <v>0.01067311886582997</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01067311886583001</v>
+        <v>0.01067311886582997</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008726197179345377</v>
+        <v>0.008726197179345405</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007586348730275115</v>
+        <v>0.007586348730275104</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01143129587906968</v>
+        <v>0.01143129587906967</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01067311886583001</v>
+        <v>0.01067311886582997</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01067311886583001</v>
+        <v>0.01067311886582997</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0106712821051282</v>
+        <v>0.01067128210512818</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01067311886583001</v>
+        <v>0.01067311886582997</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01067311886583001</v>
+        <v>0.01067311886582997</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01067311886583013</v>
+        <v>0.01067311886583009</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1187620068051895</v>
+        <v>0.007838802192321973</v>
       </c>
       <c r="O5" t="n">
-        <v>0.008617697021330414</v>
+        <v>0.008617697021330398</v>
       </c>
       <c r="P5" t="n">
-        <v>0.008426771078304418</v>
+        <v>0.008426771078304434</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.006298160578624655</v>
+        <v>0.006298160578624624</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01067311886583001</v>
+        <v>0.01067311886582997</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01067311886583001</v>
+        <v>0.01067311886582997</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01067311886583001</v>
+        <v>0.01067311886582997</v>
       </c>
       <c r="U5" t="n">
-        <v>0.008887629322647623</v>
+        <v>0.008887629322647611</v>
       </c>
       <c r="V5" t="n">
-        <v>0.009661589362275822</v>
+        <v>0.009661589362275826</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0106738374465013</v>
+        <v>0.01067383744650129</v>
       </c>
       <c r="X5" t="n">
-        <v>0.006633276305891691</v>
+        <v>0.00663327630589168</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01430712903907816</v>
+        <v>0.01430712903907813</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.006948805968930344</v>
+        <v>0.006948805968930351</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01067311886583001</v>
+        <v>0.01067311886582997</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01449252762531312</v>
+        <v>0.01449252762531311</v>
       </c>
     </row>
     <row r="6">
@@ -947,13 +947,13 @@
         <v>0.01363463266959804</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01301600700990141</v>
+        <v>0.01301600700990137</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007455585955737485</v>
+        <v>0.007455585955737462</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01363463160577547</v>
+        <v>0.01363463160577544</v>
       </c>
       <c r="H6" t="n">
         <v>0.01363463266959804</v>
@@ -962,7 +962,7 @@
         <v>0.01363463266959804</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01363279590889624</v>
+        <v>0.0136327959088962</v>
       </c>
       <c r="K6" t="n">
         <v>0.01363463266959804</v>
@@ -974,16 +974,16 @@
         <v>0.01363463266959804</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1187620068051895</v>
+        <v>0.01363463266959804</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01452291152033634</v>
+        <v>0.0145229115203363</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01471609716143667</v>
+        <v>0.01471609716143662</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01363463160577547</v>
+        <v>0.01363463160577544</v>
       </c>
       <c r="R6" t="n">
         <v>0.01363463266959804</v>
@@ -998,7 +998,7 @@
         <v>0.01363463266959804</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01671650748799233</v>
+        <v>0.01671650748799232</v>
       </c>
       <c r="W6" t="n">
         <v>0.01363463266959804</v>
@@ -1010,7 +1010,7 @@
         <v>0.01363463266959804</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0120185908225131</v>
+        <v>0.01201859082251308</v>
       </c>
       <c r="AA6" t="n">
         <v>0.01363463266959804</v>
@@ -1032,79 +1032,79 @@
         <v>0.01485757358979809</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01361955248410089</v>
+        <v>0.01361955248410088</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01138775782132361</v>
+        <v>0.0113877578213236</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01408163385471937</v>
+        <v>0.01408163385471936</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01371062929923246</v>
+        <v>0.01371062929923244</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01265856340865295</v>
+        <v>0.01265856340865292</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01342265068266299</v>
+        <v>0.01342265068266297</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01349794716700267</v>
+        <v>0.01349794716700266</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01207653459814762</v>
+        <v>0.0120765345981476</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01343935499836266</v>
+        <v>0.01343935499836268</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0100907067677977</v>
+        <v>0.01009070676779769</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01296977087366752</v>
+        <v>0.01296977087366751</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01360682426880799</v>
+        <v>0.01360682426880798</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01398666915804991</v>
+        <v>0.01398666915804989</v>
       </c>
       <c r="Q7" t="n">
         <v>0.01411682715713804</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01348588937616451</v>
+        <v>0.01348588937616449</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01368209995875941</v>
+        <v>0.01368209995875942</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01279954399498273</v>
+        <v>0.01279954399498272</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01258406433149289</v>
+        <v>0.01258406433149288</v>
       </c>
       <c r="V7" t="n">
         <v>0.01434685170886837</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01287891472797399</v>
+        <v>0.01287891472797398</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01398428242546647</v>
+        <v>0.01398428242546648</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01357866734781818</v>
+        <v>0.01357866734781817</v>
       </c>
       <c r="Z7" t="n">
         <v>0.0140806528413614</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01283671727071111</v>
+        <v>0.0128367172707111</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01238720455289743</v>
+        <v>0.01238720455289742</v>
       </c>
     </row>
     <row r="8">
@@ -1114,46 +1114,46 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01451089472867356</v>
+        <v>0.01451089472867355</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01489127150687985</v>
+        <v>0.01489127150687983</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01453940695038092</v>
+        <v>0.01453940695038089</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01163271310010202</v>
+        <v>0.011632713100102</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01467177223276842</v>
+        <v>0.0146717722327684</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01456131744194702</v>
+        <v>0.01456131744194701</v>
       </c>
       <c r="H8" t="n">
         <v>0.0142692531881812</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01448402591585473</v>
+        <v>0.01448402591585474</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0144986597153463</v>
+        <v>0.01449865971534627</v>
       </c>
       <c r="K8" t="n">
         <v>0.01409997918638476</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0144852928194638</v>
+        <v>0.01448529281946381</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01353959176548817</v>
+        <v>0.01353959176548816</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0143530234640521</v>
+        <v>0.01435302346405209</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01453108170592295</v>
+        <v>0.01453108170592294</v>
       </c>
       <c r="P8" t="n">
         <v>0.01463994067700645</v>
@@ -1162,37 +1162,37 @@
         <v>0.01468026698622593</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01450262067285722</v>
+        <v>0.0145026206728572</v>
       </c>
       <c r="S8" t="n">
         <v>0.01455381721079187</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01430656171101804</v>
+        <v>0.01430656171101802</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0142403522064181</v>
+        <v>0.01424035220641807</v>
       </c>
       <c r="V8" t="n">
         <v>0.01479837110900035</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01432576921155641</v>
+        <v>0.0143257692115564</v>
       </c>
       <c r="X8" t="n">
         <v>0.01464288069069542</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01452606276423203</v>
+        <v>0.01452606276423201</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01466755872185019</v>
+        <v>0.01466755872185017</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01431405576096726</v>
+        <v>0.01431405576096725</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01418918433197779</v>
+        <v>0.01418918433197778</v>
       </c>
     </row>
   </sheetData>
@@ -1358,25 +1358,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01448025351533153</v>
+        <v>0.01448025351533155</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01451669718138138</v>
+        <v>0.01451669718138137</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01450623233365663</v>
+        <v>0.01450623233365664</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01163182640391849</v>
+        <v>0.01163182640391848</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01452060297169222</v>
+        <v>0.01452060297169223</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0143624794067865</v>
+        <v>0.01436247940678651</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01455945184994915</v>
+        <v>0.01455945184994914</v>
       </c>
       <c r="I2" t="n">
         <v>0.01453079766101552</v>
@@ -1385,40 +1385,40 @@
         <v>0.0145356227040938</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01457077681548982</v>
+        <v>0.01457077681548983</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01453650710646334</v>
+        <v>0.01453650710646333</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01451003729804307</v>
+        <v>0.01451003729804308</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0145294631817399</v>
+        <v>0.01452946318173989</v>
       </c>
       <c r="O2" t="n">
         <v>0.01454419084946171</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01452909607632953</v>
+        <v>0.01452909607632952</v>
       </c>
       <c r="Q2" t="n">
         <v>0.01450040256107986</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01451227122435192</v>
+        <v>0.0145122712243519</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01453366453466193</v>
+        <v>0.01453366453466192</v>
       </c>
       <c r="T2" t="n">
         <v>0.01454175281169551</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01452939452833142</v>
+        <v>0.01452939452833141</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01441826741736998</v>
+        <v>0.01441826741736996</v>
       </c>
       <c r="W2" t="n">
         <v>0.0147077416174655</v>
@@ -1427,10 +1427,10 @@
         <v>0.01474891834061053</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01466648459150245</v>
+        <v>0.01466648459150244</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01454026154051303</v>
+        <v>0.01454026154051305</v>
       </c>
       <c r="AA2" t="n">
         <v>0.01468056546578072</v>
@@ -1458,10 +1458,10 @@
         <v>0.01182055334454514</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01473594868845188</v>
+        <v>0.01473594868845189</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01455276571987677</v>
+        <v>0.01455276571987678</v>
       </c>
       <c r="H3" t="n">
         <v>0.0147215167978468</v>
@@ -1470,7 +1470,7 @@
         <v>0.0147215167978468</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01472044364922922</v>
+        <v>0.01472044364922923</v>
       </c>
       <c r="K3" t="n">
         <v>0.01472904324821234</v>
@@ -1479,13 +1479,13 @@
         <v>0.0147215167978468</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01472130606291765</v>
+        <v>0.01472130606291766</v>
       </c>
       <c r="N3" t="n">
         <v>0.0147215167978468</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01472140974805883</v>
+        <v>0.01472140974805884</v>
       </c>
       <c r="P3" t="n">
         <v>0.01472093294181521</v>
@@ -1500,13 +1500,13 @@
         <v>0.0147215167978468</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01472136263708822</v>
+        <v>0.01472136263708823</v>
       </c>
       <c r="U3" t="n">
         <v>0.0147213782442679</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01459417285461791</v>
+        <v>0.01459417285461789</v>
       </c>
       <c r="W3" t="n">
         <v>0.0147215167978468</v>
@@ -1515,16 +1515,16 @@
         <v>0.01465994229821248</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01472111104136405</v>
+        <v>0.01472111104136406</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01472308994415354</v>
+        <v>0.01472308994415355</v>
       </c>
       <c r="AA3" t="n">
         <v>0.0147215167978468</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01455801907927669</v>
+        <v>0.0145580190792767</v>
       </c>
     </row>
     <row r="4">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0068801566058364</v>
+        <v>0.006880156605836387</v>
       </c>
       <c r="C4" t="n">
         <v>0.01131335051871967</v>
@@ -1543,76 +1543,76 @@
         <v>0.01386927699288656</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008937177172405532</v>
+        <v>0.008937177172405509</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01435495674627642</v>
+        <v>0.01435495674627639</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01508637480556985</v>
+        <v>0.0150863748055698</v>
       </c>
       <c r="H4" t="n">
         <v>0.02894124681419392</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02054480111000073</v>
+        <v>0.02054480111000076</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02060165570461456</v>
+        <v>0.02060165570461453</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02642725187068569</v>
+        <v>0.02642725187068568</v>
       </c>
       <c r="L4" t="n">
         <v>0.01994098596490338</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01509319911868206</v>
+        <v>0.01509319911868204</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0199811132414302</v>
+        <v>0.01998111324143021</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02115133413144467</v>
+        <v>0.02115133413144469</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01797549998495754</v>
+        <v>0.01797549998495753</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01200976469810029</v>
+        <v>0.01200976469810028</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02656212959199565</v>
+        <v>0.02656212959199564</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01894364662111261</v>
+        <v>0.01894364662111259</v>
       </c>
       <c r="T4" t="n">
         <v>0.02356970636641766</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01810335529540473</v>
+        <v>0.01810335529540466</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0212784333600976</v>
+        <v>0.02127843336009758</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06436602245000012</v>
+        <v>0.06436602245000007</v>
       </c>
       <c r="X4" t="n">
-        <v>0.08649851930404202</v>
+        <v>0.08649851930404211</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0550326850914765</v>
+        <v>0.05503268509147651</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01941827424977993</v>
+        <v>0.01941827424977995</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.05829776591183524</v>
+        <v>0.05829776591183529</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.01183128016742131</v>
+        <v>0.0118312801674213</v>
       </c>
     </row>
     <row r="5">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.005193052226403499</v>
+        <v>0.005193052226403492</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007806365946355861</v>
+        <v>0.007806365946355842</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007806365946355861</v>
+        <v>0.007806365946355842</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006414853479386906</v>
+        <v>0.006414853479386896</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005600175961037734</v>
+        <v>0.005600175961037721</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008348253569994709</v>
+        <v>0.008348253569994685</v>
       </c>
       <c r="H5" t="n">
-        <v>0.007806365946355861</v>
+        <v>0.007806365946355842</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007806365946355861</v>
+        <v>0.007806365946355842</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007804762830917597</v>
+        <v>0.007804762830917574</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007806365946355861</v>
+        <v>0.007806365946355842</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007806365946355861</v>
+        <v>0.007806365946355842</v>
       </c>
       <c r="M5" t="n">
-        <v>0.007806365946355932</v>
+        <v>0.007806365946355907</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0199811132414302</v>
+        <v>0.005780610614389909</v>
       </c>
       <c r="O5" t="n">
-        <v>0.006337305766547319</v>
+        <v>0.00633730576654731</v>
       </c>
       <c r="P5" t="n">
-        <v>0.00620084633336894</v>
+        <v>0.006200846333368923</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.004679476435778908</v>
+        <v>0.004679476435778909</v>
       </c>
       <c r="R5" t="n">
-        <v>0.007806365946355861</v>
+        <v>0.007806365946355842</v>
       </c>
       <c r="S5" t="n">
-        <v>0.007806365946355861</v>
+        <v>0.007806365946355842</v>
       </c>
       <c r="T5" t="n">
-        <v>0.007806365946355861</v>
+        <v>0.007806365946355842</v>
       </c>
       <c r="U5" t="n">
-        <v>0.006529495749895689</v>
+        <v>0.006529495749895675</v>
       </c>
       <c r="V5" t="n">
-        <v>0.007080558686668118</v>
+        <v>0.007080558686668091</v>
       </c>
       <c r="W5" t="n">
-        <v>0.007806879532777204</v>
+        <v>0.00780687953277718</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004918991828090858</v>
+        <v>0.004918991828090857</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01040242057349557</v>
+        <v>0.01040242057349555</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.005144508582837436</v>
+        <v>0.005144508582837429</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.007806365946355861</v>
+        <v>0.007806365946355842</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01053619064418236</v>
+        <v>0.01053619064418234</v>
       </c>
     </row>
     <row r="6">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00656345221521296</v>
+        <v>0.006563452215212957</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008079896459163021</v>
+        <v>0.008079896459163015</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008079896459163021</v>
+        <v>0.008079896459163015</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007729908022704168</v>
+        <v>0.007729908022704166</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004584077395858717</v>
+        <v>0.004584077395858715</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008079897381650904</v>
+        <v>0.008079897381650891</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008079896459163021</v>
+        <v>0.008079896459163015</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008079896459163021</v>
+        <v>0.008079896459163015</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008078293343724761</v>
+        <v>0.008078293343724749</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008079896459163021</v>
+        <v>0.008079896459163015</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008079896459163021</v>
+        <v>0.008079896459163015</v>
       </c>
       <c r="M6" t="n">
-        <v>0.008079896459163021</v>
+        <v>0.008079896459163015</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0199811132414302</v>
+        <v>0.008079896459163015</v>
       </c>
       <c r="O6" t="n">
-        <v>0.008582445324192906</v>
+        <v>0.008582445324192896</v>
       </c>
       <c r="P6" t="n">
-        <v>0.008691740879425175</v>
+        <v>0.008691740879425173</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.008079897381650904</v>
+        <v>0.008079897381650891</v>
       </c>
       <c r="R6" t="n">
-        <v>0.008079896459163021</v>
+        <v>0.008079896459163015</v>
       </c>
       <c r="S6" t="n">
-        <v>0.008079896459163021</v>
+        <v>0.008079896459163015</v>
       </c>
       <c r="T6" t="n">
-        <v>0.008079896459163021</v>
+        <v>0.008079896459163015</v>
       </c>
       <c r="U6" t="n">
-        <v>0.008079896459163021</v>
+        <v>0.008079896459163015</v>
       </c>
       <c r="V6" t="n">
-        <v>0.009819777549428426</v>
+        <v>0.009819777549428399</v>
       </c>
       <c r="W6" t="n">
-        <v>0.008079896459163021</v>
+        <v>0.008079896459163015</v>
       </c>
       <c r="X6" t="n">
-        <v>0.008079896459163021</v>
+        <v>0.008079896459163015</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.008079896459163021</v>
+        <v>0.008079896459163015</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.007165615793854372</v>
+        <v>0.007165615793854369</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.008079896459163021</v>
+        <v>0.008079896459163015</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.008079896459163021</v>
+        <v>0.008079896459163015</v>
       </c>
     </row>
     <row r="7">
@@ -1807,13 +1807,13 @@
         <v>0.01445529566500042</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01165924144443777</v>
+        <v>0.01165924144443775</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01446414495562198</v>
+        <v>0.01446414495562199</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01422032821700878</v>
+        <v>0.01422032821700879</v>
       </c>
       <c r="H7" t="n">
         <v>0.01414747294917203</v>
@@ -1825,19 +1825,19 @@
         <v>0.014272177052168</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01412417906607843</v>
+        <v>0.01412417906607845</v>
       </c>
       <c r="L7" t="n">
         <v>0.01427382850867363</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01443277624724552</v>
+        <v>0.01443277624724553</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01431750955491792</v>
+        <v>0.01431750955491794</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01422404385557803</v>
+        <v>0.01422404385557804</v>
       </c>
       <c r="P7" t="n">
         <v>0.01431050526939276</v>
@@ -1846,25 +1846,25 @@
         <v>0.01448883734346285</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01414898828171685</v>
+        <v>0.01414898828171684</v>
       </c>
       <c r="S7" t="n">
         <v>0.01428924431367042</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01424655703403967</v>
+        <v>0.01424655703403968</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01431458211188366</v>
+        <v>0.01431458211188367</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01410055071589456</v>
+        <v>0.01410055071589453</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01326395701606206</v>
+        <v>0.01326395701606205</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01264064366333827</v>
+        <v>0.0126406436633383</v>
       </c>
       <c r="Y7" t="n">
         <v>0.01350682820782833</v>
@@ -1873,7 +1873,7 @@
         <v>0.01425929467500262</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01342540619980602</v>
+        <v>0.01342540619980601</v>
       </c>
       <c r="AB7" t="n">
         <v>0.01435441143839667</v>
@@ -1886,58 +1886,58 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01442753399637686</v>
+        <v>0.01442753399637687</v>
       </c>
       <c r="C8" t="n">
         <v>0.01442192091350741</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01438510086981512</v>
+        <v>0.01438510086981513</v>
       </c>
       <c r="E8" t="n">
         <v>0.01155842897529911</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01439693140706753</v>
+        <v>0.01439693140706752</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01421121928356611</v>
+        <v>0.01421121928356612</v>
       </c>
       <c r="H8" t="n">
         <v>0.01429826006943293</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01434454587330547</v>
+        <v>0.01434454587330548</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01433165997389006</v>
+        <v>0.01433165997389007</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01429556168503113</v>
+        <v>0.01429556168503112</v>
       </c>
       <c r="L8" t="n">
         <v>0.01433280750819162</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01437875531242229</v>
+        <v>0.0143787553124223</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01434563859871255</v>
+        <v>0.01434563859871256</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01431788778337188</v>
+        <v>0.0143178877833719</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01434235017742192</v>
+        <v>0.01434235017742195</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01439453320887215</v>
+        <v>0.01439453320887216</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01427132467195311</v>
+        <v>0.0142713246719531</v>
       </c>
       <c r="S8" t="n">
-        <v>0.014336979176791</v>
+        <v>0.01433697917679101</v>
       </c>
       <c r="T8" t="n">
         <v>0.01432571474919275</v>
@@ -1946,25 +1946,25 @@
         <v>0.01434430099171424</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01419366777117042</v>
+        <v>0.01419366777117039</v>
       </c>
       <c r="W8" t="n">
         <v>0.01404454727178603</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01383013102661983</v>
+        <v>0.01383013102661984</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01411398203255393</v>
+        <v>0.01411398203255392</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01432923321502154</v>
+        <v>0.01432923321502153</v>
       </c>
       <c r="AA8" t="n">
         <v>0.01409083101321277</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01425350030480081</v>
+        <v>0.01425350030480082</v>
       </c>
     </row>
   </sheetData>
@@ -2133,16 +2133,16 @@
         <v>0.0151002263009869</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01495869922491863</v>
+        <v>0.01495869922491864</v>
       </c>
       <c r="D2" t="n">
         <v>0.01511221052486163</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01186602816027589</v>
+        <v>0.01186602816027591</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01500522611748112</v>
+        <v>0.01500522611748113</v>
       </c>
       <c r="G2" t="n">
         <v>0.01504016203904882</v>
@@ -2151,22 +2151,22 @@
         <v>0.01520837141665082</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01511454708317068</v>
+        <v>0.01511454708317069</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01514610228095913</v>
+        <v>0.01514610228095914</v>
       </c>
       <c r="K2" t="n">
         <v>0.01532878133894265</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0151380034130455</v>
+        <v>0.01513800341304551</v>
       </c>
       <c r="M2" t="n">
         <v>0.01568128328910496</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01514690590452784</v>
+        <v>0.01514690590452785</v>
       </c>
       <c r="O2" t="n">
         <v>0.01507932784508269</v>
@@ -2178,7 +2178,7 @@
         <v>0.01501949835694528</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0151558882432364</v>
+        <v>0.01515588824323641</v>
       </c>
       <c r="S2" t="n">
         <v>0.01512246887082849</v>
@@ -2187,28 +2187,28 @@
         <v>0.01518786682577559</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01524606170280583</v>
+        <v>0.01524606170280584</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01497354819021435</v>
+        <v>0.01497354819021434</v>
       </c>
       <c r="W2" t="n">
         <v>0.01532912126648399</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01511194080146981</v>
+        <v>0.01511194080146982</v>
       </c>
       <c r="Y2" t="n">
         <v>0.01513117935014667</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01502907644083993</v>
+        <v>0.01502907644083994</v>
       </c>
       <c r="AA2" t="n">
         <v>0.01522567490056399</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0151896799834938</v>
+        <v>0.01518967998349381</v>
       </c>
     </row>
     <row r="3">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01513344462806147</v>
+        <v>0.01513344462806148</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01515477940300408</v>
+        <v>0.01515477940300409</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01513344462806147</v>
+        <v>0.01513344462806148</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01198220779444682</v>
+        <v>0.01198220779444683</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01514114947468414</v>
+        <v>0.01514114947468415</v>
       </c>
       <c r="G3" t="n">
         <v>0.0150506108838166</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01513344462806147</v>
+        <v>0.01513344462806148</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01513344462806147</v>
+        <v>0.01513344462806148</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01512668182433125</v>
+        <v>0.01512668182433126</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01513758373890898</v>
+        <v>0.01513758373890899</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01513344462806147</v>
+        <v>0.01513344462806148</v>
       </c>
       <c r="M3" t="n">
         <v>0.01513341456953123</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01513344462806147</v>
+        <v>0.01513344462806148</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01513336083060586</v>
+        <v>0.01513336083060587</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01513342102004795</v>
+        <v>0.01513342102004796</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01513344343896558</v>
+        <v>0.01513344343896559</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01513422041483648</v>
+        <v>0.01513422041483649</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01513344462806147</v>
+        <v>0.01513344462806148</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01513340817783772</v>
+        <v>0.01513340817783773</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0151335768837731</v>
+        <v>0.01513357688377311</v>
       </c>
       <c r="V3" t="n">
         <v>0.01512645841145035</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01513344462806147</v>
+        <v>0.01513344462806148</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01512219241289031</v>
+        <v>0.01512219241289032</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01513325222156715</v>
+        <v>0.01513325222156716</v>
       </c>
       <c r="Z3" t="n">
         <v>0.01513439547646495</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01513344462806147</v>
+        <v>0.01513344462806148</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01496994690949136</v>
+        <v>0.01496994690949137</v>
       </c>
     </row>
     <row r="4">
@@ -2306,61 +2306,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0608824250622868</v>
+        <v>0.06088242506228737</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02241689079706628</v>
+        <v>0.02241689079706629</v>
       </c>
       <c r="D4" t="n">
-        <v>0.07223850583264017</v>
+        <v>0.07223850583264012</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0297663584981279</v>
+        <v>0.02976635849812831</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03982913140922396</v>
+        <v>0.03982913140922416</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06639967918419623</v>
+        <v>0.06639967918419636</v>
       </c>
       <c r="H4" t="n">
         <v>0.1030227819428611</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07367647803996973</v>
+        <v>0.07367647803996974</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07947676992074615</v>
+        <v>0.07947676992074594</v>
       </c>
       <c r="K4" t="n">
-        <v>0.12299055249216</v>
+        <v>0.1229905524921601</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07560685587412694</v>
+        <v>0.07560685587412849</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2351542989406031</v>
+        <v>0.2351542989406021</v>
       </c>
       <c r="N4" t="n">
-        <v>0.07987831636939294</v>
+        <v>0.07987831636939302</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05438467116492938</v>
+        <v>0.05438467116492939</v>
       </c>
       <c r="P4" t="n">
-        <v>0.062587117718508</v>
+        <v>0.06258711771850881</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04473524716154686</v>
+        <v>0.0447352471615472</v>
       </c>
       <c r="R4" t="n">
-        <v>0.08639423437935241</v>
+        <v>0.08639423437935244</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0681612944620177</v>
+        <v>0.06816129446201781</v>
       </c>
       <c r="T4" t="n">
-        <v>0.09361886731093469</v>
+        <v>0.09361886731093497</v>
       </c>
       <c r="U4" t="n">
         <v>0.1025651195899408</v>
@@ -2369,22 +2369,22 @@
         <v>0.03067293490913634</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1281859702064285</v>
+        <v>0.1281859702064286</v>
       </c>
       <c r="X4" t="n">
-        <v>0.073768940122225</v>
+        <v>0.07376894012222555</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.07357711006041902</v>
+        <v>0.07357711006041899</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.04392716367935555</v>
+        <v>0.04392716367935558</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.09983928620116037</v>
+        <v>0.09983928620116084</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1434139373619931</v>
+        <v>0.1434139373619943</v>
       </c>
     </row>
     <row r="5">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006278825720045142</v>
+        <v>0.00627882572004514</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009538074929038949</v>
+        <v>0.009538074929038959</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009538074929038949</v>
+        <v>0.009538074929038959</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007802620868154588</v>
+        <v>0.007802620868154597</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006786578654613496</v>
+        <v>0.006786578654613497</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01021390148417601</v>
+        <v>0.010213901484176</v>
       </c>
       <c r="H5" t="n">
-        <v>0.009538074929038949</v>
+        <v>0.009538074929038959</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009538074929038949</v>
+        <v>0.009538074929038959</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009535127825602787</v>
+        <v>0.009535127825602776</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009538074929038949</v>
+        <v>0.009538074929038959</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009538074929038949</v>
+        <v>0.009538074929038959</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0095380749290394</v>
+        <v>0.009538074929039403</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07987831636939294</v>
+        <v>0.007011611530298283</v>
       </c>
       <c r="O5" t="n">
-        <v>0.007705905606543938</v>
+        <v>0.007705905606543936</v>
       </c>
       <c r="P5" t="n">
-        <v>0.007535717352241069</v>
+        <v>0.007535717352241083</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.005638308863193017</v>
+        <v>0.005638308863193011</v>
       </c>
       <c r="R5" t="n">
-        <v>0.009538074929038949</v>
+        <v>0.009538074929038954</v>
       </c>
       <c r="S5" t="n">
-        <v>0.009538074929038949</v>
+        <v>0.009538074929038959</v>
       </c>
       <c r="T5" t="n">
-        <v>0.009538074929038949</v>
+        <v>0.009538074929038954</v>
       </c>
       <c r="U5" t="n">
         <v>0.007945971258469721</v>
       </c>
       <c r="V5" t="n">
-        <v>0.008627182581359638</v>
+        <v>0.008627182581359635</v>
       </c>
       <c r="W5" t="n">
         <v>0.009538715459836328</v>
       </c>
       <c r="X5" t="n">
-        <v>0.005937025526287492</v>
+        <v>0.005937025526287478</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01277643525736502</v>
+        <v>0.01277643525736503</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.006218283493188815</v>
+        <v>0.006218283493188827</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.009538074929038949</v>
+        <v>0.009538074929038959</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01294263325698614</v>
+        <v>0.01294263325698616</v>
       </c>
     </row>
     <row r="6">
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.009044529188302676</v>
+        <v>0.009044529188302664</v>
       </c>
       <c r="C6" t="n">
         <v>0.01122799925783298</v>
@@ -2491,13 +2491,13 @@
         <v>0.01122799925783298</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01072406256205653</v>
+        <v>0.01072406256205654</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006194506026753553</v>
+        <v>0.006194506026753548</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01122799833487758</v>
+        <v>0.01122799833487759</v>
       </c>
       <c r="H6" t="n">
         <v>0.01122799925783298</v>
@@ -2506,7 +2506,7 @@
         <v>0.01122799925783298</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0112250521543968</v>
+        <v>0.01122505215439679</v>
       </c>
       <c r="K6" t="n">
         <v>0.01122799925783298</v>
@@ -2518,16 +2518,16 @@
         <v>0.01122799925783298</v>
       </c>
       <c r="N6" t="n">
-        <v>0.07987831636939294</v>
+        <v>0.01122799925783298</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01195159715104362</v>
+        <v>0.01195159715104363</v>
       </c>
       <c r="P6" t="n">
         <v>0.01210896747869488</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01122799833487758</v>
+        <v>0.01122799833487759</v>
       </c>
       <c r="R6" t="n">
         <v>0.01122799925783298</v>
@@ -2542,7 +2542,7 @@
         <v>0.01122799925783298</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01372902438170667</v>
+        <v>0.01372902438170668</v>
       </c>
       <c r="W6" t="n">
         <v>0.01122799925783298</v>
@@ -2554,7 +2554,7 @@
         <v>0.01122799925783298</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.00991156060114508</v>
+        <v>0.009911560601145081</v>
       </c>
       <c r="AA6" t="n">
         <v>0.01122799925783298</v>
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01374658594173474</v>
+        <v>0.01374658594173475</v>
       </c>
       <c r="C7" t="n">
         <v>0.01473202574474615</v>
@@ -2579,52 +2579,52 @@
         <v>0.01369778557258123</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01138183945344058</v>
+        <v>0.01138183945344057</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0143771547011103</v>
+        <v>0.01437715470111029</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01357158300866909</v>
+        <v>0.0135715830086691</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01314801576158692</v>
+        <v>0.01314801576158694</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01368681631998327</v>
+        <v>0.01368681631998328</v>
       </c>
       <c r="J7" t="n">
         <v>0.01344117371960281</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01245170468256121</v>
+        <v>0.01245170468256123</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01353197094469936</v>
+        <v>0.01353197094469943</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01038234010789582</v>
+        <v>0.01038234010789583</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01348761338194629</v>
+        <v>0.0134876133819463</v>
       </c>
       <c r="O7" t="n">
         <v>0.01386899731061859</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01373369401041716</v>
+        <v>0.01373369401041718</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01423855430126571</v>
+        <v>0.01423855430126572</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01345352798038161</v>
+        <v>0.01345352798038163</v>
       </c>
       <c r="S7" t="n">
         <v>0.01361895829275451</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01325558933685532</v>
+        <v>0.01325558933685533</v>
       </c>
       <c r="U7" t="n">
         <v>0.01289175645811797</v>
@@ -2636,19 +2636,19 @@
         <v>0.0124066737889209</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01362644283507078</v>
+        <v>0.0136264428350708</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01357621394616696</v>
+        <v>0.01357621394616698</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01417705329130677</v>
+        <v>0.01417705329130678</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01301893366808342</v>
+        <v>0.01301893366808343</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01220597521023602</v>
+        <v>0.01220597521023601</v>
       </c>
     </row>
     <row r="8">
@@ -2670,7 +2670,7 @@
         <v>0.01159285865185767</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01465760606079813</v>
+        <v>0.01465760606079814</v>
       </c>
       <c r="G8" t="n">
         <v>0.01436719964247452</v>
@@ -2682,25 +2682,25 @@
         <v>0.01445632659286422</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01437919072191207</v>
+        <v>0.01437919072191208</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01410669780891573</v>
+        <v>0.01410669780891574</v>
       </c>
       <c r="L8" t="n">
         <v>0.01440932778352193</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01351952926828489</v>
+        <v>0.0135195292682849</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01439804744259245</v>
+        <v>0.01439804744259247</v>
       </c>
       <c r="O8" t="n">
         <v>0.01450403841420101</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0144650222641205</v>
+        <v>0.01446502226412051</v>
       </c>
       <c r="Q8" t="n">
         <v>0.01461232094744936</v>
@@ -2709,10 +2709,10 @@
         <v>0.01439116782951045</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01443337276188224</v>
+        <v>0.01443337276188225</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01433345326887501</v>
+        <v>0.01433345326887502</v>
       </c>
       <c r="U8" t="n">
         <v>0.01422602626487493</v>
@@ -2721,19 +2721,19 @@
         <v>0.014666102778505</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01408843184497196</v>
+        <v>0.01408843184497197</v>
       </c>
       <c r="X8" t="n">
         <v>0.01443136997689085</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01442272197285302</v>
+        <v>0.01442272197285303</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01459348269572444</v>
+        <v>0.01459348269572445</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01426356567522736</v>
+        <v>0.01426356567522737</v>
       </c>
       <c r="AB8" t="n">
         <v>0.01393206405207744</v>
@@ -2908,10 +2908,10 @@
         <v>0.01492756918745221</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01512745266808716</v>
+        <v>0.01512745266808717</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0118608040457672</v>
+        <v>0.01186080404576721</v>
       </c>
       <c r="F2" t="n">
         <v>0.01496564687641236</v>
@@ -2926,13 +2926,13 @@
         <v>0.0151363713767168</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01511020305018137</v>
+        <v>0.01511020305018138</v>
       </c>
       <c r="K2" t="n">
         <v>0.0151549207630467</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01506325449488666</v>
+        <v>0.01506325449488665</v>
       </c>
       <c r="M2" t="n">
         <v>0.01554845016704028</v>
@@ -2959,10 +2959,10 @@
         <v>0.01510958335052924</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01513076935610413</v>
+        <v>0.01513076935610414</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01496912986097019</v>
+        <v>0.0149691298609702</v>
       </c>
       <c r="W2" t="n">
         <v>0.01527268617439096</v>
@@ -2974,7 +2974,7 @@
         <v>0.01525099323233117</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01500334714972173</v>
+        <v>0.01500334714972174</v>
       </c>
       <c r="AA2" t="n">
         <v>0.01520313640286984</v>
@@ -2999,7 +2999,7 @@
         <v>0.01510746362363655</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01196825840230931</v>
+        <v>0.0119682584023093</v>
       </c>
       <c r="F3" t="n">
         <v>0.01511833765623701</v>
@@ -3014,7 +3014,7 @@
         <v>0.01510746362363655</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01510231461490751</v>
+        <v>0.01510231461490752</v>
       </c>
       <c r="K3" t="n">
         <v>0.01511333467256998</v>
@@ -3023,7 +3023,7 @@
         <v>0.01510746362363655</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01510738231879223</v>
+        <v>0.01510738231879224</v>
       </c>
       <c r="N3" t="n">
         <v>0.01510746362363655</v>
@@ -3035,10 +3035,10 @@
         <v>0.0151074517816603</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01510746243454066</v>
+        <v>0.01510746243454067</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01508516772322902</v>
+        <v>0.01508516772322903</v>
       </c>
       <c r="S3" t="n">
         <v>0.01510746362363655</v>
@@ -3059,16 +3059,16 @@
         <v>0.01497315338819352</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01510723235867047</v>
+        <v>0.01510723235867048</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01510906243880435</v>
+        <v>0.01510906243880436</v>
       </c>
       <c r="AA3" t="n">
         <v>0.01510746362363655</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01494396590506644</v>
+        <v>0.01494396590506645</v>
       </c>
     </row>
     <row r="4">
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04532655936265418</v>
+        <v>0.04532655936265436</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01890958605047834</v>
+        <v>0.01890958605047836</v>
       </c>
       <c r="D4" t="n">
-        <v>0.07742311848532347</v>
+        <v>0.07742311848532357</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02996252522576102</v>
+        <v>0.02996252522576097</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03223452897618282</v>
+        <v>0.03223452897618288</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05749820857269054</v>
+        <v>0.05749820857269064</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08505145848536504</v>
+        <v>0.08505145848536511</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08104079068253499</v>
+        <v>0.08104079068253488</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07081144251941626</v>
+        <v>0.0708114425194163</v>
       </c>
       <c r="K4" t="n">
-        <v>0.07461413023242738</v>
+        <v>0.07461413023242736</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05780942878954428</v>
+        <v>0.05780942878954437</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1909309926053191</v>
+        <v>0.190930992605319</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05102278727025394</v>
+        <v>0.05102278727025403</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03850049650093177</v>
+        <v>0.03850049650093187</v>
       </c>
       <c r="P4" t="n">
-        <v>0.05495498036763196</v>
+        <v>0.05495498036763213</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03266516585476077</v>
+        <v>0.03266516585476082</v>
       </c>
       <c r="R4" t="n">
-        <v>0.06736786146985642</v>
+        <v>0.06736786146985636</v>
       </c>
       <c r="S4" t="n">
-        <v>0.05765288019721876</v>
+        <v>0.05765288019721881</v>
       </c>
       <c r="T4" t="n">
-        <v>0.073467577349101</v>
+        <v>0.07346757734910124</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0727669232181674</v>
+        <v>0.07276692321816741</v>
       </c>
       <c r="V4" t="n">
-        <v>0.03362036230889859</v>
+        <v>0.03362036230889884</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1116666509031556</v>
+        <v>0.1116666509031553</v>
       </c>
       <c r="X4" t="n">
-        <v>0.09712480145281414</v>
+        <v>0.09712480145281426</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1052389131762306</v>
+        <v>0.1052389131762311</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03857325646377208</v>
+        <v>0.03857325646377207</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.094060180600016</v>
+        <v>0.09406018060001613</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1245659978372143</v>
+        <v>0.1245659978372144</v>
       </c>
     </row>
     <row r="5">
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.005807551203601257</v>
+        <v>0.005807551203601275</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008757351084545305</v>
+        <v>0.008757351084545322</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008757351084545305</v>
+        <v>0.008757351084545322</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007186669662590062</v>
+        <v>0.007186669662590073</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006267095549509491</v>
+        <v>0.006267095549509496</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009369011305662782</v>
+        <v>0.00936901130566282</v>
       </c>
       <c r="H5" t="n">
-        <v>0.008757351084545305</v>
+        <v>0.008757351084545322</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008757351084545305</v>
+        <v>0.008757351084545322</v>
       </c>
       <c r="J5" t="n">
-        <v>0.008754971647866323</v>
+        <v>0.00875497164786633</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008757351084545305</v>
+        <v>0.008757351084545322</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008757351084545305</v>
+        <v>0.008757351084545326</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008757351084546342</v>
+        <v>0.008757351084546365</v>
       </c>
       <c r="N5" t="n">
-        <v>0.05102278727025394</v>
+        <v>0.00647076268487662</v>
       </c>
       <c r="O5" t="n">
-        <v>0.007099137028761736</v>
+        <v>0.00709913702876176</v>
       </c>
       <c r="P5" t="n">
-        <v>0.006945107293684853</v>
+        <v>0.006945107293684866</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.005227848202448072</v>
+        <v>0.0052278482024481</v>
       </c>
       <c r="R5" t="n">
-        <v>0.008757351084545305</v>
+        <v>0.008757351084545322</v>
       </c>
       <c r="S5" t="n">
-        <v>0.008757351084545305</v>
+        <v>0.008757351084545322</v>
       </c>
       <c r="T5" t="n">
-        <v>0.008757351084545305</v>
+        <v>0.008757351084545322</v>
       </c>
       <c r="U5" t="n">
-        <v>0.007316086559396427</v>
+        <v>0.007316086559396444</v>
       </c>
       <c r="V5" t="n">
-        <v>0.007934484072443118</v>
+        <v>0.007934484072443128</v>
       </c>
       <c r="W5" t="n">
-        <v>0.008757930800037058</v>
+        <v>0.00875793080003707</v>
       </c>
       <c r="X5" t="n">
-        <v>0.005498203219960398</v>
+        <v>0.005498203219960401</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01168769265835529</v>
+        <v>0.01168769265835532</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.005752757156851781</v>
+        <v>0.005752757156851802</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.008757351084545305</v>
+        <v>0.008757351084545322</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01183866371394836</v>
+        <v>0.01183866371394838</v>
       </c>
     </row>
     <row r="6">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007924711835052091</v>
+        <v>0.007924711835052093</v>
       </c>
       <c r="C6" t="n">
-        <v>0.009794134834657383</v>
+        <v>0.009794134834657395</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009794134834657383</v>
+        <v>0.009794134834657395</v>
       </c>
       <c r="E6" t="n">
-        <v>0.009362679179437072</v>
+        <v>0.009362679179437075</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005484605373881453</v>
+        <v>0.005484605373881461</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009794134246843347</v>
+        <v>0.009794134246843349</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009794134834657383</v>
+        <v>0.009794134834657395</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009794134834657383</v>
+        <v>0.009794134834657395</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009791755397978372</v>
+        <v>0.009791755397978375</v>
       </c>
       <c r="K6" t="n">
-        <v>0.009794134834657383</v>
+        <v>0.009794134834657395</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009794134834657384</v>
+        <v>0.009794134834657398</v>
       </c>
       <c r="M6" t="n">
-        <v>0.009794134834657383</v>
+        <v>0.009794134834657395</v>
       </c>
       <c r="N6" t="n">
-        <v>0.05102278727025394</v>
+        <v>0.009794134834657395</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01041365838631124</v>
+        <v>0.01041365838631123</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01054839425740132</v>
+        <v>0.01054839425740133</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.009794134246843347</v>
+        <v>0.009794134246843349</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009794134834657383</v>
+        <v>0.009794134834657395</v>
       </c>
       <c r="S6" t="n">
-        <v>0.009794134834657383</v>
+        <v>0.009794134834657395</v>
       </c>
       <c r="T6" t="n">
-        <v>0.009794134834657383</v>
+        <v>0.009794134834657395</v>
       </c>
       <c r="U6" t="n">
-        <v>0.009794134834657383</v>
+        <v>0.009794134834657395</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01193642501953673</v>
+        <v>0.01193642501953674</v>
       </c>
       <c r="W6" t="n">
-        <v>0.009794134834657383</v>
+        <v>0.009794134834657395</v>
       </c>
       <c r="X6" t="n">
-        <v>0.009794134834657384</v>
+        <v>0.009794134834657398</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.009794134834657383</v>
+        <v>0.009794134834657395</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.008667038768060123</v>
+        <v>0.008667038768060138</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.009794134834657383</v>
+        <v>0.009794134834657395</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.009794134834657383</v>
+        <v>0.009794134834657395</v>
       </c>
     </row>
     <row r="7">
@@ -3345,43 +3345,43 @@
         <v>0.01403155640750921</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01474707339012438</v>
+        <v>0.01474707339012439</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01343435566469708</v>
+        <v>0.01343435566469709</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01131930929896767</v>
+        <v>0.01131930929896768</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01445448478989293</v>
+        <v>0.01445448478989294</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01361924576158736</v>
+        <v>0.01361924576158737</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0133676467992597</v>
+        <v>0.01336764679925969</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01338534787153968</v>
+        <v>0.01338534787153967</v>
       </c>
       <c r="J7" t="n">
         <v>0.01349006703347287</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01330819940164877</v>
+        <v>0.01330819940164876</v>
       </c>
       <c r="L7" t="n">
         <v>0.01379835244107295</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01098355067456364</v>
+        <v>0.01098355067456365</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01399958804314591</v>
+        <v>0.01399958804314592</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01415689080513133</v>
+        <v>0.01415689080513134</v>
       </c>
       <c r="P7" t="n">
         <v>0.01377790264594003</v>
@@ -3390,28 +3390,28 @@
         <v>0.0144057971340809</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01368846978376541</v>
+        <v>0.01368846978376542</v>
       </c>
       <c r="S7" t="n">
         <v>0.01372799469942676</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01353934146405629</v>
+        <v>0.0135393414640563</v>
       </c>
       <c r="U7" t="n">
         <v>0.01339547426634607</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01428123894530146</v>
+        <v>0.01428123894530144</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01256447969293174</v>
+        <v>0.01256447969293175</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01282875613939571</v>
+        <v>0.01282875613939569</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01269493764953756</v>
+        <v>0.01269493764953757</v>
       </c>
       <c r="Z7" t="n">
         <v>0.01415781879561806</v>
@@ -3433,13 +3433,13 @@
         <v>0.01453312191415147</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01475339570491633</v>
+        <v>0.01475339570491634</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01436618321489101</v>
+        <v>0.01436618321489102</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01156553013566867</v>
+        <v>0.01156553013566869</v>
       </c>
       <c r="F8" t="n">
         <v>0.01466359170665225</v>
@@ -3451,10 +3451,10 @@
         <v>0.01434923830068071</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01435280322145547</v>
+        <v>0.01435280322145548</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0143766252627004</v>
+        <v>0.01437662526270041</v>
       </c>
       <c r="K8" t="n">
         <v>0.01433357846215278</v>
@@ -3463,13 +3463,13 @@
         <v>0.01446760473493042</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01367209362704457</v>
+        <v>0.01367209362704458</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01452607069185186</v>
+        <v>0.01452607069185187</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01456884906619699</v>
+        <v>0.014568849066197</v>
       </c>
       <c r="P8" t="n">
         <v>0.0144598960687966</v>
@@ -3478,25 +3478,25 @@
         <v>0.01464204008207155</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0144253320708911</v>
+        <v>0.01442533207089111</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01444674549821891</v>
+        <v>0.0144467454982189</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01439613161318958</v>
+        <v>0.01439613161318959</v>
       </c>
       <c r="U8" t="n">
         <v>0.01435195314679453</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01459769214497143</v>
+        <v>0.01459769214497142</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01411562038191131</v>
+        <v>0.01411562038191132</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01410911540114713</v>
+        <v>0.01410911540114715</v>
       </c>
       <c r="Y8" t="n">
         <v>0.01415339145214859</v>
@@ -3680,19 +3680,19 @@
         <v>0.01474780946811987</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01485848340217644</v>
+        <v>0.01485848340217645</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0117981094404065</v>
+        <v>0.01179810944040651</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0148112433791802</v>
+        <v>0.01481124337918021</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01472318318154746</v>
+        <v>0.01472318318154747</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01494298119261768</v>
+        <v>0.01494298119261767</v>
       </c>
       <c r="I2" t="n">
         <v>0.01493079699016387</v>
@@ -3701,58 +3701,58 @@
         <v>0.01492298478570868</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01503363856839563</v>
+        <v>0.01503363856839564</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01486236043254226</v>
+        <v>0.01486236043254225</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0152548340111064</v>
+        <v>0.01525483401110639</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01480007123862709</v>
+        <v>0.0148000712386271</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0148211248397391</v>
+        <v>0.01482112483973913</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01486602175473991</v>
+        <v>0.01486602175473994</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01478478944273648</v>
+        <v>0.01478478944273649</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01487975921287948</v>
+        <v>0.0148797592128795</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01488360855938838</v>
+        <v>0.0148836085593884</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01494642757031576</v>
+        <v>0.01494642757031577</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01496877430686017</v>
+        <v>0.01496877430686018</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01475761697382479</v>
+        <v>0.0147576169738248</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01504075706886549</v>
+        <v>0.0150407570688655</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01501877467903829</v>
+        <v>0.01501877467903832</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0152626780502964</v>
+        <v>0.01526267805029639</v>
       </c>
       <c r="Z2" t="n">
         <v>0.01480307840613611</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01503445062739493</v>
+        <v>0.01503445062739495</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01491506854743798</v>
+        <v>0.01491506854743799</v>
       </c>
     </row>
     <row r="3">
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0149293079405234</v>
+        <v>0.01492930794052341</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01495162629847369</v>
+        <v>0.0149516262984737</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0149293079405234</v>
+        <v>0.01492930794052341</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01193910245516511</v>
+        <v>0.01193910245516512</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01494373983112848</v>
+        <v>0.01494373983112849</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01476055686255337</v>
+        <v>0.01476055686255338</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0149293079405234</v>
+        <v>0.01492930794052341</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0149293079405234</v>
+        <v>0.01492930794052341</v>
       </c>
       <c r="J3" t="n">
         <v>0.01492759461797795</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01493683439088893</v>
+        <v>0.01493683439088895</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0149293079405234</v>
+        <v>0.01492930794052341</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01492909720559425</v>
+        <v>0.01492909720559426</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0149293079405234</v>
+        <v>0.01492930794052341</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01492920089073544</v>
+        <v>0.01492920089073545</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01492872408449181</v>
+        <v>0.01492872408449182</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01492930675142751</v>
+        <v>0.01492930675142753</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01488632857785673</v>
+        <v>0.01488632857785674</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0149293079405234</v>
+        <v>0.01492930794052341</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01492915377976482</v>
+        <v>0.01492915377976483</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0149291693869445</v>
+        <v>0.01492916938694451</v>
       </c>
       <c r="V3" t="n">
         <v>0.01482726416306042</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0149293079405234</v>
+        <v>0.01492930794052341</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01486773344088908</v>
+        <v>0.01486773344088909</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01492890218404065</v>
+        <v>0.01492890218404066</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01493088108683014</v>
+        <v>0.01493088108683015</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0149293079405234</v>
+        <v>0.01492930794052341</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01476581022195329</v>
+        <v>0.0147658102219533</v>
       </c>
     </row>
     <row r="4">
@@ -3850,85 +3850,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03851139415107912</v>
+        <v>0.03851139415107911</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01773764480647228</v>
+        <v>0.01773764480647229</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05089079045859234</v>
+        <v>0.05089079045859247</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02053935251235053</v>
+        <v>0.02053935251235052</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03653173798799986</v>
+        <v>0.03653173798799991</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05055134312375242</v>
+        <v>0.05055134312375233</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07905492284203067</v>
+        <v>0.07905492284203074</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07169978093036605</v>
+        <v>0.07169978093036609</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06549886180580436</v>
+        <v>0.06549886180580439</v>
       </c>
       <c r="K4" t="n">
-        <v>0.08688116287740869</v>
+        <v>0.08688116287740887</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0496258869279505</v>
+        <v>0.04962588692795064</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1526400878269774</v>
+        <v>0.1526400878269775</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03696125958467317</v>
+        <v>0.03696125958467314</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03745279111798571</v>
+        <v>0.03745279111798573</v>
       </c>
       <c r="P4" t="n">
-        <v>0.04799659970016006</v>
+        <v>0.04799659970016</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0316502524136064</v>
       </c>
       <c r="R4" t="n">
-        <v>0.07092327459208798</v>
+        <v>0.07092327459208804</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0532802388226226</v>
+        <v>0.05328023882262266</v>
       </c>
       <c r="T4" t="n">
-        <v>0.07678594710664008</v>
+        <v>0.07678594710664013</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07337353094615054</v>
+        <v>0.07337353094615046</v>
       </c>
       <c r="V4" t="n">
-        <v>0.04534154883288274</v>
+        <v>0.04534154883288287</v>
       </c>
       <c r="W4" t="n">
-        <v>0.09745756465962395</v>
+        <v>0.09745756465962402</v>
       </c>
       <c r="X4" t="n">
         <v>0.1048558212909868</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1553187362441722</v>
+        <v>0.155318736244172</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03146715997090006</v>
+        <v>0.03146715997090009</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0962755375603883</v>
+        <v>0.09627553756038844</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1119033573747459</v>
+        <v>0.1119033573747458</v>
       </c>
     </row>
     <row r="5">
@@ -3938,85 +3938,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.005779273428680711</v>
+        <v>0.005779273428680692</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008684175640668408</v>
+        <v>0.008684175640668411</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008684175640668408</v>
+        <v>0.008684175640668411</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007137400903030891</v>
+        <v>0.007137400903030917</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00623182324249753</v>
+        <v>0.006231823242497546</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009286526037647345</v>
+        <v>0.009286526037647364</v>
       </c>
       <c r="H5" t="n">
-        <v>0.008684175640668408</v>
+        <v>0.008684175640668411</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008684175640668408</v>
+        <v>0.008684175640668411</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00868242343524262</v>
+        <v>0.008682423435242654</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008684175640668408</v>
+        <v>0.008684175640668411</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008684175640668408</v>
+        <v>0.008684175640668413</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008684175640669863</v>
+        <v>0.00868417564066986</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03696125958467317</v>
+        <v>0.00643239044566108</v>
       </c>
       <c r="O5" t="n">
-        <v>0.007051200566721625</v>
+        <v>0.007051200566721646</v>
       </c>
       <c r="P5" t="n">
-        <v>0.006899515253762024</v>
+        <v>0.006899515253762027</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.005208393844212794</v>
+        <v>0.005208393844212825</v>
       </c>
       <c r="R5" t="n">
-        <v>0.008684175640668408</v>
+        <v>0.008684175640668411</v>
       </c>
       <c r="S5" t="n">
-        <v>0.008684175640668408</v>
+        <v>0.008684175640668411</v>
       </c>
       <c r="T5" t="n">
-        <v>0.008684175640668408</v>
+        <v>0.008684175640668411</v>
       </c>
       <c r="U5" t="n">
-        <v>0.007264850783916279</v>
+        <v>0.007264850783916298</v>
       </c>
       <c r="V5" t="n">
-        <v>0.007877598462578883</v>
+        <v>0.007877598462578884</v>
       </c>
       <c r="W5" t="n">
-        <v>0.008684746532496459</v>
+        <v>0.008684746532496478</v>
       </c>
       <c r="X5" t="n">
-        <v>0.005474633901161309</v>
+        <v>0.005474633901161333</v>
       </c>
       <c r="Y5" t="n">
         <v>0.01156992047576789</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.005725313379181414</v>
+        <v>0.005725313379181409</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.008684175640668408</v>
+        <v>0.008684175640668411</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01171858890057835</v>
+        <v>0.01171858890057832</v>
       </c>
     </row>
     <row r="6">
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007505480251263607</v>
+        <v>0.007505480251263619</v>
       </c>
       <c r="C6" t="n">
         <v>0.00924724097884836</v>
@@ -4035,13 +4035,13 @@
         <v>0.00924724097884836</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00884524936396584</v>
+        <v>0.008845249363965852</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005232007712998268</v>
+        <v>0.005232007712998281</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009247240532323722</v>
+        <v>0.009247240532323717</v>
       </c>
       <c r="H6" t="n">
         <v>0.00924724097884836</v>
@@ -4050,28 +4050,28 @@
         <v>0.00924724097884836</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009245488773422605</v>
+        <v>0.009245488773422612</v>
       </c>
       <c r="K6" t="n">
         <v>0.00924724097884836</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00924724097884836</v>
+        <v>0.009247240978848364</v>
       </c>
       <c r="M6" t="n">
         <v>0.00924724097884836</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03696125958467317</v>
+        <v>0.00924724097884836</v>
       </c>
       <c r="O6" t="n">
-        <v>0.009824457608826593</v>
+        <v>0.009824457608826612</v>
       </c>
       <c r="P6" t="n">
-        <v>0.009949992419588775</v>
+        <v>0.009949992419588782</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.009247240532323722</v>
+        <v>0.009247240532323717</v>
       </c>
       <c r="R6" t="n">
         <v>0.00924724097884836</v>
@@ -4086,25 +4086,25 @@
         <v>0.00924724097884836</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01124620263133357</v>
+        <v>0.01124620263133359</v>
       </c>
       <c r="W6" t="n">
         <v>0.00924724097884836</v>
       </c>
       <c r="X6" t="n">
-        <v>0.00924724097884836</v>
+        <v>0.009247240978848364</v>
       </c>
       <c r="Y6" t="n">
         <v>0.00924724097884836</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.008197113966211802</v>
+        <v>0.008197113966211795</v>
       </c>
       <c r="AA6" t="n">
         <v>0.00924724097884836</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.00924724097884836</v>
+        <v>0.009247240978848362</v>
       </c>
     </row>
     <row r="7">
@@ -4114,73 +4114,73 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01399746581811065</v>
+        <v>0.01399746581811067</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01459538477583589</v>
+        <v>0.0145953847758359</v>
       </c>
       <c r="D7" t="n">
         <v>0.01380574057330125</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01149239198098597</v>
+        <v>0.01149239198098599</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01417789935456665</v>
+        <v>0.01417789935456666</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01350758365522902</v>
+        <v>0.01350758365522903</v>
       </c>
       <c r="H7" t="n">
         <v>0.01332172217803656</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01338506166996186</v>
+        <v>0.01338506166996187</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01340785180861228</v>
+        <v>0.01340785180861227</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01282458419197048</v>
+        <v>0.01282458419197046</v>
       </c>
       <c r="L7" t="n">
         <v>0.01377238284713391</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01149585251266515</v>
+        <v>0.01149585251266514</v>
       </c>
       <c r="N7" t="n">
         <v>0.01414457660233143</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01400868780710185</v>
+        <v>0.01400868780710186</v>
       </c>
       <c r="P7" t="n">
         <v>0.01373716623617394</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01423562281206364</v>
+        <v>0.01423562281206365</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01341391271549315</v>
+        <v>0.01341391271549316</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01364264567113274</v>
+        <v>0.01364264567113273</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01329066790343417</v>
+        <v>0.01329066790343415</v>
       </c>
       <c r="U7" t="n">
         <v>0.01314060814424815</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01368866390163822</v>
+        <v>0.01368866390163823</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01272142420463366</v>
+        <v>0.01272142420463365</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01247335765992783</v>
+        <v>0.01247335765992784</v>
       </c>
       <c r="Y7" t="n">
         <v>0.01141474544120178</v>
@@ -4192,7 +4192,7 @@
         <v>0.0127604108679911</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01243616145037351</v>
+        <v>0.01243616145037352</v>
       </c>
     </row>
     <row r="8">
@@ -4202,46 +4202,46 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01439930455508877</v>
+        <v>0.0143993045550888</v>
       </c>
       <c r="C8" t="n">
         <v>0.01458571844004532</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0143472566694936</v>
+        <v>0.01434725666949361</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01159485475107319</v>
+        <v>0.01159485475107318</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01446278352175579</v>
+        <v>0.0144627835217558</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01415307637922619</v>
+        <v>0.0141530763792262</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01421152454761431</v>
+        <v>0.0142115245476143</v>
       </c>
       <c r="I8" t="n">
         <v>0.0142281600158375</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01423149696431433</v>
+        <v>0.01423149696431431</v>
       </c>
       <c r="K8" t="n">
         <v>0.01407255799654574</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01433595582814855</v>
+        <v>0.01433595582814853</v>
       </c>
       <c r="M8" t="n">
         <v>0.01369269673472199</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01444301597895938</v>
+        <v>0.01444301597895936</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01440228845318471</v>
+        <v>0.01440228845318472</v>
       </c>
       <c r="P8" t="n">
         <v>0.01432385913648576</v>
@@ -4259,13 +4259,13 @@
         <v>0.01420091127504064</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01415497324162685</v>
+        <v>0.01415497324162686</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01423955022637397</v>
+        <v>0.01423955022637398</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01403616293292767</v>
+        <v>0.01403616293292768</v>
       </c>
       <c r="X8" t="n">
         <v>0.01392932606827809</v>
@@ -4274,13 +4274,13 @@
         <v>0.01366372553335164</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01443811054878123</v>
+        <v>0.01443811054878122</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0140475955475279</v>
+        <v>0.01404759554752789</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01385507093221904</v>
+        <v>0.01385507093221905</v>
       </c>
     </row>
   </sheetData>
@@ -4446,16 +4446,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01472415981554427</v>
+        <v>0.01472415981554426</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01470494963371391</v>
+        <v>0.0147049496337139</v>
       </c>
       <c r="D2" t="n">
         <v>0.01480490832563216</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01171677691425787</v>
+        <v>0.01171677691425788</v>
       </c>
       <c r="F2" t="n">
         <v>0.01472571645350603</v>
@@ -4467,34 +4467,34 @@
         <v>0.01484224569327413</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01481394093422987</v>
+        <v>0.01481394093422986</v>
       </c>
       <c r="J2" t="n">
         <v>0.01478758166713184</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01488493460661471</v>
+        <v>0.0148849346066147</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01482031330442512</v>
+        <v>0.01482031330442511</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0149442524125311</v>
+        <v>0.01494425241253109</v>
       </c>
       <c r="N2" t="n">
         <v>0.01484100950080583</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01473984501203708</v>
+        <v>0.01473984501203709</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01477870200792433</v>
+        <v>0.01477870200792432</v>
       </c>
       <c r="Q2" t="n">
         <v>0.01477189406083124</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01481363487988162</v>
+        <v>0.01481363487988161</v>
       </c>
       <c r="S2" t="n">
         <v>0.01478461150123229</v>
@@ -4503,7 +4503,7 @@
         <v>0.01477551358277293</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01485237680032459</v>
+        <v>0.0148523768003246</v>
       </c>
       <c r="V2" t="n">
         <v>0.01471977880339401</v>
@@ -4512,13 +4512,13 @@
         <v>0.01504959366587698</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0148152043908231</v>
+        <v>0.01481520439082309</v>
       </c>
       <c r="Y2" t="n">
         <v>0.01474336329077492</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01477299682379599</v>
+        <v>0.01477299682379598</v>
       </c>
       <c r="AA2" t="n">
         <v>0.0148954026187814</v>
@@ -4543,7 +4543,7 @@
         <v>0.01493039387731158</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01186786635082122</v>
+        <v>0.01186786635082124</v>
       </c>
       <c r="F3" t="n">
         <v>0.01493809872393426</v>
@@ -4558,10 +4558,10 @@
         <v>0.01493039387731158</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01492675164894533</v>
+        <v>0.01492675164894532</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01493453298815909</v>
+        <v>0.0149345329881591</v>
       </c>
       <c r="L3" t="n">
         <v>0.01493039387731158</v>
@@ -4622,85 +4622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01688127680723885</v>
+        <v>0.01688127680723886</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007878274934956452</v>
+        <v>0.007878274934956438</v>
       </c>
       <c r="D4" t="n">
         <v>0.04127791828176836</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02007575715602339</v>
+        <v>0.02007575715602338</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01716262326043846</v>
+        <v>0.01716262326043844</v>
       </c>
       <c r="G4" t="n">
         <v>0.02299416013684964</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05408873794034081</v>
+        <v>0.05408873794034082</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04438981874960144</v>
+        <v>0.04438981874960141</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03435677112620885</v>
+        <v>0.03435677112620886</v>
       </c>
       <c r="K4" t="n">
         <v>0.05735737250711168</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03955454944642766</v>
+        <v>0.03955454944642769</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0742288512841127</v>
+        <v>0.07422885128411272</v>
       </c>
       <c r="N4" t="n">
         <v>0.04921252722493451</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02037931086533111</v>
+        <v>0.02037931086533114</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03088179191634164</v>
+        <v>0.03088179191634155</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03038627349957817</v>
+        <v>0.03038627349957813</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04510849714109545</v>
+        <v>0.04510849714109541</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0292912573252489</v>
+        <v>0.02929125732524889</v>
       </c>
       <c r="T4" t="n">
-        <v>0.03209908535174081</v>
+        <v>0.03209908535174077</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05027249400861175</v>
+        <v>0.05027249400861181</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01731118261867321</v>
+        <v>0.0173111826186732</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1066271702027564</v>
+        <v>0.1066271702027565</v>
       </c>
       <c r="X4" t="n">
-        <v>0.04643565360439857</v>
+        <v>0.0464356536043986</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02322385702293575</v>
+        <v>0.02322385702293573</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02810040776985543</v>
+        <v>0.02810040776985541</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.06452250028896017</v>
+        <v>0.0645225002889601</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.07050865239119923</v>
+        <v>0.07050865239119915</v>
       </c>
     </row>
     <row r="5">
@@ -4710,85 +4710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.005664200626796178</v>
+        <v>0.005664200626796187</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008586248738889767</v>
+        <v>0.008586248738889777</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008586248738889767</v>
+        <v>0.008586248738889777</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00703034431528019</v>
+        <v>0.007030344315280183</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006119421571426863</v>
+        <v>0.006119421571426873</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009192154449927685</v>
+        <v>0.009192154449927679</v>
       </c>
       <c r="H5" t="n">
-        <v>0.008586248738889767</v>
+        <v>0.008586248738889777</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008586248738889767</v>
+        <v>0.008586248738889777</v>
       </c>
       <c r="J5" t="n">
-        <v>0.008583980497527694</v>
+        <v>0.008583980497527696</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008586248738889767</v>
+        <v>0.008586248738889777</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008586248738889767</v>
+        <v>0.008586248738889777</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008586248738889983</v>
+        <v>0.008586248738889994</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04921252722493451</v>
+        <v>0.006321172602777369</v>
       </c>
       <c r="O5" t="n">
-        <v>0.006943635189699831</v>
+        <v>0.006943635189699833</v>
       </c>
       <c r="P5" t="n">
-        <v>0.006791054569118459</v>
+        <v>0.006791054569118466</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.00508995148170431</v>
+        <v>0.005089951481704314</v>
       </c>
       <c r="R5" t="n">
-        <v>0.008586248738889767</v>
+        <v>0.008586248738889777</v>
       </c>
       <c r="S5" t="n">
-        <v>0.008586248738889767</v>
+        <v>0.008586248738889777</v>
       </c>
       <c r="T5" t="n">
-        <v>0.008586248738889767</v>
+        <v>0.008586248738889777</v>
       </c>
       <c r="U5" t="n">
-        <v>0.007158254257487152</v>
+        <v>0.007158254257487156</v>
       </c>
       <c r="V5" t="n">
-        <v>0.007771318370718054</v>
+        <v>0.007771318370718048</v>
       </c>
       <c r="W5" t="n">
-        <v>0.008586823000076443</v>
+        <v>0.008586823000076453</v>
       </c>
       <c r="X5" t="n">
-        <v>0.005357762994280674</v>
+        <v>0.005357762994280671</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01148852653223042</v>
+        <v>0.01148852653223043</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.005609922083426942</v>
+        <v>0.005609922083426933</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.008586248738889767</v>
+        <v>0.008586248738889777</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01163857232489208</v>
+        <v>0.01163857232489206</v>
       </c>
     </row>
     <row r="6">
@@ -4798,85 +4798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007967634715745929</v>
+        <v>0.007967634715745927</v>
       </c>
       <c r="C6" t="n">
-        <v>0.009876492498674684</v>
+        <v>0.009876492498674687</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009876492498674684</v>
+        <v>0.009876492498674687</v>
       </c>
       <c r="E6" t="n">
-        <v>0.009435936249259926</v>
+        <v>0.009435936249259933</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005476053754005382</v>
+        <v>0.005476053754005386</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009876492941725042</v>
+        <v>0.009876492941725048</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009876492498674684</v>
+        <v>0.009876492498674687</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009876492498674684</v>
+        <v>0.009876492498674687</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009874224257312594</v>
+        <v>0.009874224257312601</v>
       </c>
       <c r="K6" t="n">
-        <v>0.009876492498674684</v>
+        <v>0.009876492498674687</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009876492498674684</v>
+        <v>0.009876492498674687</v>
       </c>
       <c r="M6" t="n">
-        <v>0.009876492498674684</v>
+        <v>0.009876492498674687</v>
       </c>
       <c r="N6" t="n">
-        <v>0.04921252722493451</v>
+        <v>0.009876492498674687</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01050908605837788</v>
+        <v>0.0105090860583779</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01064666420777987</v>
+        <v>0.01064666420777989</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.009876492941725042</v>
+        <v>0.009876492941725048</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009876492498674684</v>
+        <v>0.009876492498674687</v>
       </c>
       <c r="S6" t="n">
-        <v>0.009876492498674684</v>
+        <v>0.009876492498674687</v>
       </c>
       <c r="T6" t="n">
-        <v>0.009876492498674684</v>
+        <v>0.009876492498674687</v>
       </c>
       <c r="U6" t="n">
-        <v>0.009876492498674684</v>
+        <v>0.009876492498674687</v>
       </c>
       <c r="V6" t="n">
         <v>0.01206494746778434</v>
       </c>
       <c r="W6" t="n">
-        <v>0.009876492498674684</v>
+        <v>0.009876492498674687</v>
       </c>
       <c r="X6" t="n">
-        <v>0.009876492498674684</v>
+        <v>0.009876492498674687</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.009876492498674684</v>
+        <v>0.009876492498674687</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.008725621173755919</v>
+        <v>0.008725621173755934</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.009876492498674684</v>
+        <v>0.009876492498674687</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.009876492498674684</v>
+        <v>0.009876492498674687</v>
       </c>
     </row>
     <row r="7">
@@ -4889,55 +4889,55 @@
         <v>0.01458467137901459</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01483795477295389</v>
+        <v>0.01483795477295388</v>
       </c>
       <c r="D7" t="n">
         <v>0.01411704266175111</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0114776283293401</v>
+        <v>0.01147762832934013</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01463137334087462</v>
+        <v>0.01463137334087461</v>
       </c>
       <c r="G7" t="n">
         <v>0.01433529375083875</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01390531265399329</v>
+        <v>0.0139053126539933</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01406575940512303</v>
+        <v>0.01406575940512304</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01418798496568564</v>
+        <v>0.01418798496568565</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01367279202926864</v>
+        <v>0.01367279202926863</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01401841030110371</v>
+        <v>0.0140184103011037</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01330683204919662</v>
+        <v>0.01330683204919661</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01390123435924517</v>
+        <v>0.01390123435924516</v>
       </c>
       <c r="O7" t="n">
         <v>0.01449033707645069</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01425870821645452</v>
+        <v>0.01425870821645453</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01430882640989683</v>
+        <v>0.01430882640989682</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01407425346333036</v>
+        <v>0.01407425346333038</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01422721812540958</v>
+        <v>0.01422721812540957</v>
       </c>
       <c r="T7" t="n">
         <v>0.01428940035457696</v>
@@ -4949,16 +4949,16 @@
         <v>0.01456840411111756</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0126667283889193</v>
+        <v>0.01266672838891929</v>
       </c>
       <c r="X7" t="n">
         <v>0.01398434979092442</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01447360426356539</v>
+        <v>0.0144736042635654</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01430095335189153</v>
+        <v>0.01430095335189152</v>
       </c>
       <c r="AA7" t="n">
         <v>0.01357786225103857</v>
@@ -4977,19 +4977,19 @@
         <v>0.01456685497706691</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01465318215605644</v>
+        <v>0.01465318215605643</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01443483093055562</v>
+        <v>0.01443483093055561</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01153921737086919</v>
+        <v>0.0115392173708692</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0145861554267381</v>
+        <v>0.01458615542673809</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01444342400664693</v>
+        <v>0.01444342400664692</v>
       </c>
       <c r="H8" t="n">
         <v>0.01437583046992428</v>
@@ -4998,7 +4998,7 @@
         <v>0.01442052949395751</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01445144047193897</v>
+        <v>0.01445144047193896</v>
       </c>
       <c r="K8" t="n">
         <v>0.01431083844938968</v>
@@ -5010,28 +5010,28 @@
         <v>0.01420554028348129</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01437273864034884</v>
+        <v>0.01437273864034883</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01453965589337691</v>
+        <v>0.0145396558933769</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01447309363342056</v>
+        <v>0.01447309363342055</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01448907942338195</v>
+        <v>0.01448907942338196</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01442373527770764</v>
+        <v>0.01442373527770763</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01446466429322873</v>
+        <v>0.01446466429322872</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01448387607217148</v>
+        <v>0.01448387607217146</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01435099770269802</v>
+        <v>0.01435099770269803</v>
       </c>
       <c r="V8" t="n">
         <v>0.01455780269727821</v>
@@ -5049,7 +5049,7 @@
         <v>0.01448616673976818</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01427999641856466</v>
+        <v>0.01427999641856464</v>
       </c>
       <c r="AB8" t="n">
         <v>0.01412108637024517</v>
@@ -5218,7 +5218,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01463556884895487</v>
+        <v>0.01463556884895486</v>
       </c>
       <c r="C2" t="n">
         <v>0.01466447138377023</v>
@@ -5230,49 +5230,49 @@
         <v>0.01166097133629214</v>
       </c>
       <c r="F2" t="n">
-        <v>0.014669801577771</v>
+        <v>0.01466980157777099</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01457626587195753</v>
+        <v>0.01457626587195752</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01470639389089618</v>
+        <v>0.01470639389089617</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01469710816943595</v>
+        <v>0.01469710816943594</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01467799051618084</v>
+        <v>0.01467799051618083</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0146694994635223</v>
+        <v>0.01466949946352229</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01465932285696407</v>
+        <v>0.01465932285696406</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01464139342314171</v>
+        <v>0.01464139342314169</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01468292573725189</v>
+        <v>0.01468292573725188</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01467839186225584</v>
+        <v>0.01467839186225582</v>
       </c>
       <c r="P2" t="n">
         <v>0.01466487595395845</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01464016108223056</v>
+        <v>0.01464016108223055</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01467301257570373</v>
+        <v>0.01467301257570372</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01468286090883301</v>
+        <v>0.014682860908833</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01465793264977559</v>
+        <v>0.01465793264977557</v>
       </c>
       <c r="U2" t="n">
         <v>0.01463439639374163</v>
@@ -5281,16 +5281,16 @@
         <v>0.01466285919260252</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01486011601347028</v>
+        <v>0.01486011601347027</v>
       </c>
       <c r="X2" t="n">
         <v>0.01474400511035779</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01470592961878231</v>
+        <v>0.01470592961878229</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0146983770530345</v>
+        <v>0.01469837705303448</v>
       </c>
       <c r="AA2" t="n">
         <v>0.01477377806926961</v>
@@ -5315,7 +5315,7 @@
         <v>0.01486663079813583</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01182626423827333</v>
+        <v>0.01182626423827332</v>
       </c>
       <c r="F3" t="n">
         <v>0.01487750483073629</v>
@@ -5330,7 +5330,7 @@
         <v>0.01486663079813583</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01486462128457288</v>
+        <v>0.01486462128457289</v>
       </c>
       <c r="K3" t="n">
         <v>0.01487250184706926</v>
@@ -5339,7 +5339,7 @@
         <v>0.01486663079813583</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01486654949329152</v>
+        <v>0.01486654949329151</v>
       </c>
       <c r="N3" t="n">
         <v>0.01486663079813583</v>
@@ -5351,10 +5351,10 @@
         <v>0.01486661895615958</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01486662960903995</v>
+        <v>0.01486662960903994</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01484433489772831</v>
+        <v>0.0148443348977283</v>
       </c>
       <c r="S3" t="n">
         <v>0.01486663079813583</v>
@@ -5366,7 +5366,7 @@
         <v>0.01486631342883352</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01485389144510184</v>
+        <v>0.01485389144510181</v>
       </c>
       <c r="W3" t="n">
         <v>0.01486663079813583</v>
@@ -5375,16 +5375,16 @@
         <v>0.0147323205626928</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01486639953316976</v>
+        <v>0.01486639953316975</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01486822961330364</v>
+        <v>0.01486822961330363</v>
       </c>
       <c r="AA3" t="n">
         <v>0.01486663079813583</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01470313307956573</v>
+        <v>0.01470313307956572</v>
       </c>
     </row>
     <row r="4">
@@ -5394,85 +5394,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009848084345927597</v>
+        <v>0.009848084345927611</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01256260761980197</v>
+        <v>0.01256260761980196</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01475135835088508</v>
+        <v>0.01475135835088506</v>
       </c>
       <c r="E4" t="n">
         <v>0.01496250964852227</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01670592837472674</v>
+        <v>0.01670592837472673</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01612797370489174</v>
+        <v>0.01612797370489177</v>
       </c>
       <c r="H4" t="n">
         <v>0.03012511913298887</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02648208287889161</v>
+        <v>0.02648208287889156</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02018081084683434</v>
+        <v>0.02018081084683433</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01691020005086416</v>
+        <v>0.01691020005086415</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01452027516070023</v>
+        <v>0.0145202751607002</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01183110639498215</v>
+        <v>0.01183110639498214</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0217677903144405</v>
+        <v>0.02176779031444048</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01921209437152561</v>
+        <v>0.01921209437152563</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0165725767365075</v>
+        <v>0.01657257673650752</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01094572069772088</v>
+        <v>0.01094572069772087</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02602335993086623</v>
+        <v>0.0260233599308662</v>
       </c>
       <c r="S4" t="n">
         <v>0.01941076908263829</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01601955485841807</v>
+        <v>0.01601955485841806</v>
       </c>
       <c r="U4" t="n">
-        <v>0.009724034082453115</v>
+        <v>0.00972403408245311</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01860896285009745</v>
+        <v>0.0186089628500975</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06341617694540656</v>
+        <v>0.06341617694540654</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06607334009734334</v>
+        <v>0.06607334009734347</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02823631665184402</v>
+        <v>0.0282363166518441</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02315367168000729</v>
+        <v>0.02315367168000724</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.04524784250547974</v>
+        <v>0.04524784250547983</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.007158553952097398</v>
+        <v>0.00715855395209739</v>
       </c>
     </row>
     <row r="5">
@@ -5482,85 +5482,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.005138235015339835</v>
+        <v>0.005138235015339822</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007724645276981051</v>
+        <v>0.007724645276981024</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007724645276981051</v>
+        <v>0.007724645276981024</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006347458107962017</v>
+        <v>0.006347458107962</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005541167505594984</v>
+        <v>0.005541167505594973</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008260954293279024</v>
+        <v>0.008260954293278996</v>
       </c>
       <c r="H5" t="n">
-        <v>0.007724645276981051</v>
+        <v>0.007724645276981024</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007724645276981051</v>
+        <v>0.007724645276981024</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007722935468496641</v>
+        <v>0.00772293546849661</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007724645276981051</v>
+        <v>0.007724645276981024</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007724645276981051</v>
+        <v>0.007724645276981024</v>
       </c>
       <c r="M5" t="n">
-        <v>0.007724645276980767</v>
+        <v>0.007724645276980739</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0217677903144405</v>
+        <v>0.005719744626054037</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00627070873077913</v>
+        <v>0.006270708730779101</v>
       </c>
       <c r="P5" t="n">
-        <v>0.006135654115808749</v>
+        <v>0.00613565411580873</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.004629946368316709</v>
+        <v>0.004629946368316705</v>
       </c>
       <c r="R5" t="n">
-        <v>0.007724645276981051</v>
+        <v>0.007724645276981024</v>
       </c>
       <c r="S5" t="n">
-        <v>0.007724645276981051</v>
+        <v>0.007724645276981024</v>
       </c>
       <c r="T5" t="n">
-        <v>0.007724645276981051</v>
+        <v>0.007724645276981024</v>
       </c>
       <c r="U5" t="n">
-        <v>0.00646092003680625</v>
+        <v>0.006460920036806234</v>
       </c>
       <c r="V5" t="n">
-        <v>0.007005542538766509</v>
+        <v>0.007005542538766485</v>
       </c>
       <c r="W5" t="n">
-        <v>0.00772515357609263</v>
+        <v>0.00772515357609261</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004866996005210765</v>
+        <v>0.004866996005210748</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01029397390851764</v>
+        <v>0.01029397390851761</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.005090191117324327</v>
+        <v>0.005090191117324313</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.007724645276981051</v>
+        <v>0.007724645276981024</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01042636706296317</v>
+        <v>0.01042636706296315</v>
       </c>
     </row>
     <row r="6">
@@ -5570,85 +5570,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.006883228265873794</v>
+        <v>0.006883228265873789</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008491558200263451</v>
+        <v>0.008491558200263453</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008491558200263451</v>
+        <v>0.008491558200263453</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008120363038059197</v>
+        <v>0.008120363038059185</v>
       </c>
       <c r="F6" t="n">
         <v>0.004783917344289863</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008491559274613683</v>
+        <v>0.008491559274613682</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008491558200263451</v>
+        <v>0.008491558200263453</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008491558200263451</v>
+        <v>0.008491558200263453</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008489848391779064</v>
+        <v>0.008489848391779032</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008491558200263451</v>
+        <v>0.008491558200263453</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008491558200263451</v>
+        <v>0.008491558200263453</v>
       </c>
       <c r="M6" t="n">
-        <v>0.008491558200263451</v>
+        <v>0.008491558200263453</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0217677903144405</v>
+        <v>0.008491558200263453</v>
       </c>
       <c r="O6" t="n">
-        <v>0.009024558064980299</v>
+        <v>0.009024558064980292</v>
       </c>
       <c r="P6" t="n">
-        <v>0.009140476157165879</v>
+        <v>0.009140476157165867</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.008491559274613683</v>
+        <v>0.008491559274613682</v>
       </c>
       <c r="R6" t="n">
-        <v>0.008491558200263451</v>
+        <v>0.008491558200263453</v>
       </c>
       <c r="S6" t="n">
-        <v>0.008491558200263451</v>
+        <v>0.008491558200263453</v>
       </c>
       <c r="T6" t="n">
-        <v>0.008491558200263451</v>
+        <v>0.008491558200263453</v>
       </c>
       <c r="U6" t="n">
-        <v>0.008491558200263451</v>
+        <v>0.008491558200263453</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01033680986452429</v>
+        <v>0.01033680986452427</v>
       </c>
       <c r="W6" t="n">
-        <v>0.008491558200263451</v>
+        <v>0.008491558200263453</v>
       </c>
       <c r="X6" t="n">
-        <v>0.008491558200263451</v>
+        <v>0.008491558200263453</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.008491558200263451</v>
+        <v>0.008491558200263453</v>
       </c>
       <c r="Z6" t="n">
         <v>0.007521878694716979</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.008491558200263451</v>
+        <v>0.008491558200263453</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.008491558200263451</v>
+        <v>0.008491558200263453</v>
       </c>
     </row>
     <row r="7">
@@ -5658,13 +5658,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01467516768009554</v>
+        <v>0.01467516768009553</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01465091320909163</v>
+        <v>0.01465091320909162</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01457706332141303</v>
+        <v>0.01457706332141301</v>
       </c>
       <c r="E7" t="n">
         <v>0.01152452577878701</v>
@@ -5682,16 +5682,16 @@
         <v>0.01431871203564277</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01441167980487321</v>
+        <v>0.01441167980487322</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01451618971034774</v>
+        <v>0.01451618971034773</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01453595237040362</v>
+        <v>0.01453595237040361</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01464436920418097</v>
+        <v>0.01464436920418096</v>
       </c>
       <c r="N7" t="n">
         <v>0.0143987749257819</v>
@@ -5700,7 +5700,7 @@
         <v>0.01441931502162322</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01450001051412481</v>
+        <v>0.01450001051412482</v>
       </c>
       <c r="Q7" t="n">
         <v>0.01465068619464534</v>
@@ -5709,19 +5709,19 @@
         <v>0.01431926640430401</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01439528521940259</v>
+        <v>0.01439528521940258</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01454667504141127</v>
+        <v>0.01454667504141126</v>
       </c>
       <c r="U7" t="n">
         <v>0.01468109493596105</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0144246950590647</v>
+        <v>0.01442469505906467</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01335143125649093</v>
+        <v>0.01335143125649092</v>
       </c>
       <c r="X7" t="n">
         <v>0.01318825316588403</v>
@@ -5733,7 +5733,7 @@
         <v>0.01431242041975962</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01386181493920239</v>
+        <v>0.01386181493920238</v>
       </c>
       <c r="AB7" t="n">
         <v>0.01459943246073212</v>
@@ -5746,43 +5746,43 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01454845252008979</v>
+        <v>0.01454845252008978</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01455612441551166</v>
+        <v>0.01455612441551165</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01452107212028426</v>
+        <v>0.01452107212028424</v>
       </c>
       <c r="E8" t="n">
         <v>0.01152367937564245</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01452002808309935</v>
+        <v>0.01452002808309934</v>
       </c>
       <c r="G8" t="n">
         <v>0.01440629952804452</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01443372950752725</v>
+        <v>0.01443372950752724</v>
       </c>
       <c r="I8" t="n">
         <v>0.01444780338638812</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01447190069947865</v>
+        <v>0.01447190069947864</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0145073763058146</v>
+        <v>0.01450737630581459</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01450886311853629</v>
+        <v>0.01450886311853628</v>
       </c>
       <c r="M8" t="n">
         <v>0.01454030068354981</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01447004982436265</v>
+        <v>0.01447004982436264</v>
       </c>
       <c r="O8" t="n">
         <v>0.01447490433582172</v>
@@ -5797,7 +5797,7 @@
         <v>0.01443410473790166</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01446839716842014</v>
+        <v>0.01446839716842015</v>
       </c>
       <c r="T8" t="n">
         <v>0.0145124006034056</v>
@@ -5809,7 +5809,7 @@
         <v>0.01446757346918789</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01417069539336742</v>
+        <v>0.01417069539336741</v>
       </c>
       <c r="X8" t="n">
         <v>0.01404144952415897</v>
@@ -5821,10 +5821,10 @@
         <v>0.01444548209871317</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01431658365129675</v>
+        <v>0.01431658365129674</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01442450646874966</v>
+        <v>0.01442450646874965</v>
       </c>
     </row>
   </sheetData>
@@ -5990,64 +5990,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01447115815080082</v>
+        <v>0.01447115815080081</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01448528055416858</v>
+        <v>0.01448528055416856</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01447985472940054</v>
+        <v>0.01447985472940053</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01167216753305261</v>
+        <v>0.01167216753305259</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01448762736749961</v>
+        <v>0.0144876273674996</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0143171072287122</v>
+        <v>0.01431710722871219</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01449858551884333</v>
+        <v>0.01449858551884332</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01448203422520159</v>
+        <v>0.01448203422520157</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01449176046629025</v>
+        <v>0.01449176046629024</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01447471920517975</v>
+        <v>0.01447471920517974</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01448287179446196</v>
+        <v>0.01448287179446195</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01446556154137062</v>
+        <v>0.01446556154137061</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0144842634986464</v>
+        <v>0.01448426349864638</v>
       </c>
       <c r="O2" t="n">
         <v>0.01454239454306046</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01449473812111995</v>
+        <v>0.01449473812111994</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01446075528340235</v>
+        <v>0.01446075528340234</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01447544158707721</v>
+        <v>0.0144754415870772</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01449234275134315</v>
+        <v>0.01449234275134314</v>
       </c>
       <c r="T2" t="n">
         <v>0.01446807783280351</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01446345160917095</v>
+        <v>0.01446345160917094</v>
       </c>
       <c r="V2" t="n">
         <v>0.0143780801773436</v>
@@ -6056,19 +6056,19 @@
         <v>0.01463301553144639</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01469090963393812</v>
+        <v>0.01469090963393811</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01451698251460814</v>
+        <v>0.01451698251460813</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01449776044619105</v>
+        <v>0.01449776044619104</v>
       </c>
       <c r="AA2" t="n">
         <v>0.0146058309015862</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01431099759194287</v>
+        <v>0.01431099759194285</v>
       </c>
     </row>
     <row r="3">
@@ -6087,10 +6087,10 @@
         <v>0.01468558585858018</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01182354758393708</v>
+        <v>0.01182354758393707</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01470001774918527</v>
+        <v>0.01470001774918526</v>
       </c>
       <c r="G3" t="n">
         <v>0.01451683478061015</v>
@@ -6102,7 +6102,7 @@
         <v>0.01468558585858018</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0146848345944822</v>
+        <v>0.01468483459448218</v>
       </c>
       <c r="K3" t="n">
         <v>0.01469311230894572</v>
@@ -6150,13 +6150,13 @@
         <v>0.01468518010209744</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01468715900488693</v>
+        <v>0.01468715900488692</v>
       </c>
       <c r="AA3" t="n">
         <v>0.01468558585858018</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01452208814001008</v>
+        <v>0.01452208814001007</v>
       </c>
     </row>
     <row r="4">
@@ -6169,82 +6169,82 @@
         <v>0.01297362427920204</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0123449259059561</v>
+        <v>0.01234492590595611</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01615940151820075</v>
+        <v>0.01615940151820074</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01767646916758765</v>
+        <v>0.01767646916758764</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01510839172623384</v>
+        <v>0.01510839172623386</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01286341948191532</v>
+        <v>0.01286341948191534</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02198689722701459</v>
+        <v>0.0219868972270146</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01712683644399359</v>
+        <v>0.01712683644399357</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01835592795623368</v>
+        <v>0.01835592795623371</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01293303690965829</v>
+        <v>0.01293303690965828</v>
       </c>
       <c r="L4" t="n">
         <v>0.01531849933797075</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01270639473611442</v>
+        <v>0.01270639473611443</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01703527514673336</v>
+        <v>0.01703527514673335</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02862854351444535</v>
+        <v>0.02862854351444533</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0181933109802532</v>
+        <v>0.01819331098025317</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01095087415915186</v>
+        <v>0.01095087415915187</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02609942455575609</v>
+        <v>0.02609942455575603</v>
       </c>
       <c r="S4" t="n">
         <v>0.01754195933555507</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01336535150817851</v>
+        <v>0.0133653515081785</v>
       </c>
       <c r="U4" t="n">
         <v>0.01127133862977345</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02144581197593359</v>
+        <v>0.02144581197593362</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05272880477471682</v>
+        <v>0.0527288047747169</v>
       </c>
       <c r="X4" t="n">
-        <v>0.07898155394788296</v>
+        <v>0.07898155394788299</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02578328401759879</v>
+        <v>0.02578328401759885</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01790880808053554</v>
+        <v>0.01790880808053552</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.04797969797169477</v>
+        <v>0.04797969797169479</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.01181225247416884</v>
+        <v>0.01181225247416883</v>
       </c>
     </row>
     <row r="5">
@@ -6254,7 +6254,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.005094953715071003</v>
+        <v>0.005094953715071007</v>
       </c>
       <c r="C5" t="n">
         <v>0.007647843942282745</v>
@@ -6263,13 +6263,13 @@
         <v>0.007647843942282745</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006288505202813199</v>
+        <v>0.006288505202813196</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005492664175722011</v>
+        <v>0.005492664175722012</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00817720236108088</v>
+        <v>0.008177202361080884</v>
       </c>
       <c r="H5" t="n">
         <v>0.007647843942282745</v>
@@ -6278,7 +6278,7 @@
         <v>0.007647843942282745</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007646285086221875</v>
+        <v>0.007646285086221883</v>
       </c>
       <c r="K5" t="n">
         <v>0.007647843942282745</v>
@@ -6290,16 +6290,16 @@
         <v>0.007647843942282323</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01703527514673336</v>
+        <v>0.005668926925824941</v>
       </c>
       <c r="O5" t="n">
-        <v>0.006212750502199225</v>
+        <v>0.006212750502199215</v>
       </c>
       <c r="P5" t="n">
-        <v>0.006079446203265398</v>
+        <v>0.006079446203265388</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.004593252519863852</v>
+        <v>0.00459325251986386</v>
       </c>
       <c r="R5" t="n">
         <v>0.007647843942282745</v>
@@ -6311,22 +6311,22 @@
         <v>0.007647843942282745</v>
       </c>
       <c r="U5" t="n">
-        <v>0.006400707184953012</v>
+        <v>0.006400707184953013</v>
       </c>
       <c r="V5" t="n">
-        <v>0.006939095346214886</v>
+        <v>0.00693909534621489</v>
       </c>
       <c r="W5" t="n">
-        <v>0.007648345653773208</v>
+        <v>0.007648345653773204</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004827229979013077</v>
+        <v>0.004827229979013072</v>
       </c>
       <c r="Y5" t="n">
         <v>0.01018423406849612</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.005047532468902116</v>
+        <v>0.005047532468902121</v>
       </c>
       <c r="AA5" t="n">
         <v>0.007647843942282745</v>
@@ -6342,85 +6342,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.006485334647420186</v>
+        <v>0.006485334647420191</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007981005199212261</v>
+        <v>0.00798100519921225</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007981005199212261</v>
+        <v>0.00798100519921225</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007635811233381232</v>
+        <v>0.007635811233381216</v>
       </c>
       <c r="F6" t="n">
         <v>0.004533075187710588</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007981006105075284</v>
+        <v>0.007981006105075282</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007981005199212261</v>
+        <v>0.00798100519921225</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007981005199212261</v>
+        <v>0.00798100519921225</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007979446343151396</v>
+        <v>0.007979446343151383</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007981005199212261</v>
+        <v>0.00798100519921225</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007981005199212261</v>
+        <v>0.00798100519921225</v>
       </c>
       <c r="M6" t="n">
-        <v>0.007981005199212261</v>
+        <v>0.00798100519921225</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01703527514673336</v>
+        <v>0.00798100519921225</v>
       </c>
       <c r="O6" t="n">
-        <v>0.008476669667727511</v>
+        <v>0.008476669667727508</v>
       </c>
       <c r="P6" t="n">
-        <v>0.008584467988449827</v>
+        <v>0.00858446798844981</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.007981006105075284</v>
+        <v>0.007981006105075282</v>
       </c>
       <c r="R6" t="n">
-        <v>0.007981005199212261</v>
+        <v>0.00798100519921225</v>
       </c>
       <c r="S6" t="n">
-        <v>0.007981005199212261</v>
+        <v>0.00798100519921225</v>
       </c>
       <c r="T6" t="n">
-        <v>0.007981005199212261</v>
+        <v>0.00798100519921225</v>
       </c>
       <c r="U6" t="n">
-        <v>0.007981005199212261</v>
+        <v>0.00798100519921225</v>
       </c>
       <c r="V6" t="n">
-        <v>0.009697191535697791</v>
+        <v>0.009697191535697787</v>
       </c>
       <c r="W6" t="n">
-        <v>0.007981005199212261</v>
+        <v>0.00798100519921225</v>
       </c>
       <c r="X6" t="n">
-        <v>0.007981005199212261</v>
+        <v>0.00798100519921225</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.007981005199212261</v>
+        <v>0.00798100519921225</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.007079249216404555</v>
+        <v>0.007079249216404552</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.007981005199212261</v>
+        <v>0.00798100519921225</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.007981005199212261</v>
+        <v>0.00798100519921225</v>
       </c>
     </row>
     <row r="7">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01441271303178245</v>
+        <v>0.01441271303178246</v>
       </c>
       <c r="C7" t="n">
         <v>0.01447573790276709</v>
@@ -6439,22 +6439,22 @@
         <v>0.01436600784699733</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01144053139161396</v>
+        <v>0.01144053139161395</v>
       </c>
       <c r="F7" t="n">
         <v>0.01441357686355295</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01424317506837965</v>
+        <v>0.01424317506837966</v>
       </c>
       <c r="H7" t="n">
         <v>0.01425920136857848</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01435386737968385</v>
+        <v>0.01435386737968384</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01428783772347351</v>
+        <v>0.01428783772347349</v>
       </c>
       <c r="K7" t="n">
         <v>0.01444354710218995</v>
@@ -6472,7 +6472,7 @@
         <v>0.01398746475222133</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01426784602994694</v>
+        <v>0.01426784602994693</v>
       </c>
       <c r="Q7" t="n">
         <v>0.01447733939269919</v>
@@ -6487,28 +6487,28 @@
         <v>0.01443417304870083</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01445888321222894</v>
+        <v>0.01445888321222893</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01405611796359194</v>
+        <v>0.01405611796359195</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01345961595564444</v>
+        <v>0.01345961595564443</v>
       </c>
       <c r="X7" t="n">
         <v>0.01273676296064257</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01414272652253202</v>
+        <v>0.01414272652253203</v>
       </c>
       <c r="Z7" t="n">
         <v>0.01426504741360615</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01362092691606981</v>
+        <v>0.01362092691606979</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01431647843030252</v>
+        <v>0.01431647843030253</v>
       </c>
     </row>
     <row r="8">
@@ -6518,43 +6518,43 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01434700014501375</v>
+        <v>0.01434700014501373</v>
       </c>
       <c r="C8" t="n">
         <v>0.01437964414153609</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01433444571569565</v>
+        <v>0.01433444571569566</v>
       </c>
       <c r="E8" t="n">
         <v>0.01149789394494537</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01435729585170399</v>
+        <v>0.01435729585170398</v>
       </c>
       <c r="G8" t="n">
         <v>0.01419259118754558</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01430457921708581</v>
+        <v>0.0143045792170858</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01433110126017967</v>
+        <v>0.01433110126017968</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01431112562482732</v>
+        <v>0.01431112562482733</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01436116624078875</v>
+        <v>0.01436116624078876</v>
       </c>
       <c r="L8" t="n">
         <v>0.01432799025535504</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01435814618859478</v>
+        <v>0.01435814618859477</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01432643542102795</v>
+        <v>0.01432643542102793</v>
       </c>
       <c r="O8" t="n">
         <v>0.01422479592288191</v>
@@ -6575,13 +6575,13 @@
         <v>0.01435375434673976</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0143603642249426</v>
+        <v>0.01436036422494259</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01415203793265961</v>
+        <v>0.01415203793265962</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01407519531867636</v>
+        <v>0.01407519531867635</v>
       </c>
       <c r="X8" t="n">
         <v>0.01383220559840632</v>
@@ -6590,13 +6590,13 @@
         <v>0.0142701644072089</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01430569832696848</v>
+        <v>0.01430569832696847</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01412140768987725</v>
+        <v>0.01412140768987724</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01421744451878666</v>
+        <v>0.01421744451878665</v>
       </c>
     </row>
   </sheetData>
@@ -6765,13 +6765,13 @@
         <v>0.01495308493731114</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01485940298988713</v>
+        <v>0.01485940298988714</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01499068629254611</v>
+        <v>0.01499068629254612</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01180420263658745</v>
+        <v>0.01180420263658746</v>
       </c>
       <c r="F2" t="n">
         <v>0.01490366845443749</v>
@@ -6783,34 +6783,34 @@
         <v>0.0151059423672148</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01503959061410555</v>
+        <v>0.01503959061410556</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01504887991086532</v>
+        <v>0.01504887991086531</v>
       </c>
       <c r="K2" t="n">
         <v>0.01513834778679425</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01504514073378343</v>
+        <v>0.01504514073378344</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01559181064394331</v>
+        <v>0.01559181064394332</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01510609284342866</v>
+        <v>0.01510609284342867</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01495476997457288</v>
+        <v>0.01495476997457289</v>
       </c>
       <c r="P2" t="n">
         <v>0.01500041658115612</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01493320978047261</v>
+        <v>0.01493320978047262</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01504534298003381</v>
+        <v>0.01504534298003382</v>
       </c>
       <c r="S2" t="n">
         <v>0.01498649729847596</v>
@@ -6819,25 +6819,25 @@
         <v>0.01503482535437459</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01510391539652704</v>
+        <v>0.01510391539652705</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0148857654220624</v>
+        <v>0.01488576542206241</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01516309337782662</v>
+        <v>0.01516309337782663</v>
       </c>
       <c r="X2" t="n">
         <v>0.01509738763478959</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01503662861400031</v>
+        <v>0.01503662861400032</v>
       </c>
       <c r="Z2" t="n">
         <v>0.01495441795026337</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01512697394808316</v>
+        <v>0.01512697394808317</v>
       </c>
       <c r="AB2" t="n">
         <v>0.01505942820450714</v>
@@ -6859,10 +6859,10 @@
         <v>0.01506443844831582</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01194118856232512</v>
+        <v>0.01194118856232514</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01507214329493849</v>
+        <v>0.0150721432949385</v>
       </c>
       <c r="G3" t="n">
         <v>0.01498160470407095</v>
@@ -6877,7 +6877,7 @@
         <v>0.01505780483215739</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01506857755916333</v>
+        <v>0.01506857755916334</v>
       </c>
       <c r="L3" t="n">
         <v>0.01506443844831582</v>
@@ -6892,22 +6892,22 @@
         <v>0.01506435465086022</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0150644148403023</v>
+        <v>0.01506441484030231</v>
       </c>
       <c r="Q3" t="n">
         <v>0.01506443725921994</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01506521423509083</v>
+        <v>0.01506521423509084</v>
       </c>
       <c r="S3" t="n">
         <v>0.01506443844831582</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01506440199809207</v>
+        <v>0.01506440199809208</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01506457070402745</v>
+        <v>0.01506457070402746</v>
       </c>
       <c r="V3" t="n">
         <v>0.01504898654461423</v>
@@ -6919,7 +6919,7 @@
         <v>0.01505318623314466</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0150642460418215</v>
+        <v>0.01506424604182151</v>
       </c>
       <c r="Z3" t="n">
         <v>0.0150653892967193</v>
@@ -6928,7 +6928,7 @@
         <v>0.01506443844831582</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01490094072974571</v>
+        <v>0.01490094072974572</v>
       </c>
     </row>
     <row r="4">
@@ -6938,82 +6938,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0408864324945685</v>
+        <v>0.04088643249456892</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01388777134549335</v>
+        <v>0.01388777134549336</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05701368461966497</v>
+        <v>0.05701368461966499</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02402865063995785</v>
+        <v>0.02402865063995793</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0300151593419175</v>
+        <v>0.03001515934191748</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06120443682266435</v>
+        <v>0.06120443682266443</v>
       </c>
       <c r="H4" t="n">
-        <v>0.092757138904485</v>
+        <v>0.09275713890448509</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07088430586381238</v>
+        <v>0.07088430586381229</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06881449230288593</v>
+        <v>0.06881449230288601</v>
       </c>
       <c r="K4" t="n">
-        <v>0.08769782610725903</v>
+        <v>0.08769782610725906</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06661027511049247</v>
+        <v>0.06661027511049331</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2103627567346743</v>
+        <v>0.2103627567346746</v>
       </c>
       <c r="N4" t="n">
-        <v>0.08732258326960099</v>
+        <v>0.08732258326960096</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04040128423199867</v>
+        <v>0.04040128423199864</v>
       </c>
       <c r="P4" t="n">
-        <v>0.05395956969951832</v>
+        <v>0.05395956969951836</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03881902157324526</v>
+        <v>0.03881902157324527</v>
       </c>
       <c r="R4" t="n">
-        <v>0.07401535717162647</v>
+        <v>0.0740153571716264</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04777068112200996</v>
+        <v>0.0477706811220101</v>
       </c>
       <c r="T4" t="n">
         <v>0.06941065054473355</v>
       </c>
       <c r="U4" t="n">
-        <v>0.08244939878684351</v>
+        <v>0.08244939878684381</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02780558584340906</v>
+        <v>0.02780558584340918</v>
       </c>
       <c r="W4" t="n">
         <v>0.1014807560331688</v>
       </c>
       <c r="X4" t="n">
-        <v>0.08862003622844998</v>
+        <v>0.08862003622845059</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06625898441079929</v>
+        <v>0.06625898441079933</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.04130375156475138</v>
+        <v>0.04130375156475139</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.09139194813664026</v>
+        <v>0.09139194813664027</v>
       </c>
       <c r="AB4" t="n">
         <v>0.1243659823813117</v>
@@ -7026,85 +7026,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006072268846553584</v>
+        <v>0.006072268846553599</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009212318969462775</v>
+        <v>0.009212318969462785</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009212318969462775</v>
+        <v>0.009212318969462785</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007540334905765579</v>
+        <v>0.007540334905765594</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006561451956618766</v>
+        <v>0.006561451956618771</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009863428817589918</v>
+        <v>0.009863428817589937</v>
       </c>
       <c r="H5" t="n">
-        <v>0.009212318969462775</v>
+        <v>0.009212318969462783</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009212318969462775</v>
+        <v>0.009212318969462785</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009209397932706396</v>
+        <v>0.009209397932706408</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009212318969462775</v>
+        <v>0.009212318969462785</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009212318969462775</v>
+        <v>0.009212318969462785</v>
       </c>
       <c r="M5" t="n">
-        <v>0.009212318969463345</v>
+        <v>0.009212318969463356</v>
       </c>
       <c r="N5" t="n">
-        <v>0.08732258326960099</v>
+        <v>0.006778254804009779</v>
       </c>
       <c r="O5" t="n">
-        <v>0.007447156768657269</v>
+        <v>0.007447156768657276</v>
       </c>
       <c r="P5" t="n">
-        <v>0.007283192734466659</v>
+        <v>0.007283192734466665</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.005455177330703978</v>
+        <v>0.005455177330703985</v>
       </c>
       <c r="R5" t="n">
-        <v>0.009212318969462775</v>
+        <v>0.009212318969462781</v>
       </c>
       <c r="S5" t="n">
-        <v>0.009212318969462775</v>
+        <v>0.009212318969462778</v>
       </c>
       <c r="T5" t="n">
-        <v>0.009212318969462775</v>
+        <v>0.009212318969462785</v>
       </c>
       <c r="U5" t="n">
-        <v>0.007678083212913026</v>
+        <v>0.007678083212913043</v>
       </c>
       <c r="V5" t="n">
-        <v>0.008333819293928048</v>
+        <v>0.00833381929392805</v>
       </c>
       <c r="W5" t="n">
         <v>0.009212936074221708</v>
       </c>
       <c r="X5" t="n">
-        <v>0.00574296916070514</v>
+        <v>0.005742969160705137</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01233162935579258</v>
+        <v>0.0123316293557926</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00601394080391828</v>
+        <v>0.006013940803918285</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.009212318969462775</v>
+        <v>0.009212318969462781</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01249236388472693</v>
+        <v>0.01249236388472689</v>
       </c>
     </row>
     <row r="6">
@@ -7114,85 +7114,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008835665435419613</v>
+        <v>0.008835665435419611</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01096661574301863</v>
+        <v>0.01096661574301864</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01096661574301863</v>
+        <v>0.01096661574301864</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01047480036059727</v>
+        <v>0.01047480036059725</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006054194953997073</v>
+        <v>0.006054194953997075</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01096661477654494</v>
+        <v>0.01096661477654495</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01096661574301863</v>
+        <v>0.01096661574301864</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01096661574301863</v>
+        <v>0.01096661574301864</v>
       </c>
       <c r="J6" t="n">
         <v>0.01096369470626224</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01096661574301863</v>
+        <v>0.01096661574301864</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01096661574301863</v>
+        <v>0.01096661574301864</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01096661574301863</v>
+        <v>0.01096661574301864</v>
       </c>
       <c r="N6" t="n">
-        <v>0.08732258326960099</v>
+        <v>0.01096661574301864</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0116728085979538</v>
+        <v>0.01167280859795381</v>
       </c>
       <c r="P6" t="n">
         <v>0.01182639363786478</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01096661477654494</v>
+        <v>0.01096661477654495</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01096661574301863</v>
+        <v>0.01096661574301864</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01096661574301863</v>
+        <v>0.01096661574301864</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01096661574301863</v>
+        <v>0.01096661574301864</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01096661574301863</v>
+        <v>0.01096661574301864</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01340719169741418</v>
+        <v>0.0134071916974142</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01096661574301863</v>
+        <v>0.01096661574301864</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01096661574301863</v>
+        <v>0.01096661574301864</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01096661574301863</v>
+        <v>0.01096661574301864</v>
       </c>
       <c r="Z6" t="n">
         <v>0.009681841815255193</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01096661574301863</v>
+        <v>0.01096661574301864</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01096661574301863</v>
+        <v>0.01096661574301864</v>
       </c>
     </row>
     <row r="7">
@@ -7208,10 +7208,10 @@
         <v>0.01484543997852273</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01394118965909412</v>
+        <v>0.01394118965909413</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01146610038196652</v>
+        <v>0.01146610038196653</v>
       </c>
       <c r="F7" t="n">
         <v>0.01450265008117795</v>
@@ -7220,7 +7220,7 @@
         <v>0.01356316692096445</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0132782165438854</v>
+        <v>0.01327821654388541</v>
       </c>
       <c r="I7" t="n">
         <v>0.01365737401785696</v>
@@ -7229,22 +7229,22 @@
         <v>0.01354405038611802</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01309976249557883</v>
+        <v>0.01309976249557882</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01360882926978758</v>
+        <v>0.01360882926978757</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01043752781021678</v>
+        <v>0.01043752781021679</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01325757092673036</v>
+        <v>0.01325757092673038</v>
       </c>
       <c r="O7" t="n">
         <v>0.01413570233661483</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01386316680808785</v>
+        <v>0.01386316680808784</v>
       </c>
       <c r="Q7" t="n">
         <v>0.01427583557512278</v>
@@ -7253,7 +7253,7 @@
         <v>0.01363164472089844</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0139519551339165</v>
+        <v>0.01395195513391649</v>
       </c>
       <c r="T7" t="n">
         <v>0.01368329105876432</v>
@@ -7268,19 +7268,19 @@
         <v>0.0129151079391731</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01324295828439641</v>
+        <v>0.0132429582843964</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01366254043755426</v>
+        <v>0.01366254043755427</v>
       </c>
       <c r="Z7" t="n">
         <v>0.01414649040528039</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01312985954295134</v>
+        <v>0.01312985954295136</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01250041809215227</v>
+        <v>0.01250041809215228</v>
       </c>
     </row>
     <row r="8">
@@ -7299,7 +7299,7 @@
         <v>0.01447960451386875</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01158803600050809</v>
+        <v>0.0115880360005081</v>
       </c>
       <c r="F8" t="n">
         <v>0.01464454722730926</v>
@@ -7308,7 +7308,7 @@
         <v>0.0143163886724201</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01429320570834751</v>
+        <v>0.01429320570834752</v>
       </c>
       <c r="I8" t="n">
         <v>0.01439937181419849</v>
@@ -7317,7 +7317,7 @@
         <v>0.0143601168138682</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01424253065862196</v>
+        <v>0.01424253065862197</v>
       </c>
       <c r="L8" t="n">
         <v>0.01438283391880187</v>
@@ -7326,43 +7326,43 @@
         <v>0.01348656523524599</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01428396236296215</v>
+        <v>0.01428396236296216</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0145322302121519</v>
+        <v>0.01453223021215192</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0144538448983482</v>
+        <v>0.01445384489834821</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01457439350108396</v>
+        <v>0.01457439350108397</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01439306428256129</v>
+        <v>0.0143930642825613</v>
       </c>
       <c r="S8" t="n">
         <v>0.01448031384515031</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01440641547564105</v>
+        <v>0.01440641547564106</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01428301569548975</v>
+        <v>0.01428301569548976</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01460877096984496</v>
+        <v>0.01460877096984497</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01418514114665677</v>
+        <v>0.01418514114665678</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01427372814925495</v>
+        <v>0.01427372814925496</v>
       </c>
       <c r="Y8" t="n">
         <v>0.014398848097088</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01453631602630165</v>
+        <v>0.01453631602630166</v>
       </c>
       <c r="AA8" t="n">
         <v>0.01424673438100518</v>
@@ -7537,13 +7537,13 @@
         <v>0.01471551209259665</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01475115928018053</v>
+        <v>0.01475115928018052</v>
       </c>
       <c r="D2" t="n">
         <v>0.01475292777128437</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01170792118542779</v>
+        <v>0.0117079211854278</v>
       </c>
       <c r="F2" t="n">
         <v>0.01474466573763732</v>
@@ -7552,13 +7552,13 @@
         <v>0.01481641060442879</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01489501112624571</v>
+        <v>0.0148950111262457</v>
       </c>
       <c r="I2" t="n">
         <v>0.01477018992590986</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01482984362596106</v>
+        <v>0.01482984362596107</v>
       </c>
       <c r="K2" t="n">
         <v>0.0148341171250833</v>
@@ -7567,16 +7567,16 @@
         <v>0.01482688171059091</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0147890457125251</v>
+        <v>0.01478904571252509</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0147861319815821</v>
+        <v>0.01478613198158209</v>
       </c>
       <c r="O2" t="n">
         <v>0.01474731090374926</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0148384044094367</v>
+        <v>0.01483840440943669</v>
       </c>
       <c r="Q2" t="n">
         <v>0.01476612200524672</v>
@@ -7594,7 +7594,7 @@
         <v>0.01476045110903354</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01475447883979857</v>
+        <v>0.01475447883979856</v>
       </c>
       <c r="W2" t="n">
         <v>0.01500544214710908</v>
@@ -7603,10 +7603,10 @@
         <v>0.01488633860314666</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01504823175588826</v>
+        <v>0.01504823175588825</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01477231527681588</v>
+        <v>0.01477231527681587</v>
       </c>
       <c r="AA2" t="n">
         <v>0.01485493754767417</v>
@@ -7622,28 +7622,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01495605645569973</v>
+        <v>0.01495605645569974</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01497846240380695</v>
+        <v>0.01497846240380696</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01495605645569973</v>
+        <v>0.01495605645569974</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01187460589320135</v>
+        <v>0.01187460589320134</v>
       </c>
       <c r="F3" t="n">
         <v>0.0149669304883002</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01485762932211559</v>
+        <v>0.0148576293221156</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01495605645569973</v>
+        <v>0.01495605645569974</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01495605645569973</v>
+        <v>0.01495605645569974</v>
       </c>
       <c r="J3" t="n">
         <v>0.01495061238671487</v>
@@ -7652,55 +7652,55 @@
         <v>0.01496192750463317</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01495605645569973</v>
+        <v>0.01495605645569974</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01495597515085542</v>
+        <v>0.01495597515085543</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01495605645569973</v>
+        <v>0.01495605645569974</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01495596287967398</v>
+        <v>0.01495596287967399</v>
       </c>
       <c r="P3" t="n">
         <v>0.01495604461372349</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01495605526660385</v>
+        <v>0.01495605526660386</v>
       </c>
       <c r="R3" t="n">
         <v>0.01493376055529221</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01495605645569973</v>
+        <v>0.01495605645569974</v>
       </c>
       <c r="T3" t="n">
         <v>0.01495594911012592</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01495573908639742</v>
+        <v>0.01495573908639743</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01494019020140329</v>
+        <v>0.01494019020140328</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01495605645569973</v>
+        <v>0.01495605645569974</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0148217462202567</v>
+        <v>0.01482174622025671</v>
       </c>
       <c r="Y3" t="n">
         <v>0.01495582519073366</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01495765527086754</v>
+        <v>0.01495765527086755</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01495605645569973</v>
+        <v>0.01495605645569974</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01479255873712963</v>
+        <v>0.01479255873712964</v>
       </c>
     </row>
     <row r="4">
@@ -7710,61 +7710,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00789130575289527</v>
+        <v>0.007891305752895266</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01220684367762915</v>
+        <v>0.01220684367762916</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01806152105798737</v>
+        <v>0.0180615210579874</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01474977151155336</v>
+        <v>0.01474977151155338</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01343854065691961</v>
+        <v>0.01343854065691962</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04956841345128618</v>
+        <v>0.04956841345128614</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05835650460443214</v>
+        <v>0.05835650460443223</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02307834228684087</v>
+        <v>0.02307834228684088</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03605084092615458</v>
+        <v>0.03605084092615461</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03425263701808311</v>
+        <v>0.03425263701808313</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03340535706302907</v>
+        <v>0.03340535706302909</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02624463773115654</v>
+        <v>0.02624463773115653</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02654541252911463</v>
+        <v>0.02654541252911467</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01499545141581292</v>
+        <v>0.01499545141581304</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03632819792761193</v>
+        <v>0.03632819792761188</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01992901647555383</v>
+        <v>0.01992901647555382</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0355745629228991</v>
+        <v>0.03557456292289914</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02259638997441734</v>
+        <v>0.02259638997441733</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02462966654245976</v>
+        <v>0.02462966654245971</v>
       </c>
       <c r="U4" t="n">
         <v>0.01853543221392659</v>
@@ -7773,22 +7773,22 @@
         <v>0.02023878291305082</v>
       </c>
       <c r="W4" t="n">
-        <v>0.08173888608629258</v>
+        <v>0.08173888608629255</v>
       </c>
       <c r="X4" t="n">
-        <v>0.08200544207075046</v>
+        <v>0.08200544207075042</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.09149711953984685</v>
+        <v>0.09149711953984666</v>
       </c>
       <c r="Z4" t="n">
         <v>0.02008188152625973</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.04356104554027875</v>
+        <v>0.04356104554027874</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2499851556828779</v>
+        <v>0.249985155682878</v>
       </c>
     </row>
     <row r="5">
@@ -7798,85 +7798,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.005398603908115509</v>
+        <v>0.005398603908115519</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008131906802265955</v>
+        <v>0.00813190680226597</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008131906802265955</v>
+        <v>0.00813190680226597</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00667650363950922</v>
+        <v>0.006676503639509223</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005824420553739333</v>
+        <v>0.005824420553739339</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008698674962827778</v>
+        <v>0.008698674962827785</v>
       </c>
       <c r="H5" t="n">
-        <v>0.008131906802265955</v>
+        <v>0.00813190680226597</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008131906802265955</v>
+        <v>0.00813190680226597</v>
       </c>
       <c r="J5" t="n">
-        <v>0.008129489973537372</v>
+        <v>0.008129489973537371</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008131906802265955</v>
+        <v>0.00813190680226597</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008131906802265955</v>
+        <v>0.00813190680226597</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008131906802266003</v>
+        <v>0.008131906802266015</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02654541252911463</v>
+        <v>0.006013139786528352</v>
       </c>
       <c r="O5" t="n">
-        <v>0.006595395356959154</v>
+        <v>0.006595395356959164</v>
       </c>
       <c r="P5" t="n">
-        <v>0.006452670447639731</v>
+        <v>0.006452670447639747</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.004861447506159865</v>
+        <v>0.004861447506159868</v>
       </c>
       <c r="R5" t="n">
-        <v>0.008131906802265955</v>
+        <v>0.00813190680226597</v>
       </c>
       <c r="S5" t="n">
-        <v>0.008131906802265955</v>
+        <v>0.00813190680226597</v>
       </c>
       <c r="T5" t="n">
-        <v>0.008131906802265955</v>
+        <v>0.00813190680226597</v>
       </c>
       <c r="U5" t="n">
-        <v>0.006796220504670035</v>
+        <v>0.006796220504670041</v>
       </c>
       <c r="V5" t="n">
-        <v>0.007367853813926578</v>
+        <v>0.007367853813926589</v>
       </c>
       <c r="W5" t="n">
-        <v>0.008132443969932585</v>
+        <v>0.008132443969932604</v>
       </c>
       <c r="X5" t="n">
-        <v>0.005111960144668797</v>
+        <v>0.005111960144668799</v>
       </c>
       <c r="Y5" t="n">
         <v>0.01084683456903027</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.005347831404042178</v>
+        <v>0.005347831404042189</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.008131906802265955</v>
+        <v>0.00813190680226597</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01098707022581678</v>
+        <v>0.0109870702258168</v>
       </c>
     </row>
     <row r="6">
@@ -7886,85 +7886,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007409449915999645</v>
+        <v>0.007409449915999644</v>
       </c>
       <c r="C6" t="n">
-        <v>0.009155238574217975</v>
+        <v>0.00915523857421797</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009155238574217975</v>
+        <v>0.00915523857421797</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008752318304404719</v>
+        <v>0.008752318304404713</v>
       </c>
       <c r="F6" t="n">
         <v>0.005130718174389455</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009155239395276156</v>
+        <v>0.009155239395276162</v>
       </c>
       <c r="H6" t="n">
+        <v>0.00915523857421797</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.00915523857421797</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.009152821745489374</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.00915523857421797</v>
+      </c>
+      <c r="L6" t="n">
         <v>0.009155238574217975</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.009155238574217975</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.00915282174548937</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.009155238574217975</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.00915523857421798</v>
-      </c>
       <c r="M6" t="n">
-        <v>0.009155238574217975</v>
+        <v>0.00915523857421797</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02654541252911463</v>
+        <v>0.00915523857421797</v>
       </c>
       <c r="O6" t="n">
-        <v>0.009733791742792096</v>
+        <v>0.009733791742792094</v>
       </c>
       <c r="P6" t="n">
-        <v>0.009859616952090249</v>
+        <v>0.009859616952090252</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.009155239395276156</v>
+        <v>0.009155239395276162</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009155238574217975</v>
+        <v>0.00915523857421797</v>
       </c>
       <c r="S6" t="n">
-        <v>0.009155238574217975</v>
+        <v>0.00915523857421797</v>
       </c>
       <c r="T6" t="n">
-        <v>0.009155238574217975</v>
+        <v>0.00915523857421797</v>
       </c>
       <c r="U6" t="n">
-        <v>0.009155238574217975</v>
+        <v>0.00915523857421797</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01115460358536529</v>
+        <v>0.01115460358536528</v>
       </c>
       <c r="W6" t="n">
-        <v>0.009155238574217975</v>
+        <v>0.00915523857421797</v>
       </c>
       <c r="X6" t="n">
-        <v>0.009155238574217975</v>
+        <v>0.00915523857421797</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.009155238574217975</v>
+        <v>0.00915523857421797</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.008102683580930003</v>
+        <v>0.008102683580929998</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.009155238574217975</v>
+        <v>0.00915523857421797</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.009155238574217975</v>
+        <v>0.00915523857421797</v>
       </c>
     </row>
     <row r="7">
@@ -7977,82 +7977,82 @@
         <v>0.01481632863489475</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01475178410282661</v>
+        <v>0.0147517841028266</v>
       </c>
       <c r="D7" t="n">
         <v>0.01459935024484382</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01158015039217389</v>
+        <v>0.01158015039217388</v>
       </c>
       <c r="F7" t="n">
         <v>0.0147180566904026</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01358324947935666</v>
+        <v>0.01358324947935667</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01377512546430155</v>
+        <v>0.01377512546430156</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0144990976061711</v>
+        <v>0.01449909760617109</v>
       </c>
       <c r="J7" t="n">
         <v>0.01410335112664203</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01415994031755579</v>
+        <v>0.0141599403175558</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01415881955108521</v>
+        <v>0.0141588195510852</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01438943799190862</v>
+        <v>0.01438943799190863</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01440251469855719</v>
+        <v>0.01440251469855718</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01462618856517098</v>
+        <v>0.01462618856517099</v>
       </c>
       <c r="P7" t="n">
         <v>0.01408341768605577</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0145209417859528</v>
+        <v>0.01452094178595281</v>
       </c>
       <c r="R7" t="n">
         <v>0.01421479793742701</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01442207798280102</v>
+        <v>0.01442207798280101</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01445685157189217</v>
+        <v>0.01445685157189215</v>
       </c>
       <c r="U7" t="n">
         <v>0.01454910703432632</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01447404465586263</v>
+        <v>0.01447404465586264</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01310629392449255</v>
+        <v>0.01310629392449253</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01296286236413631</v>
+        <v>0.0129628623641363</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01285567247911426</v>
+        <v>0.01285567247911427</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01448920944672366</v>
+        <v>0.01448920944672367</v>
       </c>
       <c r="AA7" t="n">
         <v>0.01399535177288072</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.009423687494610049</v>
+        <v>0.009423687494610046</v>
       </c>
     </row>
     <row r="8">
@@ -8071,16 +8071,16 @@
         <v>0.01459062530858968</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01157394299408632</v>
+        <v>0.01157394299408633</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01463142736648017</v>
+        <v>0.01463142736648018</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01423656371476589</v>
+        <v>0.0142365637147659</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01435768376175578</v>
+        <v>0.01435768376175577</v>
       </c>
       <c r="I8" t="n">
         <v>0.01456227219313289</v>
@@ -8089,25 +8089,25 @@
         <v>0.0144443370525665</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01446921039918158</v>
+        <v>0.01446921039918157</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01446413637834803</v>
+        <v>0.01446413637834802</v>
       </c>
       <c r="M8" t="n">
         <v>0.0145312694997575</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01453426871804933</v>
+        <v>0.01453426871804931</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01459726253972199</v>
+        <v>0.014597262539722</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01444135637645088</v>
+        <v>0.01444135637645087</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01456814398492609</v>
+        <v>0.01456814398492611</v>
       </c>
       <c r="R8" t="n">
         <v>0.01446775452370416</v>
@@ -8116,10 +8116,10 @@
         <v>0.0145390990895848</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01455010218117108</v>
+        <v>0.01455010218117106</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01457543222948172</v>
+        <v>0.01457543222948171</v>
       </c>
       <c r="V8" t="n">
         <v>0.01454238113105985</v>
@@ -8128,13 +8128,13 @@
         <v>0.01416379430056637</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01404054052470051</v>
+        <v>0.01404054052470049</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01409265557931185</v>
+        <v>0.01409265557931184</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01455917093398216</v>
+        <v>0.01455917093398215</v>
       </c>
       <c r="AA8" t="n">
         <v>0.01441781385540735</v>
